--- a/outputs/VIC_mlf.xlsx
+++ b/outputs/VIC_mlf.xlsx
@@ -2449,8 +2449,10 @@
           <t>MURAYNL1</t>
         </is>
       </c>
-      <c r="B38" s="2" t="n">
-        <v/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>MURRAY</t>
+        </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
@@ -2505,8 +2507,10 @@
           <t>MURAYNL2</t>
         </is>
       </c>
-      <c r="B39" s="2" t="n">
-        <v/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>MURRAY</t>
+        </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
@@ -2561,8 +2565,10 @@
           <t>MURAYNL3</t>
         </is>
       </c>
-      <c r="B40" s="2" t="n">
-        <v/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>MURRAY</t>
+        </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
@@ -2741,8 +2747,10 @@
           <t>YWNL1</t>
         </is>
       </c>
-      <c r="B43" s="2" t="n">
-        <v/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>YALLOURN</t>
+        </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
@@ -3409,8 +3417,10 @@
           <t>MURR2-1</t>
         </is>
       </c>
-      <c r="B54" s="2" t="n">
-        <v/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>MURRAY2</t>
+        </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
@@ -3465,8 +3475,10 @@
           <t>MURR1-9</t>
         </is>
       </c>
-      <c r="B55" s="2" t="n">
-        <v/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>MURRAY1</t>
+        </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
@@ -3521,8 +3533,10 @@
           <t>MURR1-1</t>
         </is>
       </c>
-      <c r="B56" s="2" t="n">
-        <v/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>MURRAY1</t>
+        </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
@@ -3577,8 +3591,10 @@
           <t>MURR1-7</t>
         </is>
       </c>
-      <c r="B57" s="2" t="n">
-        <v/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>MURRAY1</t>
+        </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
@@ -3633,8 +3649,10 @@
           <t>MURR2-2</t>
         </is>
       </c>
-      <c r="B58" s="2" t="n">
-        <v/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>MURRAY2</t>
+        </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
@@ -3689,8 +3707,10 @@
           <t>MURR1-8</t>
         </is>
       </c>
-      <c r="B59" s="2" t="n">
-        <v/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>MURRAY1</t>
+        </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
@@ -3745,8 +3765,10 @@
           <t>MURR2-3</t>
         </is>
       </c>
-      <c r="B60" s="2" t="n">
-        <v/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>MURRAY2</t>
+        </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
@@ -3801,8 +3823,10 @@
           <t>MURR1-2</t>
         </is>
       </c>
-      <c r="B61" s="2" t="n">
-        <v/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>MURRAY1</t>
+        </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
@@ -3857,8 +3881,10 @@
           <t>MURR1-6</t>
         </is>
       </c>
-      <c r="B62" s="2" t="n">
-        <v/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>MURRAY1</t>
+        </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
@@ -3913,8 +3939,10 @@
           <t>MURR1-5</t>
         </is>
       </c>
-      <c r="B63" s="2" t="n">
-        <v/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>MURRAY1</t>
+        </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
@@ -3969,8 +3997,10 @@
           <t>MURR1-10</t>
         </is>
       </c>
-      <c r="B64" s="2" t="n">
-        <v/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>MURRAY1</t>
+        </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
@@ -4025,8 +4055,10 @@
           <t>MURR1-3</t>
         </is>
       </c>
-      <c r="B65" s="2" t="n">
-        <v/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>MURRAY1</t>
+        </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
@@ -4081,8 +4113,10 @@
           <t>MURR1-4</t>
         </is>
       </c>
-      <c r="B66" s="2" t="n">
-        <v/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>MURRAY1</t>
+        </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
@@ -4137,8 +4171,10 @@
           <t>MURR2-4</t>
         </is>
       </c>
-      <c r="B67" s="2" t="n">
-        <v/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>MURRAY2</t>
+        </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
@@ -5269,8 +5305,10 @@
           <t>LYNL1</t>
         </is>
       </c>
-      <c r="B88" s="2" t="n">
-        <v/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>LOYYANGA</t>
+        </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
@@ -6499,8 +6537,10 @@
           <t>LONGFORD</t>
         </is>
       </c>
-      <c r="B108" s="2" t="n">
-        <v/>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>LONGFORD</t>
+        </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
@@ -7701,8 +7741,10 @@
           <t>HASTING2</t>
         </is>
       </c>
-      <c r="B128" s="2" t="n">
-        <v/>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>HASTING</t>
+        </is>
       </c>
       <c r="C128" s="2" t="n">
         <v/>
@@ -7741,8 +7783,10 @@
           <t>HASTING1</t>
         </is>
       </c>
-      <c r="B129" s="2" t="n">
-        <v/>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>HASTING</t>
+        </is>
       </c>
       <c r="C129" s="2" t="n">
         <v/>
@@ -8207,8 +8251,10 @@
           <t>DG_VIC1</t>
         </is>
       </c>
-      <c r="B137" s="2" t="n">
-        <v/>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>DG_VIC1</t>
+        </is>
       </c>
       <c r="C137" s="2" t="n">
         <v/>
@@ -8263,8 +8309,10 @@
           <t>PORTWF</t>
         </is>
       </c>
-      <c r="B138" s="2" t="n">
-        <v/>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>PORTWF</t>
+        </is>
       </c>
       <c r="C138" s="2" t="n">
         <v/>
@@ -8747,8 +8795,10 @@
           <t>SNOWYGJP</t>
         </is>
       </c>
-      <c r="B146" s="2" t="n">
-        <v/>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>Jindabyne Pump At Guthega</t>
+        </is>
       </c>
       <c r="C146" s="2" t="n">
         <v/>
@@ -8803,8 +8853,10 @@
           <t>MORNL1</t>
         </is>
       </c>
-      <c r="B147" s="2" t="n">
-        <v/>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>ENERGYB</t>
+        </is>
       </c>
       <c r="C147" s="2" t="n">
         <v/>
@@ -8833,8 +8885,10 @@
           <t>APS</t>
         </is>
       </c>
-      <c r="B148" s="2" t="n">
-        <v/>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>APS</t>
+        </is>
       </c>
       <c r="C148" s="2" t="n">
         <v/>
@@ -8863,8 +8917,10 @@
           <t>MOR2</t>
         </is>
       </c>
-      <c r="B149" s="2" t="n">
-        <v/>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>ENERGYB</t>
+        </is>
       </c>
       <c r="C149" s="2" t="n">
         <v/>
@@ -8893,8 +8949,10 @@
           <t>MOR1</t>
         </is>
       </c>
-      <c r="B150" s="2" t="n">
-        <v/>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>ENERGYB</t>
+        </is>
       </c>
       <c r="C150" s="2" t="n">
         <v/>
@@ -8923,8 +8981,10 @@
           <t>MOR3</t>
         </is>
       </c>
-      <c r="B151" s="2" t="n">
-        <v/>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>ENERGYB</t>
+        </is>
       </c>
       <c r="C151" s="2" t="n">
         <v/>
@@ -8953,8 +9013,10 @@
           <t>HWPS6</t>
         </is>
       </c>
-      <c r="B152" s="2" t="n">
-        <v/>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>HAZEL</t>
+        </is>
       </c>
       <c r="C152" s="2" t="n">
         <v/>
@@ -8985,8 +9047,10 @@
           <t>HWPS2</t>
         </is>
       </c>
-      <c r="B153" s="2" t="n">
-        <v/>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>HAZEL</t>
+        </is>
       </c>
       <c r="C153" s="2" t="n">
         <v/>
@@ -9017,8 +9081,10 @@
           <t>HWPS1</t>
         </is>
       </c>
-      <c r="B154" s="2" t="n">
-        <v/>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>HAZEL</t>
+        </is>
       </c>
       <c r="C154" s="2" t="n">
         <v/>
@@ -9049,8 +9115,10 @@
           <t>HWPNL1</t>
         </is>
       </c>
-      <c r="B155" s="2" t="n">
-        <v/>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>HAZEL</t>
+        </is>
       </c>
       <c r="C155" s="2" t="n">
         <v/>
@@ -9081,8 +9149,10 @@
           <t>HWPS7</t>
         </is>
       </c>
-      <c r="B156" s="2" t="n">
-        <v/>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>HAZEL</t>
+        </is>
       </c>
       <c r="C156" s="2" t="n">
         <v/>
@@ -9113,8 +9183,10 @@
           <t>HWPS5</t>
         </is>
       </c>
-      <c r="B157" s="2" t="n">
-        <v/>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>HAZEL</t>
+        </is>
       </c>
       <c r="C157" s="2" t="n">
         <v/>
@@ -9145,8 +9217,10 @@
           <t>HWPS4</t>
         </is>
       </c>
-      <c r="B158" s="2" t="n">
-        <v/>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>HAZEL</t>
+        </is>
       </c>
       <c r="C158" s="2" t="n">
         <v/>
@@ -9177,8 +9251,10 @@
           <t>HWPS8</t>
         </is>
       </c>
-      <c r="B159" s="2" t="n">
-        <v/>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>HAZEL</t>
+        </is>
       </c>
       <c r="C159" s="2" t="n">
         <v/>
@@ -9209,8 +9285,10 @@
           <t>HWPS3</t>
         </is>
       </c>
-      <c r="B160" s="2" t="n">
-        <v/>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>HAZEL</t>
+        </is>
       </c>
       <c r="C160" s="2" t="n">
         <v/>
@@ -9241,8 +9319,10 @@
           <t>MORNW</t>
         </is>
       </c>
-      <c r="B161" s="2" t="n">
-        <v/>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>MORNW</t>
+        </is>
       </c>
       <c r="C161" s="2" t="n">
         <v/>
@@ -9275,8 +9355,10 @@
           <t>WYNDW</t>
         </is>
       </c>
-      <c r="B162" s="2" t="n">
-        <v/>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>WYNDW</t>
+        </is>
       </c>
       <c r="C162" s="2" t="n">
         <v/>
@@ -9309,8 +9391,10 @@
           <t>CORIO1</t>
         </is>
       </c>
-      <c r="B163" s="2" t="n">
-        <v/>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>CORIO</t>
+        </is>
       </c>
       <c r="C163" s="2" t="n">
         <v/>
@@ -9353,8 +9437,10 @@
           <t>BERWICK</t>
         </is>
       </c>
-      <c r="B164" s="2" t="n">
-        <v/>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>BERWICK</t>
+        </is>
       </c>
       <c r="C164" s="2" t="n">
         <v/>
@@ -9397,8 +9483,10 @@
           <t>SVALE1</t>
         </is>
       </c>
-      <c r="B165" s="2" t="n">
-        <v/>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>SVALE</t>
+        </is>
       </c>
       <c r="C165" s="2" t="n">
         <v/>
@@ -9443,8 +9531,10 @@
           <t>BROADMDW</t>
         </is>
       </c>
-      <c r="B166" s="2" t="n">
-        <v/>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>BROADMDW</t>
+        </is>
       </c>
       <c r="C166" s="2" t="n">
         <v/>
@@ -9489,8 +9579,10 @@
           <t>GANNBG1</t>
         </is>
       </c>
-      <c r="B167" s="2" t="n">
-        <v/>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>GANNBESS</t>
+        </is>
       </c>
       <c r="C167" s="2" t="n">
         <v/>
@@ -9575,8 +9667,10 @@
           <t>VBBG1</t>
         </is>
       </c>
-      <c r="B169" s="2" t="n">
-        <v/>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>VBB</t>
+        </is>
       </c>
       <c r="C169" s="2" t="n">
         <v/>
@@ -9611,8 +9705,10 @@
           <t>HBESSG1</t>
         </is>
       </c>
-      <c r="B170" s="2" t="n">
-        <v/>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>HBESS1</t>
+        </is>
       </c>
       <c r="C170" s="2" t="n">
         <v/>
@@ -9645,8 +9741,10 @@
           <t>BALBG1</t>
         </is>
       </c>
-      <c r="B171" s="2" t="n">
-        <v/>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>BALBESS</t>
+        </is>
       </c>
       <c r="C171" s="2" t="n">
         <v/>
@@ -9687,8 +9785,10 @@
           <t>PIBESSG1</t>
         </is>
       </c>
-      <c r="B172" s="2" t="n">
-        <v/>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>PIBESS</t>
+        </is>
       </c>
       <c r="C172" s="2" t="n">
         <v/>
@@ -9721,8 +9821,10 @@
           <t>BULBESG1</t>
         </is>
       </c>
-      <c r="B173" s="2" t="n">
-        <v/>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>BULGANA</t>
+        </is>
       </c>
       <c r="C173" s="2" t="n">
         <v/>
@@ -9813,8 +9915,10 @@
           <t>BBASEHOS</t>
         </is>
       </c>
-      <c r="B175" s="2" t="n">
-        <v/>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>BBASEHOS</t>
+        </is>
       </c>
       <c r="C175" s="2" t="n">
         <v/>
@@ -16611,8 +16715,10 @@
           <t>MURAYNL3</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
-        <v/>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>MURRAY</t>
+        </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
@@ -16665,8 +16771,10 @@
           <t>MURAYNL2</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
-        <v/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>MURRAY</t>
+        </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
@@ -16690,8 +16798,10 @@
           <t>MURAYNL1</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n">
-        <v/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>MURRAY</t>
+        </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
@@ -17513,8 +17623,10 @@
           <t>LONGFORD</t>
         </is>
       </c>
-      <c r="B38" s="2" t="n">
-        <v/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>LONGFORD</t>
+        </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>

--- a/outputs/VIC_mlf.xlsx
+++ b/outputs/VIC_mlf.xlsx
@@ -2451,13 +2451,17 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>MURRAY</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D38" s="2" t="inlineStr"/>
+          <t>Murray Power Station</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Hydro</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>25</v>
+      </c>
       <c r="E38" s="4" t="n">
         <v>0.9885</v>
       </c>
@@ -2509,13 +2513,17 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>MURRAY</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D39" s="2" t="inlineStr"/>
+          <t>Murray Power Station</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Hydro</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>25</v>
+      </c>
       <c r="E39" s="4" t="n">
         <v>0.9885</v>
       </c>
@@ -2567,13 +2575,17 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>MURRAY</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D40" s="2" t="inlineStr"/>
+          <t>Murray Power Station</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Hydro</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>25</v>
+      </c>
       <c r="E40" s="4" t="n">
         <v>0.9885</v>
       </c>
@@ -2749,13 +2761,17 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>YALLOURN</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D43" s="2" t="inlineStr"/>
+          <t>YALLOURN 'W' POWER STATION</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>25</v>
+      </c>
       <c r="E43" s="4" t="n">
         <v>0.9563</v>
       </c>
@@ -3422,10 +3438,10 @@
           <t>MURRAY2</t>
         </is>
       </c>
-      <c r="C54" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr"/>
+      <c r="D54" s="3" t="n">
+        <v>138</v>
+      </c>
       <c r="E54" s="4" t="n">
         <v>0.98</v>
       </c>
@@ -3480,10 +3496,10 @@
           <t>MURRAY1</t>
         </is>
       </c>
-      <c r="C55" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr"/>
+      <c r="D55" s="3" t="n">
+        <v>95</v>
+      </c>
       <c r="E55" s="4" t="n">
         <v>0.98</v>
       </c>
@@ -3538,10 +3554,10 @@
           <t>MURRAY1</t>
         </is>
       </c>
-      <c r="C56" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D56" s="2" t="inlineStr"/>
+      <c r="C56" s="2" t="inlineStr"/>
+      <c r="D56" s="3" t="n">
+        <v>95</v>
+      </c>
       <c r="E56" s="4" t="n">
         <v>0.98</v>
       </c>
@@ -3596,10 +3612,10 @@
           <t>MURRAY1</t>
         </is>
       </c>
-      <c r="C57" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D57" s="2" t="inlineStr"/>
+      <c r="C57" s="2" t="inlineStr"/>
+      <c r="D57" s="3" t="n">
+        <v>95</v>
+      </c>
       <c r="E57" s="4" t="n">
         <v>0.98</v>
       </c>
@@ -3654,10 +3670,10 @@
           <t>MURRAY2</t>
         </is>
       </c>
-      <c r="C58" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D58" s="2" t="inlineStr"/>
+      <c r="C58" s="2" t="inlineStr"/>
+      <c r="D58" s="3" t="n">
+        <v>138</v>
+      </c>
       <c r="E58" s="4" t="n">
         <v>0.98</v>
       </c>
@@ -3712,10 +3728,10 @@
           <t>MURRAY1</t>
         </is>
       </c>
-      <c r="C59" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D59" s="2" t="inlineStr"/>
+      <c r="C59" s="2" t="inlineStr"/>
+      <c r="D59" s="3" t="n">
+        <v>95</v>
+      </c>
       <c r="E59" s="4" t="n">
         <v>0.98</v>
       </c>
@@ -3770,10 +3786,10 @@
           <t>MURRAY2</t>
         </is>
       </c>
-      <c r="C60" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D60" s="2" t="inlineStr"/>
+      <c r="C60" s="2" t="inlineStr"/>
+      <c r="D60" s="3" t="n">
+        <v>138</v>
+      </c>
       <c r="E60" s="4" t="n">
         <v>0.98</v>
       </c>
@@ -3828,10 +3844,10 @@
           <t>MURRAY1</t>
         </is>
       </c>
-      <c r="C61" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D61" s="2" t="inlineStr"/>
+      <c r="C61" s="2" t="inlineStr"/>
+      <c r="D61" s="3" t="n">
+        <v>95</v>
+      </c>
       <c r="E61" s="4" t="n">
         <v>0.98</v>
       </c>
@@ -3886,10 +3902,10 @@
           <t>MURRAY1</t>
         </is>
       </c>
-      <c r="C62" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D62" s="2" t="inlineStr"/>
+      <c r="C62" s="2" t="inlineStr"/>
+      <c r="D62" s="3" t="n">
+        <v>95</v>
+      </c>
       <c r="E62" s="4" t="n">
         <v>0.98</v>
       </c>
@@ -3944,10 +3960,10 @@
           <t>MURRAY1</t>
         </is>
       </c>
-      <c r="C63" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D63" s="2" t="inlineStr"/>
+      <c r="C63" s="2" t="inlineStr"/>
+      <c r="D63" s="3" t="n">
+        <v>95</v>
+      </c>
       <c r="E63" s="4" t="n">
         <v>0.98</v>
       </c>
@@ -4002,10 +4018,10 @@
           <t>MURRAY1</t>
         </is>
       </c>
-      <c r="C64" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D64" s="2" t="inlineStr"/>
+      <c r="C64" s="2" t="inlineStr"/>
+      <c r="D64" s="3" t="n">
+        <v>95</v>
+      </c>
       <c r="E64" s="4" t="n">
         <v>0.98</v>
       </c>
@@ -4060,10 +4076,10 @@
           <t>MURRAY1</t>
         </is>
       </c>
-      <c r="C65" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D65" s="2" t="inlineStr"/>
+      <c r="C65" s="2" t="inlineStr"/>
+      <c r="D65" s="3" t="n">
+        <v>95</v>
+      </c>
       <c r="E65" s="4" t="n">
         <v>0.98</v>
       </c>
@@ -4118,10 +4134,10 @@
           <t>MURRAY1</t>
         </is>
       </c>
-      <c r="C66" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D66" s="2" t="inlineStr"/>
+      <c r="C66" s="2" t="inlineStr"/>
+      <c r="D66" s="3" t="n">
+        <v>95</v>
+      </c>
       <c r="E66" s="4" t="n">
         <v>0.98</v>
       </c>
@@ -4176,10 +4192,10 @@
           <t>MURRAY2</t>
         </is>
       </c>
-      <c r="C67" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D67" s="2" t="inlineStr"/>
+      <c r="C67" s="2" t="inlineStr"/>
+      <c r="D67" s="3" t="n">
+        <v>138</v>
+      </c>
       <c r="E67" s="4" t="n">
         <v>0.98</v>
       </c>
@@ -5307,13 +5323,17 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>LOYYANGA</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D88" s="2" t="inlineStr"/>
+          <t>LOY YANG A POWER STATION</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>25</v>
+      </c>
       <c r="E88" s="4" t="n">
         <v>0.9742</v>
       </c>
@@ -6539,13 +6559,17 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>LONGFORD</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D108" s="2" t="inlineStr"/>
+          <t>LONGFORD PLANT</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>44</v>
+      </c>
       <c r="E108" s="4" t="n">
         <v>0.9799</v>
       </c>
@@ -7743,13 +7767,13 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>HASTING</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D128" s="2" t="inlineStr"/>
+          <t>Hastings Generation Site</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr"/>
+      <c r="D128" s="3" t="n">
+        <v>14</v>
+      </c>
       <c r="E128" s="4" t="inlineStr"/>
       <c r="F128" s="4" t="inlineStr"/>
       <c r="G128" s="4" t="inlineStr"/>
@@ -7785,13 +7809,13 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>HASTING</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D129" s="2" t="inlineStr"/>
+          <t>Hastings Generation Site</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr"/>
+      <c r="D129" s="3" t="n">
+        <v>14</v>
+      </c>
       <c r="E129" s="4" t="inlineStr"/>
       <c r="F129" s="4" t="inlineStr"/>
       <c r="G129" s="4" t="inlineStr"/>
@@ -8253,13 +8277,13 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>DG_VIC1</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D137" s="2" t="inlineStr"/>
+          <t>VIC1 Dummy Generator</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr"/>
+      <c r="D137" s="3" t="n">
+        <v>3000</v>
+      </c>
       <c r="E137" s="4" t="n">
         <v>1</v>
       </c>
@@ -8311,13 +8335,17 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>PORTWF</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D138" s="2" t="inlineStr"/>
+          <t>Portland Wind Farm</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D138" s="3" t="n">
+        <v>148</v>
+      </c>
       <c r="E138" s="4" t="n">
         <v>1.0033</v>
       </c>
@@ -8855,13 +8883,17 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>ENERGYB</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D147" s="2" t="inlineStr"/>
+          <t>Energy Brix Complex Power Station</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="n">
+        <v>25</v>
+      </c>
       <c r="E147" s="4" t="n">
         <v>0.9799</v>
       </c>
@@ -8887,13 +8919,17 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>APS</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D148" s="2" t="inlineStr"/>
+          <t>ANGELSEA POWER STATION</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="n">
+        <v>165</v>
+      </c>
       <c r="E148" s="4" t="n">
         <v>0.9915</v>
       </c>
@@ -8919,7 +8955,7 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>ENERGYB</t>
+          <t>Energy Brix Complex Power Station</t>
         </is>
       </c>
       <c r="C149" s="2" t="n">
@@ -8951,7 +8987,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>ENERGYB</t>
+          <t>Energy Brix Complex Power Station</t>
         </is>
       </c>
       <c r="C150" s="2" t="n">
@@ -8983,7 +9019,7 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>ENERGYB</t>
+          <t>Energy Brix Complex Power Station</t>
         </is>
       </c>
       <c r="C151" s="2" t="n">
@@ -9015,13 +9051,17 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>HAZEL</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D152" s="2" t="inlineStr"/>
+          <t>Hazelwood Power Station</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="n">
+        <v>200</v>
+      </c>
       <c r="E152" s="4" t="n">
         <v>0.9723000000000001</v>
       </c>
@@ -9049,13 +9089,17 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>HAZEL</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D153" s="2" t="inlineStr"/>
+          <t>Hazelwood Power Station</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="n">
+        <v>220</v>
+      </c>
       <c r="E153" s="4" t="n">
         <v>0.9723000000000001</v>
       </c>
@@ -9083,13 +9127,17 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>HAZEL</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D154" s="2" t="inlineStr"/>
+          <t>Hazelwood Power Station</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="n">
+        <v>220</v>
+      </c>
       <c r="E154" s="4" t="n">
         <v>0.9723000000000001</v>
       </c>
@@ -9117,13 +9165,17 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>HAZEL</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D155" s="2" t="inlineStr"/>
+          <t>Hazelwood Power Station</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="n">
+        <v>25</v>
+      </c>
       <c r="E155" s="4" t="n">
         <v>0.9723000000000001</v>
       </c>
@@ -9151,13 +9203,17 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>HAZEL</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D156" s="2" t="inlineStr"/>
+          <t>Hazelwood Power Station</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D156" s="3" t="n">
+        <v>200</v>
+      </c>
       <c r="E156" s="4" t="n">
         <v>0.9723000000000001</v>
       </c>
@@ -9185,13 +9241,17 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>HAZEL</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D157" s="2" t="inlineStr"/>
+          <t>Hazelwood Power Station</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="n">
+        <v>200</v>
+      </c>
       <c r="E157" s="4" t="n">
         <v>0.9723000000000001</v>
       </c>
@@ -9219,13 +9279,17 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>HAZEL</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D158" s="2" t="inlineStr"/>
+          <t>Hazelwood Power Station</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D158" s="3" t="n">
+        <v>200</v>
+      </c>
       <c r="E158" s="4" t="n">
         <v>0.9723000000000001</v>
       </c>
@@ -9253,13 +9317,17 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>HAZEL</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D159" s="2" t="inlineStr"/>
+          <t>Hazelwood Power Station</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D159" s="3" t="n">
+        <v>200</v>
+      </c>
       <c r="E159" s="4" t="n">
         <v>0.9723000000000001</v>
       </c>
@@ -9287,13 +9355,17 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>HAZEL</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D160" s="2" t="inlineStr"/>
+          <t>Hazelwood Power Station</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D160" s="3" t="n">
+        <v>200</v>
+      </c>
       <c r="E160" s="4" t="n">
         <v>0.9723000000000001</v>
       </c>
@@ -9321,13 +9393,17 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>MORNW</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D161" s="2" t="inlineStr"/>
+          <t>Mornington Waste Disposal Facility</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>Other Renewable</t>
+        </is>
+      </c>
+      <c r="D161" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="E161" s="4" t="n">
         <v>0.9923999999999999</v>
       </c>
@@ -9357,13 +9433,17 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>WYNDW</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D162" s="2" t="inlineStr"/>
+          <t>Wyndham Waste Disposal Facility</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>Other Renewable</t>
+        </is>
+      </c>
+      <c r="D162" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="E162" s="4" t="n">
         <v>1.0032</v>
       </c>
@@ -9393,13 +9473,17 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>CORIO</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D163" s="2" t="inlineStr"/>
+          <t>Corio Landfill Gas Power Station</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>Other Renewable</t>
+        </is>
+      </c>
+      <c r="D163" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="E163" s="4" t="n">
         <v>0.9987</v>
       </c>
@@ -9439,13 +9523,13 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>BERWICK</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D164" s="2" t="inlineStr"/>
+          <t>Berwick Power Plant</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr"/>
+      <c r="D164" s="3" t="n">
+        <v>7</v>
+      </c>
       <c r="E164" s="4" t="n">
         <v>0.9923</v>
       </c>
@@ -9485,13 +9569,17 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>SVALE</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D165" s="2" t="inlineStr"/>
+          <t>Springvale Landfill Gas Power Station</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>Other Renewable</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="E165" s="4" t="n">
         <v>0.997</v>
       </c>
@@ -9533,13 +9621,17 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>BROADMDW</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D166" s="2" t="inlineStr"/>
+          <t>Broadmeadows Landfill Gas Power Station</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>Other Renewable</t>
+        </is>
+      </c>
+      <c r="D166" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="E166" s="4" t="n">
         <v>1</v>
       </c>
@@ -9581,13 +9673,17 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>GANNBESS</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D167" s="2" t="inlineStr"/>
+          <t>Gannawarra Energy Storage System</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="n">
+        <v>30</v>
+      </c>
       <c r="E167" s="4" t="inlineStr"/>
       <c r="F167" s="4" t="inlineStr"/>
       <c r="G167" s="4" t="inlineStr"/>
@@ -9669,13 +9765,17 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>VBB</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D169" s="2" t="inlineStr"/>
+          <t>Victorian Big Battery</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="D169" s="3" t="n">
+        <v>360</v>
+      </c>
       <c r="E169" s="4" t="inlineStr"/>
       <c r="F169" s="4" t="inlineStr"/>
       <c r="G169" s="4" t="inlineStr"/>
@@ -9707,13 +9807,17 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>HBESS1</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D170" s="2" t="inlineStr"/>
+          <t>Hazelwood Battery Energy Storage System</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="D170" s="3" t="n">
+        <v>200</v>
+      </c>
       <c r="E170" s="4" t="inlineStr"/>
       <c r="F170" s="4" t="inlineStr"/>
       <c r="G170" s="4" t="inlineStr"/>
@@ -9743,13 +9847,17 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>BALBESS</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D171" s="2" t="inlineStr"/>
+          <t>Ballarat Battery Energy Storage System</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="D171" s="3" t="n">
+        <v>30</v>
+      </c>
       <c r="E171" s="4" t="inlineStr"/>
       <c r="F171" s="4" t="inlineStr"/>
       <c r="G171" s="4" t="inlineStr"/>
@@ -9787,13 +9895,17 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>PIBESS</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D172" s="2" t="inlineStr"/>
+          <t>Phillip Island BESS</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="D172" s="3" t="n">
+        <v>7</v>
+      </c>
       <c r="E172" s="4" t="inlineStr"/>
       <c r="F172" s="4" t="inlineStr"/>
       <c r="G172" s="4" t="inlineStr"/>
@@ -9823,13 +9935,17 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>BULGANA</t>
-        </is>
-      </c>
-      <c r="C173" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D173" s="2" t="inlineStr"/>
+          <t>Bulgana Green Power Hub</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="D173" s="3" t="n">
+        <v>24</v>
+      </c>
       <c r="E173" s="4" t="inlineStr"/>
       <c r="F173" s="4" t="inlineStr"/>
       <c r="G173" s="4" t="inlineStr"/>
@@ -9917,13 +10033,17 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>BBASEHOS</t>
-        </is>
-      </c>
-      <c r="C175" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D175" s="2" t="inlineStr"/>
+          <t>Ballarat Base Hospital Plant</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D175" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="E175" s="4" t="n">
         <v>1.0207</v>
       </c>
@@ -16717,11 +16837,13 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>MURRAY</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v/>
+          <t>Murray Power Station</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Hydro</t>
+        </is>
       </c>
       <c r="D4" s="4" t="n">
         <v>0.9565</v>
@@ -16773,11 +16895,13 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>MURRAY</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v/>
+          <t>Murray Power Station</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Hydro</t>
+        </is>
       </c>
       <c r="D6" s="4" t="n">
         <v>0.9565</v>
@@ -16800,11 +16924,13 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>MURRAY</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v/>
+          <t>Murray Power Station</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Hydro</t>
+        </is>
       </c>
       <c r="D7" s="4" t="n">
         <v>0.9565</v>
@@ -17625,11 +17751,13 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>LONGFORD</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="n">
-        <v/>
+          <t>LONGFORD PLANT</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
       </c>
       <c r="D38" s="4" t="n">
         <v>0.992</v>

--- a/outputs/VIC_mlf.xlsx
+++ b/outputs/VIC_mlf.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R190"/>
+  <dimension ref="A1:R191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -622,12 +622,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MUWAWF1</t>
+          <t>MUWAWF2</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Murra Warra Wind Farm</t>
+          <t>Murra Warra Wind Farm Stage 2</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -636,20 +636,14 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>231.8</v>
+        <v>209</v>
       </c>
       <c r="E3" s="4" t="inlineStr"/>
       <c r="F3" s="4" t="inlineStr"/>
       <c r="G3" s="4" t="inlineStr"/>
-      <c r="H3" s="4" t="n">
-        <v>0.9549</v>
-      </c>
-      <c r="I3" s="4" t="n">
-        <v>0.8885</v>
-      </c>
-      <c r="J3" s="4" t="n">
-        <v>0.8885</v>
-      </c>
+      <c r="H3" s="4" t="inlineStr"/>
+      <c r="I3" s="4" t="inlineStr"/>
+      <c r="J3" s="4" t="inlineStr"/>
       <c r="K3" s="4" t="n">
         <v>0.8883</v>
       </c>
@@ -678,12 +672,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>MUWAWF2</t>
+          <t>MUWAWF1</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Murra Warra Wind Farm Stage 2</t>
+          <t>Murra Warra Wind Farm</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -692,14 +686,20 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>209</v>
+        <v>231.8</v>
       </c>
       <c r="E4" s="4" t="inlineStr"/>
       <c r="F4" s="4" t="inlineStr"/>
       <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="n">
+        <v>0.9549</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>0.8885</v>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>0.8885</v>
+      </c>
       <c r="K4" s="4" t="n">
         <v>0.8883</v>
       </c>
@@ -807,13 +807,21 @@
       <c r="K6" s="4" t="inlineStr"/>
       <c r="L6" s="4" t="inlineStr"/>
       <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr"/>
-      <c r="O6" s="4" t="inlineStr"/>
+      <c r="N6" s="4" t="n">
+        <v>0.8733</v>
+      </c>
+      <c r="O6" s="4" t="n">
+        <v>0.8907</v>
+      </c>
       <c r="P6" s="4" t="n">
         <v>0.8868</v>
       </c>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="5" t="inlineStr"/>
+      <c r="Q6" s="4" t="n">
+        <v>-0.0039</v>
+      </c>
+      <c r="R6" s="5" t="n">
+        <v>-0.44</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1306,12 +1314,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>NUMURSF1</t>
+          <t>WUNUSF1</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Numurkah Solar Farm</t>
+          <t>Wunghnu Solar Farm</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1320,29 +1328,17 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>112</v>
+        <v>93.5</v>
       </c>
       <c r="E16" s="4" t="inlineStr"/>
       <c r="F16" s="4" t="inlineStr"/>
       <c r="G16" s="4" t="inlineStr"/>
-      <c r="H16" s="4" t="n">
-        <v>0.982</v>
-      </c>
-      <c r="I16" s="4" t="n">
-        <v>0.9896</v>
-      </c>
-      <c r="J16" s="4" t="n">
-        <v>0.9945000000000001</v>
-      </c>
-      <c r="K16" s="4" t="n">
-        <v>0.9963</v>
-      </c>
-      <c r="L16" s="4" t="n">
-        <v>0.9715</v>
-      </c>
-      <c r="M16" s="4" t="n">
-        <v>0.9738</v>
-      </c>
+      <c r="H16" s="4" t="inlineStr"/>
+      <c r="I16" s="4" t="inlineStr"/>
+      <c r="J16" s="4" t="inlineStr"/>
+      <c r="K16" s="4" t="inlineStr"/>
+      <c r="L16" s="4" t="inlineStr"/>
+      <c r="M16" s="4" t="inlineStr"/>
       <c r="N16" s="4" t="n">
         <v>0.9477</v>
       </c>
@@ -1362,12 +1358,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>WUNUSF1</t>
+          <t>NUMURSF1</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Wunghnu Solar Farm</t>
+          <t>Numurkah Solar Farm</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1376,17 +1372,29 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>93.5</v>
+        <v>112</v>
       </c>
       <c r="E17" s="4" t="inlineStr"/>
       <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="4" t="inlineStr"/>
-      <c r="H17" s="4" t="inlineStr"/>
-      <c r="I17" s="4" t="inlineStr"/>
-      <c r="J17" s="4" t="inlineStr"/>
-      <c r="K17" s="4" t="inlineStr"/>
-      <c r="L17" s="4" t="inlineStr"/>
-      <c r="M17" s="4" t="inlineStr"/>
+      <c r="H17" s="4" t="n">
+        <v>0.982</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>0.9896</v>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v>0.9945000000000001</v>
+      </c>
+      <c r="K17" s="4" t="n">
+        <v>0.9963</v>
+      </c>
+      <c r="L17" s="4" t="n">
+        <v>0.9715</v>
+      </c>
+      <c r="M17" s="4" t="n">
+        <v>0.9738</v>
+      </c>
       <c r="N17" s="4" t="n">
         <v>0.9477</v>
       </c>
@@ -1492,12 +1500,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>WINTSF1</t>
+          <t>GLRWNSF1</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Winton Solar Farm</t>
+          <t>Glenrowan West Solar Farm</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1506,7 +1514,7 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="E20" s="4" t="inlineStr"/>
       <c r="F20" s="4" t="inlineStr"/>
@@ -1544,12 +1552,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>GLRWNSF1</t>
+          <t>WINTSF1</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Glenrowan West Solar Farm</t>
+          <t>Winton Solar Farm</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1558,7 +1566,7 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="E21" s="4" t="inlineStr"/>
       <c r="F21" s="4" t="inlineStr"/>
@@ -1726,12 +1734,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>GANNSF1</t>
+          <t>COHUNSF1</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Gannawarra Solar Farm</t>
+          <t>Cohuna Solar Farm</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1740,19 +1748,13 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="E25" s="4" t="inlineStr"/>
       <c r="F25" s="4" t="inlineStr"/>
-      <c r="G25" s="4" t="n">
-        <v>1.044</v>
-      </c>
-      <c r="H25" s="4" t="n">
-        <v>0.9729</v>
-      </c>
-      <c r="I25" s="4" t="n">
-        <v>0.8994</v>
-      </c>
+      <c r="G25" s="4" t="inlineStr"/>
+      <c r="H25" s="4" t="inlineStr"/>
+      <c r="I25" s="4" t="inlineStr"/>
       <c r="J25" s="4" t="n">
         <v>0.8863</v>
       </c>
@@ -1784,12 +1786,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>COHUNSF1</t>
+          <t>GANNSF1</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Cohuna Solar Farm</t>
+          <t>Gannawarra Solar Farm</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1798,13 +1800,19 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="E26" s="4" t="inlineStr"/>
       <c r="F26" s="4" t="inlineStr"/>
-      <c r="G26" s="4" t="inlineStr"/>
-      <c r="H26" s="4" t="inlineStr"/>
-      <c r="I26" s="4" t="inlineStr"/>
+      <c r="G26" s="4" t="n">
+        <v>1.044</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>0.9729</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>0.8994</v>
+      </c>
       <c r="J26" s="4" t="n">
         <v>0.8863</v>
       </c>
@@ -1988,12 +1996,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>BRYB2WF2</t>
+          <t>BRYB1WF1</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Berrybank 2 Wind Farm</t>
+          <t>Berrybank Wind Farm</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2002,15 +2010,19 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>109</v>
+        <v>180.6</v>
       </c>
       <c r="E30" s="4" t="inlineStr"/>
       <c r="F30" s="4" t="inlineStr"/>
       <c r="G30" s="4" t="inlineStr"/>
       <c r="H30" s="4" t="inlineStr"/>
       <c r="I30" s="4" t="inlineStr"/>
-      <c r="J30" s="4" t="inlineStr"/>
-      <c r="K30" s="4" t="inlineStr"/>
+      <c r="J30" s="4" t="n">
+        <v>0.9482</v>
+      </c>
+      <c r="K30" s="4" t="n">
+        <v>0.9431</v>
+      </c>
       <c r="L30" s="4" t="n">
         <v>0.9496</v>
       </c>
@@ -2036,12 +2048,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>BRYB1WF1</t>
+          <t>BRYB2WF2</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Berrybank Wind Farm</t>
+          <t>Berrybank 2 Wind Farm</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2050,19 +2062,15 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>180.6</v>
+        <v>109</v>
       </c>
       <c r="E31" s="4" t="inlineStr"/>
       <c r="F31" s="4" t="inlineStr"/>
       <c r="G31" s="4" t="inlineStr"/>
       <c r="H31" s="4" t="inlineStr"/>
       <c r="I31" s="4" t="inlineStr"/>
-      <c r="J31" s="4" t="n">
-        <v>0.9482</v>
-      </c>
-      <c r="K31" s="4" t="n">
-        <v>0.9431</v>
-      </c>
+      <c r="J31" s="4" t="inlineStr"/>
+      <c r="K31" s="4" t="inlineStr"/>
       <c r="L31" s="4" t="n">
         <v>0.9496</v>
       </c>
@@ -2366,52 +2374,32 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>MERCER01</t>
+          <t>MOORABS1</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Mt Mercer Wind Farm</t>
+          <t xml:space="preserve">Moorabool Wind Farm </t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>131.2</v>
-      </c>
-      <c r="E37" s="4" t="n">
-        <v>1.0033</v>
-      </c>
-      <c r="F37" s="4" t="n">
-        <v>1.0048</v>
-      </c>
-      <c r="G37" s="4" t="n">
-        <v>1.001</v>
-      </c>
-      <c r="H37" s="4" t="n">
-        <v>0.9909</v>
-      </c>
-      <c r="I37" s="4" t="n">
-        <v>0.965</v>
-      </c>
-      <c r="J37" s="4" t="n">
-        <v>0.9500999999999999</v>
-      </c>
-      <c r="K37" s="4" t="n">
-        <v>0.9459</v>
-      </c>
-      <c r="L37" s="4" t="n">
-        <v>0.948</v>
-      </c>
-      <c r="M37" s="4" t="n">
-        <v>0.9576</v>
-      </c>
-      <c r="N37" s="4" t="n">
-        <v>0.9475</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E37" s="4" t="inlineStr"/>
+      <c r="F37" s="4" t="inlineStr"/>
+      <c r="G37" s="4" t="inlineStr"/>
+      <c r="H37" s="4" t="inlineStr"/>
+      <c r="I37" s="4" t="inlineStr"/>
+      <c r="J37" s="4" t="inlineStr"/>
+      <c r="K37" s="4" t="inlineStr"/>
+      <c r="L37" s="4" t="inlineStr"/>
+      <c r="M37" s="4" t="inlineStr"/>
+      <c r="N37" s="4" t="inlineStr"/>
       <c r="O37" s="4" t="n">
         <v>0.9569</v>
       </c>
@@ -2428,12 +2416,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>ELAINWF1</t>
+          <t>MERCER01</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Elaine Wind Farm</t>
+          <t>Mt Mercer Wind Farm</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2442,12 +2430,20 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>83.59999999999999</v>
-      </c>
-      <c r="E38" s="4" t="inlineStr"/>
-      <c r="F38" s="4" t="inlineStr"/>
-      <c r="G38" s="4" t="inlineStr"/>
-      <c r="H38" s="4" t="inlineStr"/>
+        <v>131.2</v>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>1.0033</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>1.0048</v>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>1.001</v>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>0.9909</v>
+      </c>
       <c r="I38" s="4" t="n">
         <v>0.965</v>
       </c>
@@ -2482,43 +2478,61 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>MOORABS1</t>
+          <t>ELAINWF1</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Moorabool Wind Farm </t>
+          <t>Elaine Wind Farm</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>2</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="E39" s="4" t="inlineStr"/>
       <c r="F39" s="4" t="inlineStr"/>
       <c r="G39" s="4" t="inlineStr"/>
       <c r="H39" s="4" t="inlineStr"/>
-      <c r="I39" s="4" t="inlineStr"/>
-      <c r="J39" s="4" t="inlineStr"/>
-      <c r="K39" s="4" t="inlineStr"/>
-      <c r="L39" s="4" t="inlineStr"/>
-      <c r="M39" s="4" t="inlineStr"/>
-      <c r="N39" s="4" t="inlineStr"/>
-      <c r="O39" s="4" t="inlineStr"/>
+      <c r="I39" s="4" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="J39" s="4" t="n">
+        <v>0.9500999999999999</v>
+      </c>
+      <c r="K39" s="4" t="n">
+        <v>0.9459</v>
+      </c>
+      <c r="L39" s="4" t="n">
+        <v>0.948</v>
+      </c>
+      <c r="M39" s="4" t="n">
+        <v>0.9576</v>
+      </c>
+      <c r="N39" s="4" t="n">
+        <v>0.9475</v>
+      </c>
+      <c r="O39" s="4" t="n">
+        <v>0.9569</v>
+      </c>
       <c r="P39" s="4" t="n">
         <v>0.9556</v>
       </c>
-      <c r="Q39" s="4" t="inlineStr"/>
-      <c r="R39" s="5" t="inlineStr"/>
+      <c r="Q39" s="4" t="n">
+        <v>-0.0013</v>
+      </c>
+      <c r="R39" s="5" t="n">
+        <v>-0.14</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>MURAYNL1</t>
+          <t>MURRAY</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2532,7 +2546,7 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>25</v>
+        <v>1500</v>
       </c>
       <c r="E40" s="4" t="n">
         <v>0.9885</v>
@@ -2580,7 +2594,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>MURAYNL2</t>
+          <t>MURAYNL1</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2704,7 +2718,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>MURRAY</t>
+          <t>MURAYNL2</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2718,7 +2732,7 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>1500</v>
+        <v>25</v>
       </c>
       <c r="E43" s="4" t="n">
         <v>0.9885</v>
@@ -3287,23 +3301,31 @@
       <c r="K52" s="4" t="inlineStr"/>
       <c r="L52" s="4" t="inlineStr"/>
       <c r="M52" s="4" t="inlineStr"/>
-      <c r="N52" s="4" t="inlineStr"/>
-      <c r="O52" s="4" t="inlineStr"/>
+      <c r="N52" s="4" t="n">
+        <v>0.9605</v>
+      </c>
+      <c r="O52" s="4" t="n">
+        <v>0.9766</v>
+      </c>
       <c r="P52" s="4" t="n">
         <v>0.9761</v>
       </c>
-      <c r="Q52" s="4" t="inlineStr"/>
-      <c r="R52" s="5" t="inlineStr"/>
+      <c r="Q52" s="4" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="R52" s="5" t="n">
+        <v>-0.05</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>CHALLHWF</t>
+          <t>HEPWIND1</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Challicum Hills Wind Farm</t>
+          <t>Hepburn Community Wind Farm</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3312,22 +3334,22 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>52.5</v>
+        <v>4.1</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>1.0988</v>
+        <v>1.0207</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>1.0988</v>
+        <v>1.0209</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>1.0988</v>
+        <v>1.016</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>0.9957</v>
+        <v>1.0016</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>0.9193</v>
+        <v>0.9716</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>0.9711</v>
@@ -3418,12 +3440,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>YSWF1</t>
+          <t>CHALLHWF</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Yaloak South Wind Farm</t>
+          <t>Challicum Hills Wind Farm</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3432,18 +3454,22 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="E55" s="4" t="inlineStr"/>
-      <c r="F55" s="4" t="inlineStr"/>
+        <v>52.5</v>
+      </c>
+      <c r="E55" s="4" t="n">
+        <v>1.0988</v>
+      </c>
+      <c r="F55" s="4" t="n">
+        <v>1.0988</v>
+      </c>
       <c r="G55" s="4" t="n">
-        <v>1.016</v>
+        <v>1.0988</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v>1.0016</v>
+        <v>0.9957</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>0.9716</v>
+        <v>0.9193</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>0.9711</v>
@@ -3476,12 +3502,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>HEPWIND1</t>
+          <t>YSWF1</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Hepburn Community Wind Farm</t>
+          <t>Yaloak South Wind Farm</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3490,14 +3516,10 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="E56" s="4" t="n">
-        <v>1.0207</v>
-      </c>
-      <c r="F56" s="4" t="n">
-        <v>1.0209</v>
-      </c>
+        <v>28.7</v>
+      </c>
+      <c r="E56" s="4" t="inlineStr"/>
+      <c r="F56" s="4" t="inlineStr"/>
       <c r="G56" s="4" t="n">
         <v>1.016</v>
       </c>
@@ -3563,28 +3585,36 @@
       <c r="K57" s="4" t="inlineStr"/>
       <c r="L57" s="4" t="inlineStr"/>
       <c r="M57" s="4" t="inlineStr"/>
-      <c r="N57" s="4" t="inlineStr"/>
-      <c r="O57" s="4" t="inlineStr"/>
+      <c r="N57" s="4" t="n">
+        <v>0.9836</v>
+      </c>
+      <c r="O57" s="4" t="n">
+        <v>0.9704</v>
+      </c>
       <c r="P57" s="4" t="n">
         <v>0.9794</v>
       </c>
-      <c r="Q57" s="4" t="inlineStr"/>
-      <c r="R57" s="5" t="inlineStr"/>
+      <c r="Q57" s="4" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="R57" s="5" t="n">
+        <v>0.93</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>MURR2-1</t>
+          <t>MURR1-10</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>MURRAY2</t>
+          <t>MURRAY1</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr"/>
       <c r="D58" s="3" t="n">
-        <v>138</v>
+        <v>95</v>
       </c>
       <c r="E58" s="4" t="n">
         <v>0.98</v>
@@ -3632,7 +3662,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>MURR1-9</t>
+          <t>MURR1-1</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3690,7 +3720,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>MURR1-10</t>
+          <t>MURR1-8</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3748,17 +3778,17 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>MURR1-7</t>
+          <t>MURR2-4</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>MURRAY1</t>
+          <t>MURRAY2</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr"/>
       <c r="D61" s="3" t="n">
-        <v>95</v>
+        <v>138</v>
       </c>
       <c r="E61" s="4" t="n">
         <v>0.98</v>
@@ -3806,17 +3836,17 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>MURR2-2</t>
+          <t>MURR1-2</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>MURRAY2</t>
+          <t>MURRAY1</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr"/>
       <c r="D62" s="3" t="n">
-        <v>138</v>
+        <v>95</v>
       </c>
       <c r="E62" s="4" t="n">
         <v>0.98</v>
@@ -3864,17 +3894,17 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>MURR1-8</t>
+          <t>MURR2-3</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>MURRAY1</t>
+          <t>MURRAY2</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr"/>
       <c r="D63" s="3" t="n">
-        <v>95</v>
+        <v>138</v>
       </c>
       <c r="E63" s="4" t="n">
         <v>0.98</v>
@@ -3922,17 +3952,17 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>MURR2-3</t>
+          <t>MURR1-3</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>MURRAY2</t>
+          <t>MURRAY1</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr"/>
       <c r="D64" s="3" t="n">
-        <v>138</v>
+        <v>95</v>
       </c>
       <c r="E64" s="4" t="n">
         <v>0.98</v>
@@ -3980,17 +4010,17 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>MURR1-3</t>
+          <t>MURR2-1</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>MURRAY1</t>
+          <t>MURRAY2</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr"/>
       <c r="D65" s="3" t="n">
-        <v>95</v>
+        <v>138</v>
       </c>
       <c r="E65" s="4" t="n">
         <v>0.98</v>
@@ -4038,7 +4068,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>MURR1-6</t>
+          <t>MURR1-5</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -4096,7 +4126,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>MURR1-5</t>
+          <t>MURR1-6</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -4154,7 +4184,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>MURR1-1</t>
+          <t>MURR1-7</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -4212,7 +4242,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>MURR1-2</t>
+          <t>MURR1-9</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -4270,17 +4300,17 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>MURR1-4</t>
+          <t>MURR2-2</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>MURRAY1</t>
+          <t>MURRAY2</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr"/>
       <c r="D70" s="3" t="n">
-        <v>95</v>
+        <v>138</v>
       </c>
       <c r="E70" s="4" t="n">
         <v>0.98</v>
@@ -4328,17 +4358,17 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>MURR2-4</t>
+          <t>MURR1-4</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>MURRAY2</t>
+          <t>MURRAY1</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr"/>
       <c r="D71" s="3" t="n">
-        <v>138</v>
+        <v>95</v>
       </c>
       <c r="E71" s="4" t="n">
         <v>0.98</v>
@@ -4386,7 +4416,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>GPWFEST1</t>
+          <t>GPWFEST3</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -4474,7 +4504,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>GPWFEST3</t>
+          <t>GPWFEST1</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -4564,12 +4594,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>JLB03</t>
+          <t>JLA02</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Jeeralang "B" Power Station</t>
+          <t>Jeeralang "A" Power Station</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -4578,7 +4608,7 @@
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="E76" s="4" t="n">
         <v>0.9667</v>
@@ -4626,12 +4656,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>JLB02</t>
+          <t>JLA04</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Jeeralang "B" Power Station</t>
+          <t>Jeeralang "A" Power Station</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -4640,7 +4670,7 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="E77" s="4" t="n">
         <v>0.9667</v>
@@ -4688,12 +4718,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>JLB01</t>
+          <t>JLA01</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Jeeralang "B" Power Station</t>
+          <t>Jeeralang "A" Power Station</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -4702,7 +4732,7 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="E78" s="4" t="n">
         <v>0.9667</v>
@@ -4750,12 +4780,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>JLA03</t>
+          <t>JLB01</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Jeeralang "A" Power Station</t>
+          <t>Jeeralang "B" Power Station</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -4764,7 +4794,7 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="E79" s="4" t="n">
         <v>0.9667</v>
@@ -4812,7 +4842,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>JLA04</t>
+          <t>JLA03</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4874,12 +4904,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>JLA01</t>
+          <t>JLB03</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Jeeralang "A" Power Station</t>
+          <t>Jeeralang "B" Power Station</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -4888,7 +4918,7 @@
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="E81" s="4" t="n">
         <v>0.9667</v>
@@ -4936,43 +4966,63 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>GPWFWST2</t>
+          <t>JLB02</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Golden Plains Wind Farm West</t>
+          <t>Jeeralang "B" Power Station</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>310</v>
-      </c>
-      <c r="E82" s="4" t="inlineStr"/>
-      <c r="F82" s="4" t="inlineStr"/>
-      <c r="G82" s="4" t="inlineStr"/>
-      <c r="H82" s="4" t="inlineStr"/>
-      <c r="I82" s="4" t="inlineStr"/>
-      <c r="J82" s="4" t="inlineStr"/>
-      <c r="K82" s="4" t="inlineStr"/>
-      <c r="L82" s="4" t="inlineStr"/>
-      <c r="M82" s="4" t="inlineStr"/>
-      <c r="N82" s="4" t="inlineStr"/>
+        <v>76</v>
+      </c>
+      <c r="E82" s="4" t="n">
+        <v>0.9667</v>
+      </c>
+      <c r="F82" s="4" t="n">
+        <v>0.9641</v>
+      </c>
+      <c r="G82" s="4" t="n">
+        <v>0.983</v>
+      </c>
+      <c r="H82" s="4" t="n">
+        <v>0.9782999999999999</v>
+      </c>
+      <c r="I82" s="4" t="n">
+        <v>0.9731</v>
+      </c>
+      <c r="J82" s="4" t="n">
+        <v>0.9734</v>
+      </c>
+      <c r="K82" s="4" t="n">
+        <v>0.9755</v>
+      </c>
+      <c r="L82" s="4" t="n">
+        <v>0.9727</v>
+      </c>
+      <c r="M82" s="4" t="n">
+        <v>0.9764</v>
+      </c>
+      <c r="N82" s="4" t="n">
+        <v>0.9789</v>
+      </c>
       <c r="O82" s="4" t="n">
-        <v>0.9837</v>
+        <v>0.9768</v>
       </c>
       <c r="P82" s="4" t="n">
         <v>0.9823</v>
       </c>
       <c r="Q82" s="4" t="n">
-        <v>-0.0014</v>
+        <v>0.0055</v>
       </c>
       <c r="R82" s="5" t="n">
-        <v>-0.14</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="83">
@@ -5020,63 +5070,43 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>JLA02</t>
+          <t>GPWFWST2</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Jeeralang "A" Power Station</t>
+          <t>Golden Plains Wind Farm West</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="E84" s="4" t="n">
-        <v>0.9667</v>
-      </c>
-      <c r="F84" s="4" t="n">
-        <v>0.9641</v>
-      </c>
-      <c r="G84" s="4" t="n">
-        <v>0.983</v>
-      </c>
-      <c r="H84" s="4" t="n">
-        <v>0.9782999999999999</v>
-      </c>
-      <c r="I84" s="4" t="n">
-        <v>0.9731</v>
-      </c>
-      <c r="J84" s="4" t="n">
-        <v>0.9734</v>
-      </c>
-      <c r="K84" s="4" t="n">
-        <v>0.9755</v>
-      </c>
-      <c r="L84" s="4" t="n">
-        <v>0.9727</v>
-      </c>
-      <c r="M84" s="4" t="n">
-        <v>0.9764</v>
-      </c>
-      <c r="N84" s="4" t="n">
-        <v>0.9789</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="E84" s="4" t="inlineStr"/>
+      <c r="F84" s="4" t="inlineStr"/>
+      <c r="G84" s="4" t="inlineStr"/>
+      <c r="H84" s="4" t="inlineStr"/>
+      <c r="I84" s="4" t="inlineStr"/>
+      <c r="J84" s="4" t="inlineStr"/>
+      <c r="K84" s="4" t="inlineStr"/>
+      <c r="L84" s="4" t="inlineStr"/>
+      <c r="M84" s="4" t="inlineStr"/>
+      <c r="N84" s="4" t="inlineStr"/>
       <c r="O84" s="4" t="n">
-        <v>0.9768</v>
+        <v>0.9837</v>
       </c>
       <c r="P84" s="4" t="n">
         <v>0.9823</v>
       </c>
       <c r="Q84" s="4" t="n">
-        <v>0.0055</v>
+        <v>-0.0014</v>
       </c>
       <c r="R84" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="85">
@@ -5144,12 +5174,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>DUNDWF1</t>
+          <t>STOCKYD1</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Dundonnell Wind Farm</t>
+          <t>Stockyard Hill Wind Farm</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -5158,29 +5188,25 @@
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>168</v>
+        <v>531</v>
       </c>
       <c r="E86" s="4" t="inlineStr"/>
       <c r="F86" s="4" t="inlineStr"/>
       <c r="G86" s="4" t="inlineStr"/>
       <c r="H86" s="4" t="inlineStr"/>
-      <c r="I86" s="4" t="n">
+      <c r="I86" s="4" t="inlineStr"/>
+      <c r="J86" s="4" t="inlineStr"/>
+      <c r="K86" s="4" t="n">
+        <v>0.9782</v>
+      </c>
+      <c r="L86" s="4" t="n">
+        <v>0.9799</v>
+      </c>
+      <c r="M86" s="4" t="n">
+        <v>0.9869</v>
+      </c>
+      <c r="N86" s="4" t="n">
         <v>0.9812</v>
-      </c>
-      <c r="J86" s="4" t="n">
-        <v>0.979</v>
-      </c>
-      <c r="K86" s="4" t="n">
-        <v>0.9789</v>
-      </c>
-      <c r="L86" s="4" t="n">
-        <v>0.9824000000000001</v>
-      </c>
-      <c r="M86" s="4" t="n">
-        <v>0.987</v>
-      </c>
-      <c r="N86" s="4" t="n">
-        <v>0.981</v>
       </c>
       <c r="O86" s="4" t="n">
         <v>0.9845</v>
@@ -5198,7 +5224,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>DUNDWF2</t>
+          <t>DUNDWF3</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -5212,7 +5238,7 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>46</v>
+        <v>121</v>
       </c>
       <c r="E87" s="4" t="inlineStr"/>
       <c r="F87" s="4" t="inlineStr"/>
@@ -5252,7 +5278,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>DUNDWF3</t>
+          <t>DUNDWF2</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -5266,7 +5292,7 @@
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>121</v>
+        <v>46</v>
       </c>
       <c r="E88" s="4" t="inlineStr"/>
       <c r="F88" s="4" t="inlineStr"/>
@@ -5306,12 +5332,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>STOCKYD1</t>
+          <t>DUNDWF1</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Stockyard Hill Wind Farm</t>
+          <t>Dundonnell Wind Farm</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -5320,25 +5346,29 @@
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>531</v>
+        <v>168</v>
       </c>
       <c r="E89" s="4" t="inlineStr"/>
       <c r="F89" s="4" t="inlineStr"/>
       <c r="G89" s="4" t="inlineStr"/>
       <c r="H89" s="4" t="inlineStr"/>
-      <c r="I89" s="4" t="inlineStr"/>
-      <c r="J89" s="4" t="inlineStr"/>
+      <c r="I89" s="4" t="n">
+        <v>0.9812</v>
+      </c>
+      <c r="J89" s="4" t="n">
+        <v>0.979</v>
+      </c>
       <c r="K89" s="4" t="n">
-        <v>0.9782</v>
+        <v>0.9789</v>
       </c>
       <c r="L89" s="4" t="n">
-        <v>0.9799</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="M89" s="4" t="n">
-        <v>0.9869</v>
+        <v>0.987</v>
       </c>
       <c r="N89" s="4" t="n">
-        <v>0.9812</v>
+        <v>0.981</v>
       </c>
       <c r="O89" s="4" t="n">
         <v>0.9845</v>
@@ -5400,12 +5430,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>LYA1</t>
+          <t>VPGS1</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Loy Yang A Power Station</t>
+          <t>Valley Power Peaking Facility</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -5414,7 +5444,7 @@
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>560</v>
+        <v>50</v>
       </c>
       <c r="E91" s="4" t="n">
         <v>0.9742</v>
@@ -5462,12 +5492,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>LYNL1</t>
+          <t>VPGS2</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>LOY YANG A POWER STATION</t>
+          <t>Valley Power Peaking Facility</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -5476,7 +5506,7 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E92" s="4" t="n">
         <v>0.9742</v>
@@ -5524,12 +5554,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>LYA4</t>
+          <t>VPGS6</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Loy Yang A Power Station</t>
+          <t>Valley Power Peaking Facility</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -5538,7 +5568,7 @@
         </is>
       </c>
       <c r="D93" s="3" t="n">
-        <v>560</v>
+        <v>50</v>
       </c>
       <c r="E93" s="4" t="n">
         <v>0.9742</v>
@@ -5586,12 +5616,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>LYA3</t>
+          <t>VPGS5</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Loy Yang A Power Station</t>
+          <t>Valley Power Peaking Facility</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -5600,7 +5630,7 @@
         </is>
       </c>
       <c r="D94" s="3" t="n">
-        <v>560</v>
+        <v>50</v>
       </c>
       <c r="E94" s="4" t="n">
         <v>0.9742</v>
@@ -5648,12 +5678,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>LYA2</t>
+          <t>VPGS3</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Loy Yang A Power Station</t>
+          <t>Valley Power Peaking Facility</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -5662,7 +5692,7 @@
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>530</v>
+        <v>50</v>
       </c>
       <c r="E95" s="4" t="n">
         <v>0.9742</v>
@@ -5710,12 +5740,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>LOYYB1</t>
+          <t>LYNL1</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Loy Yang B Power Station</t>
+          <t>LOY YANG A POWER STATION</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -5724,7 +5754,7 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>500</v>
+        <v>25</v>
       </c>
       <c r="E96" s="4" t="n">
         <v>0.9742</v>
@@ -5772,12 +5802,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>LOYYB2</t>
+          <t>VPGS4</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Loy Yang B Power Station</t>
+          <t>Valley Power Peaking Facility</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -5786,7 +5816,7 @@
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="E97" s="4" t="n">
         <v>0.9742</v>
@@ -5834,12 +5864,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>VPGS2</t>
+          <t>LYA4</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Valley Power Peaking Facility</t>
+          <t>Loy Yang A Power Station</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -5848,7 +5878,7 @@
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>50</v>
+        <v>560</v>
       </c>
       <c r="E98" s="4" t="n">
         <v>0.9742</v>
@@ -5896,12 +5926,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>VPGS4</t>
+          <t>LOYYB2</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Valley Power Peaking Facility</t>
+          <t>Loy Yang B Power Station</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -5910,7 +5940,7 @@
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="E99" s="4" t="n">
         <v>0.9742</v>
@@ -5958,12 +5988,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>VPGS6</t>
+          <t>LYA1</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Valley Power Peaking Facility</t>
+          <t>Loy Yang A Power Station</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -5972,7 +6002,7 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>50</v>
+        <v>560</v>
       </c>
       <c r="E100" s="4" t="n">
         <v>0.9742</v>
@@ -6020,12 +6050,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>VPGS5</t>
+          <t>LYA2</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Valley Power Peaking Facility</t>
+          <t>Loy Yang A Power Station</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -6034,7 +6064,7 @@
         </is>
       </c>
       <c r="D101" s="3" t="n">
-        <v>50</v>
+        <v>530</v>
       </c>
       <c r="E101" s="4" t="n">
         <v>0.9742</v>
@@ -6082,12 +6112,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>VPGS1</t>
+          <t>LYA3</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Valley Power Peaking Facility</t>
+          <t>Loy Yang A Power Station</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -6096,7 +6126,7 @@
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>50</v>
+        <v>560</v>
       </c>
       <c r="E102" s="4" t="n">
         <v>0.9742</v>
@@ -6144,12 +6174,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>VPGS3</t>
+          <t>LOYYB1</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Valley Power Peaking Facility</t>
+          <t>Loy Yang B Power Station</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -6158,7 +6188,7 @@
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="E103" s="4" t="n">
         <v>0.9742</v>
@@ -6268,7 +6298,7 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>EILDON1</t>
+          <t>EILDON2</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -6330,7 +6360,7 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>EILDON2</t>
+          <t>EILDON1</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -6418,12 +6448,18 @@
       <c r="L107" s="4" t="inlineStr"/>
       <c r="M107" s="4" t="inlineStr"/>
       <c r="N107" s="4" t="inlineStr"/>
-      <c r="O107" s="4" t="inlineStr"/>
+      <c r="O107" s="4" t="n">
+        <v>0.9951</v>
+      </c>
       <c r="P107" s="4" t="n">
         <v>0.9862</v>
       </c>
-      <c r="Q107" s="4" t="inlineStr"/>
-      <c r="R107" s="5" t="inlineStr"/>
+      <c r="Q107" s="4" t="n">
+        <v>-0.0089</v>
+      </c>
+      <c r="R107" s="5" t="n">
+        <v>-0.89</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -6577,13 +6613,21 @@
       <c r="K110" s="4" t="inlineStr"/>
       <c r="L110" s="4" t="inlineStr"/>
       <c r="M110" s="4" t="inlineStr"/>
-      <c r="N110" s="4" t="inlineStr"/>
-      <c r="O110" s="4" t="inlineStr"/>
+      <c r="N110" s="4" t="n">
+        <v>0.9864000000000001</v>
+      </c>
+      <c r="O110" s="4" t="n">
+        <v>0.9873</v>
+      </c>
       <c r="P110" s="4" t="n">
         <v>0.9873</v>
       </c>
-      <c r="Q110" s="4" t="inlineStr"/>
-      <c r="R110" s="5" t="inlineStr"/>
+      <c r="Q110" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R110" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -6795,13 +6839,21 @@
       <c r="K114" s="4" t="inlineStr"/>
       <c r="L114" s="4" t="inlineStr"/>
       <c r="M114" s="4" t="inlineStr"/>
-      <c r="N114" s="4" t="inlineStr"/>
-      <c r="O114" s="4" t="inlineStr"/>
+      <c r="N114" s="4" t="n">
+        <v>0.9858</v>
+      </c>
+      <c r="O114" s="4" t="n">
+        <v>0.9918</v>
+      </c>
       <c r="P114" s="4" t="n">
         <v>0.9897</v>
       </c>
-      <c r="Q114" s="4" t="inlineStr"/>
-      <c r="R114" s="5" t="inlineStr"/>
+      <c r="Q114" s="4" t="n">
+        <v>-0.0021</v>
+      </c>
+      <c r="R114" s="5" t="n">
+        <v>-0.21</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -6831,32 +6883,40 @@
       <c r="K115" s="4" t="inlineStr"/>
       <c r="L115" s="4" t="inlineStr"/>
       <c r="M115" s="4" t="inlineStr"/>
-      <c r="N115" s="4" t="inlineStr"/>
-      <c r="O115" s="4" t="inlineStr"/>
+      <c r="N115" s="4" t="n">
+        <v>0.9597</v>
+      </c>
+      <c r="O115" s="4" t="n">
+        <v>0.9857</v>
+      </c>
       <c r="P115" s="4" t="n">
         <v>0.9919</v>
       </c>
-      <c r="Q115" s="4" t="inlineStr"/>
-      <c r="R115" s="5" t="inlineStr"/>
+      <c r="Q115" s="4" t="n">
+        <v>0.0062</v>
+      </c>
+      <c r="R115" s="5" t="n">
+        <v>0.63</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>TGNSS1</t>
+          <t>GLENMAG1</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Traralgon Network Support Station</t>
+          <t>Glenmaggie Hydro Power Station</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Hydro</t>
         </is>
       </c>
       <c r="D116" s="3" t="n">
-        <v>10</v>
+        <v>3.8</v>
       </c>
       <c r="E116" s="4" t="n">
         <v>0.9799</v>
@@ -6904,38 +6964,64 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>PIBESS1</t>
+          <t>TOORAWF</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Phillip Island BESS</t>
+          <t>Toora Wind Farm</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D117" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="E117" s="4" t="inlineStr"/>
-      <c r="F117" s="4" t="inlineStr"/>
-      <c r="G117" s="4" t="inlineStr"/>
-      <c r="H117" s="4" t="inlineStr"/>
-      <c r="I117" s="4" t="inlineStr"/>
-      <c r="J117" s="4" t="inlineStr"/>
-      <c r="K117" s="4" t="inlineStr"/>
-      <c r="L117" s="4" t="inlineStr"/>
-      <c r="M117" s="4" t="inlineStr"/>
-      <c r="N117" s="4" t="inlineStr"/>
-      <c r="O117" s="4" t="inlineStr"/>
+        <v>21</v>
+      </c>
+      <c r="E117" s="4" t="n">
+        <v>0.9799</v>
+      </c>
+      <c r="F117" s="4" t="n">
+        <v>0.9759</v>
+      </c>
+      <c r="G117" s="4" t="n">
+        <v>0.9886</v>
+      </c>
+      <c r="H117" s="4" t="n">
+        <v>0.9879</v>
+      </c>
+      <c r="I117" s="4" t="n">
+        <v>0.9938</v>
+      </c>
+      <c r="J117" s="4" t="n">
+        <v>0.9955000000000001</v>
+      </c>
+      <c r="K117" s="4" t="n">
+        <v>0.9936</v>
+      </c>
+      <c r="L117" s="4" t="n">
+        <v>0.9977</v>
+      </c>
+      <c r="M117" s="4" t="n">
+        <v>0.9825</v>
+      </c>
+      <c r="N117" s="4" t="n">
+        <v>0.9848</v>
+      </c>
+      <c r="O117" s="4" t="n">
+        <v>0.9862</v>
+      </c>
       <c r="P117" s="4" t="n">
         <v>0.992</v>
       </c>
-      <c r="Q117" s="4" t="inlineStr"/>
-      <c r="R117" s="5" t="inlineStr"/>
+      <c r="Q117" s="4" t="n">
+        <v>0.0058</v>
+      </c>
+      <c r="R117" s="5" t="n">
+        <v>0.59</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -7002,49 +7088,31 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>GLENMAG1</t>
+          <t>PIBESS1</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Glenmaggie Hydro Power Station</t>
+          <t>Phillip Island BESS</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Hydro</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D119" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="E119" s="4" t="n">
-        <v>0.9799</v>
-      </c>
-      <c r="F119" s="4" t="n">
-        <v>0.9759</v>
-      </c>
-      <c r="G119" s="4" t="n">
-        <v>0.9886</v>
-      </c>
-      <c r="H119" s="4" t="n">
-        <v>0.9879</v>
-      </c>
-      <c r="I119" s="4" t="n">
-        <v>0.9938</v>
-      </c>
-      <c r="J119" s="4" t="n">
-        <v>0.9955000000000001</v>
-      </c>
-      <c r="K119" s="4" t="n">
-        <v>0.9936</v>
-      </c>
-      <c r="L119" s="4" t="n">
-        <v>0.9977</v>
-      </c>
-      <c r="M119" s="4" t="n">
-        <v>0.9825</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="E119" s="4" t="inlineStr"/>
+      <c r="F119" s="4" t="inlineStr"/>
+      <c r="G119" s="4" t="inlineStr"/>
+      <c r="H119" s="4" t="inlineStr"/>
+      <c r="I119" s="4" t="inlineStr"/>
+      <c r="J119" s="4" t="inlineStr"/>
+      <c r="K119" s="4" t="inlineStr"/>
+      <c r="L119" s="4" t="inlineStr"/>
+      <c r="M119" s="4" t="inlineStr"/>
       <c r="N119" s="4" t="n">
         <v>0.9848</v>
       </c>
@@ -7064,12 +7132,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>TOORAWF</t>
+          <t>WONWP</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Toora Wind Farm</t>
+          <t>Wonthaggi Wind Farm</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -7078,7 +7146,7 @@
         </is>
       </c>
       <c r="D120" s="3" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E120" s="4" t="n">
         <v>0.9799</v>
@@ -7188,21 +7256,21 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>WONWP</t>
+          <t>TGNSS1</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Wonthaggi Wind Farm</t>
+          <t>Traralgon Network Support Station</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D122" s="3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E122" s="4" t="n">
         <v>0.9799</v>
@@ -7275,183 +7343,177 @@
       <c r="K123" s="4" t="inlineStr"/>
       <c r="L123" s="4" t="inlineStr"/>
       <c r="M123" s="4" t="inlineStr"/>
-      <c r="N123" s="4" t="inlineStr"/>
-      <c r="O123" s="4" t="inlineStr"/>
+      <c r="N123" s="4" t="n">
+        <v>0.9889</v>
+      </c>
+      <c r="O123" s="4" t="n">
+        <v>0.9902</v>
+      </c>
       <c r="P123" s="4" t="n">
         <v>0.9933999999999999</v>
       </c>
-      <c r="Q123" s="4" t="inlineStr"/>
-      <c r="R123" s="5" t="inlineStr"/>
+      <c r="Q123" s="4" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="R123" s="5" t="n">
+        <v>0.32</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>WILLHOV1</t>
+          <t>MLB01</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>William Hovell Power Station</t>
+          <t>Mortlake Battery Energy Storage System</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Hydro</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D124" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E124" s="4" t="n">
-        <v>1.048</v>
-      </c>
-      <c r="F124" s="4" t="n">
-        <v>1.0235</v>
-      </c>
-      <c r="G124" s="4" t="n">
-        <v>0.9621</v>
-      </c>
-      <c r="H124" s="4" t="n">
-        <v>0.9712</v>
-      </c>
-      <c r="I124" s="4" t="n">
-        <v>1.0188</v>
-      </c>
-      <c r="J124" s="4" t="n">
-        <v>1.0274</v>
-      </c>
-      <c r="K124" s="4" t="n">
-        <v>1.0299</v>
-      </c>
-      <c r="L124" s="4" t="n">
-        <v>1.0182</v>
-      </c>
-      <c r="M124" s="4" t="n">
-        <v>1.0233</v>
-      </c>
-      <c r="N124" s="4" t="n">
-        <v>1.016</v>
-      </c>
+        <v>440</v>
+      </c>
+      <c r="E124" s="4" t="inlineStr"/>
+      <c r="F124" s="4" t="inlineStr"/>
+      <c r="G124" s="4" t="inlineStr"/>
+      <c r="H124" s="4" t="inlineStr"/>
+      <c r="I124" s="4" t="inlineStr"/>
+      <c r="J124" s="4" t="inlineStr"/>
+      <c r="K124" s="4" t="inlineStr"/>
+      <c r="L124" s="4" t="inlineStr"/>
+      <c r="M124" s="4" t="inlineStr"/>
+      <c r="N124" s="4" t="inlineStr"/>
       <c r="O124" s="4" t="n">
-        <v>1.0135</v>
+        <v>0.9945000000000001</v>
       </c>
       <c r="P124" s="4" t="n">
-        <v>0.9945000000000001</v>
+        <v>0.994</v>
       </c>
       <c r="Q124" s="4" t="n">
-        <v>-0.019</v>
+        <v>-0.0005</v>
       </c>
       <c r="R124" s="5" t="n">
-        <v>-1.87</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>MREHA3</t>
+          <t>WILLHOV1</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Melbourne Renewable Energy Hub Connection A3</t>
+          <t>William Hovell Power Station</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Hydro</t>
         </is>
       </c>
       <c r="D125" s="3" t="n">
-        <v>215.4</v>
-      </c>
-      <c r="E125" s="4" t="inlineStr"/>
-      <c r="F125" s="4" t="inlineStr"/>
-      <c r="G125" s="4" t="inlineStr"/>
-      <c r="H125" s="4" t="inlineStr"/>
-      <c r="I125" s="4" t="inlineStr"/>
-      <c r="J125" s="4" t="inlineStr"/>
-      <c r="K125" s="4" t="inlineStr"/>
-      <c r="L125" s="4" t="inlineStr"/>
-      <c r="M125" s="4" t="inlineStr"/>
-      <c r="N125" s="4" t="inlineStr"/>
-      <c r="O125" s="4" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="E125" s="4" t="n">
+        <v>1.048</v>
+      </c>
+      <c r="F125" s="4" t="n">
+        <v>1.0235</v>
+      </c>
+      <c r="G125" s="4" t="n">
+        <v>0.9621</v>
+      </c>
+      <c r="H125" s="4" t="n">
+        <v>0.9712</v>
+      </c>
+      <c r="I125" s="4" t="n">
+        <v>1.0188</v>
+      </c>
+      <c r="J125" s="4" t="n">
+        <v>1.0274</v>
+      </c>
+      <c r="K125" s="4" t="n">
+        <v>1.0299</v>
+      </c>
+      <c r="L125" s="4" t="n">
+        <v>1.0182</v>
+      </c>
+      <c r="M125" s="4" t="n">
+        <v>1.0233</v>
+      </c>
+      <c r="N125" s="4" t="n">
+        <v>1.016</v>
+      </c>
+      <c r="O125" s="4" t="n">
+        <v>1.0135</v>
+      </c>
       <c r="P125" s="4" t="n">
-        <v>0.9947</v>
-      </c>
-      <c r="Q125" s="4" t="inlineStr"/>
-      <c r="R125" s="5" t="inlineStr"/>
+        <v>0.9945000000000001</v>
+      </c>
+      <c r="Q125" s="4" t="n">
+        <v>-0.019</v>
+      </c>
+      <c r="R125" s="5" t="n">
+        <v>-1.87</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>CODRNGTON</t>
+          <t>MREHA3</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Codrington Wind Farm</t>
+          <t>Melbourne Renewable Energy Hub Connection A3</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D126" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="E126" s="4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="F126" s="4" t="n">
-        <v>1.0339</v>
-      </c>
-      <c r="G126" s="4" t="n">
-        <v>1.0322</v>
-      </c>
-      <c r="H126" s="4" t="n">
-        <v>1.0149</v>
-      </c>
-      <c r="I126" s="4" t="n">
-        <v>1.0019</v>
-      </c>
-      <c r="J126" s="4" t="n">
-        <v>1.0063</v>
-      </c>
-      <c r="K126" s="4" t="n">
-        <v>1.0035</v>
-      </c>
-      <c r="L126" s="4" t="n">
-        <v>0.9972</v>
-      </c>
-      <c r="M126" s="4" t="n">
-        <v>0.9933</v>
-      </c>
-      <c r="N126" s="4" t="n">
-        <v>0.9993</v>
-      </c>
+        <v>215.4</v>
+      </c>
+      <c r="E126" s="4" t="inlineStr"/>
+      <c r="F126" s="4" t="inlineStr"/>
+      <c r="G126" s="4" t="inlineStr"/>
+      <c r="H126" s="4" t="inlineStr"/>
+      <c r="I126" s="4" t="inlineStr"/>
+      <c r="J126" s="4" t="inlineStr"/>
+      <c r="K126" s="4" t="inlineStr"/>
+      <c r="L126" s="4" t="inlineStr"/>
+      <c r="M126" s="4" t="inlineStr"/>
+      <c r="N126" s="4" t="inlineStr"/>
       <c r="O126" s="4" t="n">
-        <v>1.0018</v>
+        <v>0.9957</v>
       </c>
       <c r="P126" s="4" t="n">
-        <v>0.9949</v>
+        <v>0.9947</v>
       </c>
       <c r="Q126" s="4" t="n">
-        <v>-0.0069</v>
+        <v>-0.001</v>
       </c>
       <c r="R126" s="5" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>TIMWEST</t>
+          <t>FSWF1</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Timboon West Wind Farm</t>
+          <t>Ferguson South Wind Farm</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -7460,19 +7522,15 @@
         </is>
       </c>
       <c r="D127" s="3" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="E127" s="4" t="inlineStr"/>
       <c r="F127" s="4" t="inlineStr"/>
       <c r="G127" s="4" t="inlineStr"/>
-      <c r="H127" s="4" t="n">
-        <v>1.0149</v>
-      </c>
-      <c r="I127" s="4" t="n">
-        <v>1.0019</v>
-      </c>
+      <c r="H127" s="4" t="inlineStr"/>
+      <c r="I127" s="4" t="inlineStr"/>
       <c r="J127" s="4" t="n">
-        <v>1.0063</v>
+        <v>1.0079</v>
       </c>
       <c r="K127" s="4" t="n">
         <v>1.0035</v>
@@ -7502,12 +7560,12 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>FSWF1</t>
+          <t>OAKLAND1</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Ferguson South Wind Farm</t>
+          <t>Oaklands Hill Wind Farm</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -7516,15 +7574,25 @@
         </is>
       </c>
       <c r="D128" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="E128" s="4" t="inlineStr"/>
-      <c r="F128" s="4" t="inlineStr"/>
-      <c r="G128" s="4" t="inlineStr"/>
-      <c r="H128" s="4" t="inlineStr"/>
-      <c r="I128" s="4" t="inlineStr"/>
+        <v>67</v>
+      </c>
+      <c r="E128" s="4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="F128" s="4" t="n">
+        <v>1.0339</v>
+      </c>
+      <c r="G128" s="4" t="n">
+        <v>1.0322</v>
+      </c>
+      <c r="H128" s="4" t="n">
+        <v>1.0149</v>
+      </c>
+      <c r="I128" s="4" t="n">
+        <v>1.0019</v>
+      </c>
       <c r="J128" s="4" t="n">
-        <v>1.0079</v>
+        <v>1.0063</v>
       </c>
       <c r="K128" s="4" t="n">
         <v>1.0035</v>
@@ -7554,12 +7622,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>YAMBUKWF</t>
+          <t>MLWF1</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Yambuk Wind Farm</t>
+          <t>Mortons Lane Wind Farm</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -7568,7 +7636,7 @@
         </is>
       </c>
       <c r="D129" s="3" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E129" s="4" t="n">
         <v>1.03</v>
@@ -7616,12 +7684,12 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>MLWF1</t>
+          <t>YAMBUKWF</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Mortons Lane Wind Farm</t>
+          <t>Yambuk Wind Farm</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -7630,7 +7698,7 @@
         </is>
       </c>
       <c r="D130" s="3" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E130" s="4" t="n">
         <v>1.03</v>
@@ -7678,12 +7746,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>OAKLAND1</t>
+          <t>CODRNGTON</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>Oaklands Hill Wind Farm</t>
+          <t>Codrington Wind Farm</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -7692,7 +7760,7 @@
         </is>
       </c>
       <c r="D131" s="3" t="n">
-        <v>67</v>
+        <v>18.2</v>
       </c>
       <c r="E131" s="4" t="n">
         <v>1.03</v>
@@ -7740,38 +7808,58 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>MREHA1</t>
+          <t>TIMWEST</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Melbourne Renewable Energy Hub Connection A1</t>
+          <t>Timboon West Wind Farm</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D132" s="3" t="n">
-        <v>215.8</v>
+        <v>7.2</v>
       </c>
       <c r="E132" s="4" t="inlineStr"/>
       <c r="F132" s="4" t="inlineStr"/>
       <c r="G132" s="4" t="inlineStr"/>
-      <c r="H132" s="4" t="inlineStr"/>
-      <c r="I132" s="4" t="inlineStr"/>
-      <c r="J132" s="4" t="inlineStr"/>
-      <c r="K132" s="4" t="inlineStr"/>
-      <c r="L132" s="4" t="inlineStr"/>
-      <c r="M132" s="4" t="inlineStr"/>
-      <c r="N132" s="4" t="inlineStr"/>
-      <c r="O132" s="4" t="inlineStr"/>
+      <c r="H132" s="4" t="n">
+        <v>1.0149</v>
+      </c>
+      <c r="I132" s="4" t="n">
+        <v>1.0019</v>
+      </c>
+      <c r="J132" s="4" t="n">
+        <v>1.0063</v>
+      </c>
+      <c r="K132" s="4" t="n">
+        <v>1.0035</v>
+      </c>
+      <c r="L132" s="4" t="n">
+        <v>0.9972</v>
+      </c>
+      <c r="M132" s="4" t="n">
+        <v>0.9933</v>
+      </c>
+      <c r="N132" s="4" t="n">
+        <v>0.9993</v>
+      </c>
+      <c r="O132" s="4" t="n">
+        <v>1.0018</v>
+      </c>
       <c r="P132" s="4" t="n">
-        <v>0.9951</v>
-      </c>
-      <c r="Q132" s="4" t="inlineStr"/>
-      <c r="R132" s="5" t="inlineStr"/>
+        <v>0.9949</v>
+      </c>
+      <c r="Q132" s="4" t="n">
+        <v>-0.0069</v>
+      </c>
+      <c r="R132" s="5" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -7801,74 +7889,64 @@
       <c r="K133" s="4" t="inlineStr"/>
       <c r="L133" s="4" t="inlineStr"/>
       <c r="M133" s="4" t="inlineStr"/>
-      <c r="N133" s="4" t="inlineStr"/>
-      <c r="O133" s="4" t="inlineStr"/>
+      <c r="N133" s="4" t="n">
+        <v>0.993</v>
+      </c>
+      <c r="O133" s="4" t="n">
+        <v>0.9955000000000001</v>
+      </c>
       <c r="P133" s="4" t="n">
         <v>0.9951</v>
       </c>
-      <c r="Q133" s="4" t="inlineStr"/>
-      <c r="R133" s="5" t="inlineStr"/>
+      <c r="Q133" s="4" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="R133" s="5" t="n">
+        <v>-0.04</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>MORTLK11</t>
+          <t>MREHA1</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Mortlake Power Station</t>
+          <t>Melbourne Renewable Energy Hub Connection A1</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D134" s="3" t="n">
-        <v>283</v>
-      </c>
-      <c r="E134" s="4" t="n">
-        <v>0.9942</v>
-      </c>
-      <c r="F134" s="4" t="n">
-        <v>1.0015</v>
-      </c>
-      <c r="G134" s="4" t="n">
-        <v>1.005</v>
-      </c>
-      <c r="H134" s="4" t="n">
-        <v>0.9961</v>
-      </c>
-      <c r="I134" s="4" t="n">
-        <v>0.9852</v>
-      </c>
-      <c r="J134" s="4" t="n">
-        <v>0.9845</v>
-      </c>
-      <c r="K134" s="4" t="n">
-        <v>0.9865</v>
-      </c>
-      <c r="L134" s="4" t="n">
-        <v>0.9901</v>
-      </c>
-      <c r="M134" s="4" t="n">
-        <v>0.9927</v>
-      </c>
+        <v>215.8</v>
+      </c>
+      <c r="E134" s="4" t="inlineStr"/>
+      <c r="F134" s="4" t="inlineStr"/>
+      <c r="G134" s="4" t="inlineStr"/>
+      <c r="H134" s="4" t="inlineStr"/>
+      <c r="I134" s="4" t="inlineStr"/>
+      <c r="J134" s="4" t="inlineStr"/>
+      <c r="K134" s="4" t="inlineStr"/>
+      <c r="L134" s="4" t="inlineStr"/>
+      <c r="M134" s="4" t="inlineStr"/>
       <c r="N134" s="4" t="n">
-        <v>0.9913999999999999</v>
+        <v>0.993</v>
       </c>
       <c r="O134" s="4" t="n">
-        <v>0.9969</v>
+        <v>0.9955000000000001</v>
       </c>
       <c r="P134" s="4" t="n">
-        <v>0.9955000000000001</v>
+        <v>0.9951</v>
       </c>
       <c r="Q134" s="4" t="n">
-        <v>-0.0014</v>
+        <v>-0.0004</v>
       </c>
       <c r="R134" s="5" t="n">
-        <v>-0.14</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="135">
@@ -7936,181 +8014,189 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>RANGEB1</t>
+          <t>MORTLK11</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Rangebank BESS</t>
+          <t>Mortlake Power Station</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D136" s="3" t="n">
-        <v>260</v>
-      </c>
-      <c r="E136" s="4" t="inlineStr"/>
-      <c r="F136" s="4" t="inlineStr"/>
-      <c r="G136" s="4" t="inlineStr"/>
-      <c r="H136" s="4" t="inlineStr"/>
-      <c r="I136" s="4" t="inlineStr"/>
-      <c r="J136" s="4" t="inlineStr"/>
-      <c r="K136" s="4" t="inlineStr"/>
-      <c r="L136" s="4" t="inlineStr"/>
-      <c r="M136" s="4" t="inlineStr"/>
-      <c r="N136" s="4" t="inlineStr"/>
-      <c r="O136" s="4" t="inlineStr"/>
+        <v>283</v>
+      </c>
+      <c r="E136" s="4" t="n">
+        <v>0.9942</v>
+      </c>
+      <c r="F136" s="4" t="n">
+        <v>1.0015</v>
+      </c>
+      <c r="G136" s="4" t="n">
+        <v>1.005</v>
+      </c>
+      <c r="H136" s="4" t="n">
+        <v>0.9961</v>
+      </c>
+      <c r="I136" s="4" t="n">
+        <v>0.9852</v>
+      </c>
+      <c r="J136" s="4" t="n">
+        <v>0.9845</v>
+      </c>
+      <c r="K136" s="4" t="n">
+        <v>0.9865</v>
+      </c>
+      <c r="L136" s="4" t="n">
+        <v>0.9901</v>
+      </c>
+      <c r="M136" s="4" t="n">
+        <v>0.9927</v>
+      </c>
+      <c r="N136" s="4" t="n">
+        <v>0.9913999999999999</v>
+      </c>
+      <c r="O136" s="4" t="n">
+        <v>0.9969</v>
+      </c>
       <c r="P136" s="4" t="n">
-        <v>0.9957</v>
-      </c>
-      <c r="Q136" s="4" t="inlineStr"/>
-      <c r="R136" s="5" t="inlineStr"/>
+        <v>0.9955000000000001</v>
+      </c>
+      <c r="Q136" s="4" t="n">
+        <v>-0.0014</v>
+      </c>
+      <c r="R136" s="5" t="n">
+        <v>-0.14</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>NPS</t>
+          <t>RANGEB1</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>Newport Power Station</t>
+          <t>Rangebank BESS</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D137" s="3" t="n">
-        <v>500</v>
-      </c>
-      <c r="E137" s="4" t="n">
-        <v>0.9952</v>
-      </c>
-      <c r="F137" s="4" t="n">
-        <v>0.9939</v>
-      </c>
-      <c r="G137" s="4" t="n">
-        <v>0.999</v>
-      </c>
-      <c r="H137" s="4" t="n">
-        <v>0.9962</v>
-      </c>
-      <c r="I137" s="4" t="n">
-        <v>0.9922</v>
-      </c>
-      <c r="J137" s="4" t="n">
-        <v>0.9913999999999999</v>
-      </c>
-      <c r="K137" s="4" t="n">
-        <v>0.9926</v>
-      </c>
-      <c r="L137" s="4" t="n">
-        <v>0.9919</v>
-      </c>
-      <c r="M137" s="4" t="n">
-        <v>0.9937</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="E137" s="4" t="inlineStr"/>
+      <c r="F137" s="4" t="inlineStr"/>
+      <c r="G137" s="4" t="inlineStr"/>
+      <c r="H137" s="4" t="inlineStr"/>
+      <c r="I137" s="4" t="inlineStr"/>
+      <c r="J137" s="4" t="inlineStr"/>
+      <c r="K137" s="4" t="inlineStr"/>
+      <c r="L137" s="4" t="inlineStr"/>
+      <c r="M137" s="4" t="inlineStr"/>
       <c r="N137" s="4" t="n">
-        <v>0.9941</v>
+        <v>0.9955000000000001</v>
       </c>
       <c r="O137" s="4" t="n">
-        <v>0.9943</v>
+        <v>0.9961</v>
       </c>
       <c r="P137" s="4" t="n">
         <v>0.9957</v>
       </c>
       <c r="Q137" s="4" t="n">
-        <v>0.0014</v>
+        <v>-0.0004</v>
       </c>
       <c r="R137" s="5" t="n">
-        <v>0.14</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>HALAMRD1</t>
+          <t>NPS</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Hallam Road Renewable Energy Facility</t>
+          <t>Newport Power Station</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Other Renewable</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D138" s="3" t="n">
-        <v>8.984</v>
+        <v>500</v>
       </c>
       <c r="E138" s="4" t="n">
-        <v>0.9931</v>
+        <v>0.9952</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>0.9932</v>
+        <v>0.9939</v>
       </c>
       <c r="G138" s="4" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="H138" s="4" t="n">
         <v>0.9962</v>
       </c>
-      <c r="H138" s="4" t="n">
-        <v>0.9956</v>
-      </c>
       <c r="I138" s="4" t="n">
-        <v>0.9944</v>
+        <v>0.9922</v>
       </c>
       <c r="J138" s="4" t="n">
-        <v>0.9948</v>
+        <v>0.9913999999999999</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>0.9944</v>
+        <v>0.9926</v>
       </c>
       <c r="L138" s="4" t="n">
-        <v>0.9962</v>
+        <v>0.9919</v>
       </c>
       <c r="M138" s="4" t="n">
+        <v>0.9937</v>
+      </c>
+      <c r="N138" s="4" t="n">
+        <v>0.9941</v>
+      </c>
+      <c r="O138" s="4" t="n">
+        <v>0.9943</v>
+      </c>
+      <c r="P138" s="4" t="n">
         <v>0.9957</v>
       </c>
-      <c r="N138" s="4" t="n">
-        <v>0.9954</v>
-      </c>
-      <c r="O138" s="4" t="n">
-        <v>0.9955000000000001</v>
-      </c>
-      <c r="P138" s="4" t="n">
-        <v>0.9959</v>
-      </c>
       <c r="Q138" s="4" t="n">
-        <v>0.0004</v>
+        <v>0.0014</v>
       </c>
       <c r="R138" s="5" t="n">
-        <v>0.04</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>HLMSEW01</t>
+          <t>HALAMRD1</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>South East Water - Halllam Hydro Plant</t>
+          <t>Hallam Road Renewable Energy Facility</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Hydro</t>
+          <t>Other Renewable</t>
         </is>
       </c>
       <c r="D139" s="3" t="n">
-        <v>0.25</v>
+        <v>8.984</v>
       </c>
       <c r="E139" s="4" t="n">
         <v>0.9931</v>
@@ -8131,138 +8217,158 @@
         <v>0.9948</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>0.9921</v>
+        <v>0.9944</v>
       </c>
       <c r="L139" s="4" t="n">
-        <v>0.9935</v>
+        <v>0.9962</v>
       </c>
       <c r="M139" s="4" t="n">
-        <v>0.9956</v>
+        <v>0.9957</v>
       </c>
       <c r="N139" s="4" t="n">
+        <v>0.9954</v>
+      </c>
+      <c r="O139" s="4" t="n">
         <v>0.9955000000000001</v>
       </c>
-      <c r="O139" s="4" t="n">
-        <v>0.996</v>
-      </c>
       <c r="P139" s="4" t="n">
-        <v>0.9961</v>
+        <v>0.9959</v>
       </c>
       <c r="Q139" s="4" t="n">
-        <v>0.0001</v>
+        <v>0.0004</v>
       </c>
       <c r="R139" s="5" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>AGLSOM</t>
+          <t>HLMSEW01</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Somerton Power Station</t>
+          <t>South East Water - Halllam Hydro Plant</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Hydro</t>
         </is>
       </c>
       <c r="D140" s="3" t="n">
-        <v>170</v>
+        <v>0.25</v>
       </c>
       <c r="E140" s="4" t="n">
-        <v>0.9946</v>
+        <v>0.9931</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>0.9949</v>
+        <v>0.9932</v>
       </c>
       <c r="G140" s="4" t="n">
-        <v>0.9968</v>
+        <v>0.9962</v>
       </c>
       <c r="H140" s="4" t="n">
-        <v>0.9963</v>
+        <v>0.9956</v>
       </c>
       <c r="I140" s="4" t="n">
-        <v>0.9915</v>
+        <v>0.9944</v>
       </c>
       <c r="J140" s="4" t="n">
-        <v>0.9923999999999999</v>
+        <v>0.9948</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>0.9932</v>
+        <v>0.9921</v>
       </c>
       <c r="L140" s="4" t="n">
-        <v>0.9923999999999999</v>
+        <v>0.9935</v>
       </c>
       <c r="M140" s="4" t="n">
+        <v>0.9956</v>
+      </c>
+      <c r="N140" s="4" t="n">
+        <v>0.9955000000000001</v>
+      </c>
+      <c r="O140" s="4" t="n">
         <v>0.996</v>
       </c>
-      <c r="N140" s="4" t="n">
-        <v>0.9962</v>
-      </c>
-      <c r="O140" s="4" t="n">
-        <v>0.9965000000000001</v>
-      </c>
       <c r="P140" s="4" t="n">
-        <v>0.9968</v>
+        <v>0.9961</v>
       </c>
       <c r="Q140" s="4" t="n">
-        <v>0.0003</v>
+        <v>0.0001</v>
       </c>
       <c r="R140" s="5" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>HASTING1</t>
+          <t>AGLSOM</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>Hastings Generation Site</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr"/>
+          <t>Somerton Power Station</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
       <c r="D141" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="E141" s="4" t="inlineStr"/>
-      <c r="F141" s="4" t="inlineStr"/>
-      <c r="G141" s="4" t="inlineStr"/>
-      <c r="H141" s="4" t="inlineStr"/>
-      <c r="I141" s="4" t="inlineStr"/>
-      <c r="J141" s="4" t="inlineStr"/>
-      <c r="K141" s="4" t="inlineStr"/>
-      <c r="L141" s="4" t="inlineStr"/>
+        <v>170</v>
+      </c>
+      <c r="E141" s="4" t="n">
+        <v>0.9946</v>
+      </c>
+      <c r="F141" s="4" t="n">
+        <v>0.9949</v>
+      </c>
+      <c r="G141" s="4" t="n">
+        <v>0.9968</v>
+      </c>
+      <c r="H141" s="4" t="n">
+        <v>0.9963</v>
+      </c>
+      <c r="I141" s="4" t="n">
+        <v>0.9915</v>
+      </c>
+      <c r="J141" s="4" t="n">
+        <v>0.9923999999999999</v>
+      </c>
+      <c r="K141" s="4" t="n">
+        <v>0.9932</v>
+      </c>
+      <c r="L141" s="4" t="n">
+        <v>0.9923999999999999</v>
+      </c>
       <c r="M141" s="4" t="n">
         <v>0.996</v>
       </c>
       <c r="N141" s="4" t="n">
-        <v>0.9959</v>
+        <v>0.9962</v>
       </c>
       <c r="O141" s="4" t="n">
-        <v>0.9964</v>
+        <v>0.9965000000000001</v>
       </c>
       <c r="P141" s="4" t="n">
-        <v>0.9969</v>
+        <v>0.9968</v>
       </c>
       <c r="Q141" s="4" t="n">
-        <v>0.0005</v>
+        <v>0.0003</v>
       </c>
       <c r="R141" s="5" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>HASTING2</t>
+          <t>HASTING3</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
@@ -8270,9 +8376,13 @@
           <t>Hastings Generation Site</t>
         </is>
       </c>
-      <c r="C142" s="2" t="inlineStr"/>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
       <c r="D142" s="3" t="n">
-        <v>14</v>
+        <v>14.817</v>
       </c>
       <c r="E142" s="4" t="inlineStr"/>
       <c r="F142" s="4" t="inlineStr"/>
@@ -8304,7 +8414,7 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>HASTING3</t>
+          <t>HASTING2</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
@@ -8312,13 +8422,9 @@
           <t>Hastings Generation Site</t>
         </is>
       </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>Fossil</t>
-        </is>
-      </c>
+      <c r="C143" s="2" t="inlineStr"/>
       <c r="D143" s="3" t="n">
-        <v>14.817</v>
+        <v>14</v>
       </c>
       <c r="E143" s="4" t="inlineStr"/>
       <c r="F143" s="4" t="inlineStr"/>
@@ -8350,21 +8456,17 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>MRNBESS1</t>
+          <t>HASTING1</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Mornington BESS</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>Battery</t>
-        </is>
-      </c>
+          <t>Hastings Generation Site</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr"/>
       <c r="D144" s="3" t="n">
-        <v>336</v>
+        <v>14</v>
       </c>
       <c r="E144" s="4" t="inlineStr"/>
       <c r="F144" s="4" t="inlineStr"/>
@@ -8374,123 +8476,113 @@
       <c r="J144" s="4" t="inlineStr"/>
       <c r="K144" s="4" t="inlineStr"/>
       <c r="L144" s="4" t="inlineStr"/>
-      <c r="M144" s="4" t="inlineStr"/>
-      <c r="N144" s="4" t="inlineStr"/>
-      <c r="O144" s="4" t="inlineStr"/>
+      <c r="M144" s="4" t="n">
+        <v>0.996</v>
+      </c>
+      <c r="N144" s="4" t="n">
+        <v>0.9959</v>
+      </c>
+      <c r="O144" s="4" t="n">
+        <v>0.9964</v>
+      </c>
       <c r="P144" s="4" t="n">
-        <v>0.9971</v>
-      </c>
-      <c r="Q144" s="4" t="inlineStr"/>
-      <c r="R144" s="5" t="inlineStr"/>
+        <v>0.9969</v>
+      </c>
+      <c r="Q144" s="4" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="R144" s="5" t="n">
+        <v>0.05</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>CHYTWF1</t>
+          <t>MRNBESS1</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>Cherry Tree Wind Farm</t>
+          <t>Mornington BESS</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D145" s="3" t="n">
-        <v>57.6</v>
+        <v>336</v>
       </c>
       <c r="E145" s="4" t="inlineStr"/>
       <c r="F145" s="4" t="inlineStr"/>
       <c r="G145" s="4" t="inlineStr"/>
       <c r="H145" s="4" t="inlineStr"/>
-      <c r="I145" s="4" t="n">
-        <v>0.9944</v>
-      </c>
-      <c r="J145" s="4" t="n">
-        <v>0.9958</v>
-      </c>
-      <c r="K145" s="4" t="n">
-        <v>0.9959</v>
-      </c>
-      <c r="L145" s="4" t="n">
-        <v>0.9955000000000001</v>
-      </c>
-      <c r="M145" s="4" t="n">
-        <v>0.9974</v>
-      </c>
-      <c r="N145" s="4" t="n">
-        <v>0.9976</v>
-      </c>
+      <c r="I145" s="4" t="inlineStr"/>
+      <c r="J145" s="4" t="inlineStr"/>
+      <c r="K145" s="4" t="inlineStr"/>
+      <c r="L145" s="4" t="inlineStr"/>
+      <c r="M145" s="4" t="inlineStr"/>
+      <c r="N145" s="4" t="inlineStr"/>
       <c r="O145" s="4" t="n">
-        <v>0.998</v>
+        <v>0.9984</v>
       </c>
       <c r="P145" s="4" t="n">
-        <v>0.9977</v>
+        <v>0.9971</v>
       </c>
       <c r="Q145" s="4" t="n">
-        <v>-0.0003</v>
+        <v>-0.0013</v>
       </c>
       <c r="R145" s="5" t="n">
-        <v>-0.03</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>WOLLERT1</t>
+          <t>CHYTWF1</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Wollert Renewable Energy Facility</t>
+          <t>Cherry Tree Wind Farm</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Other Renewable</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D146" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="E146" s="4" t="n">
-        <v>0.9987</v>
-      </c>
-      <c r="F146" s="4" t="n">
-        <v>0.9985000000000001</v>
-      </c>
-      <c r="G146" s="4" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="E146" s="4" t="inlineStr"/>
+      <c r="F146" s="4" t="inlineStr"/>
+      <c r="G146" s="4" t="inlineStr"/>
+      <c r="H146" s="4" t="inlineStr"/>
+      <c r="I146" s="4" t="n">
+        <v>0.9944</v>
+      </c>
+      <c r="J146" s="4" t="n">
+        <v>0.9958</v>
+      </c>
+      <c r="K146" s="4" t="n">
+        <v>0.9959</v>
+      </c>
+      <c r="L146" s="4" t="n">
+        <v>0.9955000000000001</v>
+      </c>
+      <c r="M146" s="4" t="n">
+        <v>0.9974</v>
+      </c>
+      <c r="N146" s="4" t="n">
+        <v>0.9976</v>
+      </c>
+      <c r="O146" s="4" t="n">
         <v>0.998</v>
       </c>
-      <c r="H146" s="4" t="n">
-        <v>0.9979</v>
-      </c>
-      <c r="I146" s="4" t="n">
-        <v>0.9941</v>
-      </c>
-      <c r="J146" s="4" t="n">
-        <v>0.9954</v>
-      </c>
-      <c r="K146" s="4" t="n">
-        <v>0.9956</v>
-      </c>
-      <c r="L146" s="4" t="n">
-        <v>0.9951</v>
-      </c>
-      <c r="M146" s="4" t="n">
-        <v>0.9975000000000001</v>
-      </c>
-      <c r="N146" s="4" t="n">
+      <c r="P146" s="4" t="n">
         <v>0.9977</v>
-      </c>
-      <c r="O146" s="4" t="n">
-        <v>0.9981</v>
-      </c>
-      <c r="P146" s="4" t="n">
-        <v>0.9978</v>
       </c>
       <c r="Q146" s="4" t="n">
         <v>-0.0003</v>
@@ -8502,30 +8594,30 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>RUBICON</t>
+          <t>WOLLERT1</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>Rubicon Mountain Streams Station</t>
+          <t>Wollert Renewable Energy Facility</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Hydro</t>
+          <t>Other Renewable</t>
         </is>
       </c>
       <c r="D147" s="3" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E147" s="4" t="n">
-        <v>1</v>
+        <v>0.9987</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>1</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="G147" s="4" t="n">
-        <v>1</v>
+        <v>0.998</v>
       </c>
       <c r="H147" s="4" t="n">
         <v>0.9979</v>
@@ -8564,12 +8656,12 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>EILDON3</t>
+          <t>RUBICON</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Eildon Power Station</t>
+          <t>Rubicon Mountain Streams Station</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -8578,16 +8670,16 @@
         </is>
       </c>
       <c r="D148" s="3" t="n">
-        <v>4.5</v>
+        <v>13</v>
       </c>
       <c r="E148" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F148" s="4" t="n">
-        <v>0.9985000000000001</v>
+        <v>1</v>
       </c>
       <c r="G148" s="4" t="n">
-        <v>0.998</v>
+        <v>1</v>
       </c>
       <c r="H148" s="4" t="n">
         <v>0.9979</v>
@@ -8626,131 +8718,131 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>CLAYTON</t>
+          <t>EILDON3</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>Clayton Landfill Gas Power Station</t>
+          <t>Eildon Power Station</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Other Renewable</t>
+          <t>Hydro</t>
         </is>
       </c>
       <c r="D149" s="3" t="n">
-        <v>11</v>
+        <v>4.5</v>
       </c>
       <c r="E149" s="4" t="n">
-        <v>0.997</v>
+        <v>1</v>
       </c>
       <c r="F149" s="4" t="n">
-        <v>0.9972</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="G149" s="4" t="n">
-        <v>0.9989</v>
+        <v>0.998</v>
       </c>
       <c r="H149" s="4" t="n">
-        <v>0.9986</v>
+        <v>0.9979</v>
       </c>
       <c r="I149" s="4" t="n">
-        <v>0.9987</v>
+        <v>0.9941</v>
       </c>
       <c r="J149" s="4" t="n">
-        <v>0.9984</v>
+        <v>0.9954</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>0.9957</v>
+        <v>0.9956</v>
       </c>
       <c r="L149" s="4" t="n">
-        <v>0.9972</v>
+        <v>0.9951</v>
       </c>
       <c r="M149" s="4" t="n">
-        <v>1.0001</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="N149" s="4" t="n">
+        <v>0.9977</v>
+      </c>
+      <c r="O149" s="4" t="n">
+        <v>0.9981</v>
+      </c>
+      <c r="P149" s="4" t="n">
         <v>0.9978</v>
       </c>
-      <c r="O149" s="4" t="n">
-        <v>0.9977</v>
-      </c>
-      <c r="P149" s="4" t="n">
-        <v>0.9982</v>
-      </c>
       <c r="Q149" s="4" t="n">
-        <v>0.0005</v>
+        <v>-0.0003</v>
       </c>
       <c r="R149" s="5" t="n">
-        <v>0.05</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>LNGS1</t>
+          <t>CLAYTON</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Laverton North Power Station</t>
+          <t>Clayton Landfill Gas Power Station</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Other Renewable</t>
         </is>
       </c>
       <c r="D150" s="3" t="n">
-        <v>156</v>
+        <v>11</v>
       </c>
       <c r="E150" s="4" t="n">
-        <v>0.9985000000000001</v>
+        <v>0.997</v>
       </c>
       <c r="F150" s="4" t="n">
-        <v>1.001</v>
+        <v>0.9972</v>
       </c>
       <c r="G150" s="4" t="n">
-        <v>1.0081</v>
+        <v>0.9989</v>
       </c>
       <c r="H150" s="4" t="n">
-        <v>1.0018</v>
+        <v>0.9986</v>
       </c>
       <c r="I150" s="4" t="n">
-        <v>0.9944</v>
+        <v>0.9987</v>
       </c>
       <c r="J150" s="4" t="n">
-        <v>0.991</v>
+        <v>0.9984</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>0.9936</v>
+        <v>0.9957</v>
       </c>
       <c r="L150" s="4" t="n">
-        <v>0.9949</v>
+        <v>0.9972</v>
       </c>
       <c r="M150" s="4" t="n">
-        <v>0.9979</v>
+        <v>1.0001</v>
       </c>
       <c r="N150" s="4" t="n">
-        <v>0.9975000000000001</v>
+        <v>0.9978</v>
       </c>
       <c r="O150" s="4" t="n">
+        <v>0.9977</v>
+      </c>
+      <c r="P150" s="4" t="n">
         <v>0.9982</v>
       </c>
-      <c r="P150" s="4" t="n">
-        <v>0.9999</v>
-      </c>
       <c r="Q150" s="4" t="n">
-        <v>0.0017</v>
+        <v>0.0005</v>
       </c>
       <c r="R150" s="5" t="n">
-        <v>0.17</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>LNGS2</t>
+          <t>LNGS1</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
@@ -8812,115 +8904,115 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>DG_VIC1</t>
+          <t>LNGS2</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>VIC1 Dummy Generator</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr"/>
+          <t>Laverton North Power Station</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
       <c r="D152" s="3" t="n">
-        <v>3000</v>
+        <v>156</v>
       </c>
       <c r="E152" s="4" t="n">
-        <v>1</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="F152" s="4" t="n">
-        <v>1</v>
+        <v>1.001</v>
       </c>
       <c r="G152" s="4" t="n">
-        <v>1</v>
+        <v>1.0081</v>
       </c>
       <c r="H152" s="4" t="n">
-        <v>1</v>
+        <v>1.0018</v>
       </c>
       <c r="I152" s="4" t="n">
-        <v>1</v>
+        <v>0.9944</v>
       </c>
       <c r="J152" s="4" t="n">
-        <v>1</v>
+        <v>0.991</v>
       </c>
       <c r="K152" s="4" t="n">
-        <v>1</v>
+        <v>0.9936</v>
       </c>
       <c r="L152" s="4" t="n">
-        <v>1</v>
+        <v>0.9949</v>
       </c>
       <c r="M152" s="4" t="n">
-        <v>1</v>
+        <v>0.9979</v>
       </c>
       <c r="N152" s="4" t="n">
-        <v>1</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="O152" s="4" t="n">
-        <v>1</v>
+        <v>0.9982</v>
       </c>
       <c r="P152" s="4" t="n">
-        <v>1</v>
+        <v>0.9999</v>
       </c>
       <c r="Q152" s="4" t="n">
-        <v>0</v>
+        <v>0.0017</v>
       </c>
       <c r="R152" s="5" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>PORTWF</t>
+          <t>DG_VIC1</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>Portland Wind Farm</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>Wind</t>
-        </is>
-      </c>
+          <t>VIC1 Dummy Generator</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr"/>
       <c r="D153" s="3" t="n">
-        <v>148</v>
+        <v>3000</v>
       </c>
       <c r="E153" s="4" t="n">
-        <v>1.0033</v>
+        <v>1</v>
       </c>
       <c r="F153" s="4" t="n">
-        <v>1.0135</v>
+        <v>1</v>
       </c>
       <c r="G153" s="4" t="n">
-        <v>1.0121</v>
+        <v>1</v>
       </c>
       <c r="H153" s="4" t="n">
-        <v>1.0058</v>
+        <v>1</v>
       </c>
       <c r="I153" s="4" t="n">
-        <v>0.9922</v>
+        <v>1</v>
       </c>
       <c r="J153" s="4" t="n">
-        <v>0.9913</v>
+        <v>1</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>0.9908</v>
+        <v>1</v>
       </c>
       <c r="L153" s="4" t="n">
-        <v>0.9945000000000001</v>
+        <v>1</v>
       </c>
       <c r="M153" s="4" t="n">
-        <v>0.9983</v>
+        <v>1</v>
       </c>
       <c r="N153" s="4" t="n">
-        <v>0.9936</v>
+        <v>1</v>
       </c>
       <c r="O153" s="4" t="n">
-        <v>1.0003</v>
+        <v>1</v>
       </c>
       <c r="P153" s="4" t="n">
-        <v>1.0003</v>
+        <v>1</v>
       </c>
       <c r="Q153" s="4" t="n">
         <v>0</v>
@@ -8932,181 +9024,187 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>CLOVER</t>
+          <t>PORTWF</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Clover Power Station</t>
+          <t>Portland Wind Farm</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Hydro</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D154" s="3" t="n">
-        <v>37.5</v>
+        <v>148</v>
       </c>
       <c r="E154" s="4" t="n">
-        <v>1.0285</v>
+        <v>1.0033</v>
       </c>
       <c r="F154" s="4" t="n">
-        <v>1.0285</v>
+        <v>1.0135</v>
       </c>
       <c r="G154" s="4" t="n">
-        <v>1.0285</v>
+        <v>1.0121</v>
       </c>
       <c r="H154" s="4" t="n">
-        <v>0.9882</v>
+        <v>1.0058</v>
       </c>
       <c r="I154" s="4" t="n">
-        <v>1.0192</v>
+        <v>0.9922</v>
       </c>
       <c r="J154" s="4" t="n">
-        <v>1.0235</v>
+        <v>0.9913</v>
       </c>
       <c r="K154" s="4" t="n">
-        <v>1.0292</v>
+        <v>0.9908</v>
       </c>
       <c r="L154" s="4" t="n">
-        <v>1.019</v>
+        <v>0.9945000000000001</v>
       </c>
       <c r="M154" s="4" t="n">
-        <v>1.0335</v>
+        <v>0.9983</v>
       </c>
       <c r="N154" s="4" t="n">
-        <v>1.0284</v>
+        <v>0.9936</v>
       </c>
       <c r="O154" s="4" t="n">
-        <v>1.0191</v>
+        <v>1.0003</v>
       </c>
       <c r="P154" s="4" t="n">
-        <v>1.0012</v>
+        <v>1.0003</v>
       </c>
       <c r="Q154" s="4" t="n">
-        <v>-0.0179</v>
+        <v>0</v>
       </c>
       <c r="R154" s="5" t="n">
-        <v>-1.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>BROOKLYN</t>
+          <t>CLOVER</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>Brooklyn LFG U1-3</t>
+          <t>Clover Power Station</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>Other Renewable</t>
+          <t>Hydro</t>
         </is>
       </c>
       <c r="D155" s="3" t="n">
-        <v>2.83</v>
+        <v>37.5</v>
       </c>
       <c r="E155" s="4" t="n">
-        <v>1.0053</v>
+        <v>1.0285</v>
       </c>
       <c r="F155" s="4" t="n">
-        <v>1.0054</v>
+        <v>1.0285</v>
       </c>
       <c r="G155" s="4" t="n">
-        <v>1.0069</v>
+        <v>1.0285</v>
       </c>
       <c r="H155" s="4" t="n">
-        <v>1.0042</v>
+        <v>0.9882</v>
       </c>
       <c r="I155" s="4" t="n">
-        <v>1.0027</v>
+        <v>1.0192</v>
       </c>
       <c r="J155" s="4" t="n">
-        <v>1.0037</v>
+        <v>1.0235</v>
       </c>
       <c r="K155" s="4" t="n">
-        <v>1.0062</v>
+        <v>1.0292</v>
       </c>
       <c r="L155" s="4" t="n">
-        <v>1.0066</v>
+        <v>1.019</v>
       </c>
       <c r="M155" s="4" t="n">
-        <v>1.0032</v>
+        <v>1.0335</v>
       </c>
       <c r="N155" s="4" t="n">
-        <v>1.0053</v>
+        <v>1.0284</v>
       </c>
       <c r="O155" s="4" t="n">
-        <v>1.0062</v>
+        <v>1.0191</v>
       </c>
       <c r="P155" s="4" t="n">
-        <v>1.0029</v>
+        <v>1.0012</v>
       </c>
       <c r="Q155" s="4" t="n">
-        <v>-0.0033</v>
+        <v>-0.0179</v>
       </c>
       <c r="R155" s="5" t="n">
-        <v>-0.33</v>
+        <v>-1.76</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>YAWWF1</t>
+          <t>BROOKLYN</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Yawong Wind Farm</t>
+          <t>Brooklyn LFG U1-3</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Other Renewable</t>
         </is>
       </c>
       <c r="D156" s="3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="E156" s="4" t="inlineStr"/>
-      <c r="F156" s="4" t="inlineStr"/>
-      <c r="G156" s="4" t="inlineStr"/>
+        <v>2.83</v>
+      </c>
+      <c r="E156" s="4" t="n">
+        <v>1.0053</v>
+      </c>
+      <c r="F156" s="4" t="n">
+        <v>1.0054</v>
+      </c>
+      <c r="G156" s="4" t="n">
+        <v>1.0069</v>
+      </c>
       <c r="H156" s="4" t="n">
-        <v>1.0136</v>
+        <v>1.0042</v>
       </c>
       <c r="I156" s="4" t="n">
-        <v>1.0012</v>
+        <v>1.0027</v>
       </c>
       <c r="J156" s="4" t="n">
-        <v>1.0022</v>
+        <v>1.0037</v>
       </c>
       <c r="K156" s="4" t="n">
-        <v>1.0101</v>
+        <v>1.0062</v>
       </c>
       <c r="L156" s="4" t="n">
-        <v>1.0084</v>
+        <v>1.0066</v>
       </c>
       <c r="M156" s="4" t="n">
-        <v>1.0165</v>
+        <v>1.0032</v>
       </c>
       <c r="N156" s="4" t="n">
-        <v>1.0072</v>
+        <v>1.0053</v>
       </c>
       <c r="O156" s="4" t="n">
-        <v>1.0166</v>
+        <v>1.0062</v>
       </c>
       <c r="P156" s="4" t="n">
-        <v>1.0031</v>
+        <v>1.0029</v>
       </c>
       <c r="Q156" s="4" t="n">
-        <v>-0.0135</v>
+        <v>-0.0033</v>
       </c>
       <c r="R156" s="5" t="n">
-        <v>-1.33</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="157">
@@ -9174,74 +9272,68 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>YWNGAHYD</t>
+          <t>YAWWF1</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Yarrawonga Hydro Power Station</t>
+          <t>Yawong Wind Farm</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Hydro</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D158" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="E158" s="4" t="n">
-        <v>1.0639</v>
-      </c>
-      <c r="F158" s="4" t="n">
-        <v>1.0502</v>
-      </c>
-      <c r="G158" s="4" t="n">
-        <v>1.0037</v>
-      </c>
+        <v>7.2</v>
+      </c>
+      <c r="E158" s="4" t="inlineStr"/>
+      <c r="F158" s="4" t="inlineStr"/>
+      <c r="G158" s="4" t="inlineStr"/>
       <c r="H158" s="4" t="n">
-        <v>1.0002</v>
+        <v>1.0136</v>
       </c>
       <c r="I158" s="4" t="n">
-        <v>1.0203</v>
+        <v>1.0012</v>
       </c>
       <c r="J158" s="4" t="n">
-        <v>1.0289</v>
+        <v>1.0022</v>
       </c>
       <c r="K158" s="4" t="n">
-        <v>1.0346</v>
+        <v>1.0101</v>
       </c>
       <c r="L158" s="4" t="n">
-        <v>1.0313</v>
+        <v>1.0084</v>
       </c>
       <c r="M158" s="4" t="n">
-        <v>1.041</v>
+        <v>1.0165</v>
       </c>
       <c r="N158" s="4" t="n">
-        <v>1.0372</v>
+        <v>1.0072</v>
       </c>
       <c r="O158" s="4" t="n">
-        <v>1.0315</v>
+        <v>1.0166</v>
       </c>
       <c r="P158" s="4" t="n">
-        <v>1.0142</v>
+        <v>1.0031</v>
       </c>
       <c r="Q158" s="4" t="n">
-        <v>-0.0173</v>
+        <v>-0.0135</v>
       </c>
       <c r="R158" s="5" t="n">
-        <v>-1.68</v>
+        <v>-1.33</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>TATURA01</t>
+          <t>SHEP1</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>Tatura Biomass Generator</t>
+          <t>Shepparton Wastewater Treatment Facility</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -9298,21 +9390,21 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>SHEP1</t>
+          <t>YWNGAHYD</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Shepparton Wastewater Treatment Facility</t>
+          <t>Yarrawonga Hydro Power Station</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Other Renewable</t>
+          <t>Hydro</t>
         </is>
       </c>
       <c r="D160" s="3" t="n">
-        <v>1.1</v>
+        <v>9</v>
       </c>
       <c r="E160" s="4" t="n">
         <v>1.0639</v>
@@ -9360,104 +9452,130 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>SNOWYGJP</t>
+          <t>TATURA01</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>Jindabyne Pump At Guthega</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="n"/>
-      <c r="D161" s="2" t="inlineStr"/>
+          <t>Tatura Biomass Generator</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>Other Renewable</t>
+        </is>
+      </c>
+      <c r="D161" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="E161" s="4" t="n">
-        <v>1.138</v>
+        <v>1.0639</v>
       </c>
       <c r="F161" s="4" t="n">
-        <v>1.1115</v>
+        <v>1.0502</v>
       </c>
       <c r="G161" s="4" t="n">
-        <v>1.0474</v>
+        <v>1.0037</v>
       </c>
       <c r="H161" s="4" t="n">
-        <v>1.0124</v>
+        <v>1.0002</v>
       </c>
       <c r="I161" s="4" t="n">
-        <v>1.0211</v>
+        <v>1.0203</v>
       </c>
       <c r="J161" s="4" t="n">
-        <v>1.1231</v>
+        <v>1.0289</v>
       </c>
       <c r="K161" s="4" t="n">
-        <v>1.135</v>
+        <v>1.0346</v>
       </c>
       <c r="L161" s="4" t="n">
-        <v>1.0914</v>
+        <v>1.0313</v>
       </c>
       <c r="M161" s="4" t="n">
-        <v>1.0783</v>
+        <v>1.041</v>
       </c>
       <c r="N161" s="4" t="n">
-        <v>1.093</v>
+        <v>1.0372</v>
       </c>
       <c r="O161" s="4" t="n">
-        <v>1.0606</v>
+        <v>1.0315</v>
       </c>
       <c r="P161" s="4" t="n">
-        <v>1.0587</v>
+        <v>1.0142</v>
       </c>
       <c r="Q161" s="4" t="n">
-        <v>-0.0019</v>
+        <v>-0.0173</v>
       </c>
       <c r="R161" s="5" t="n">
-        <v>-0.18</v>
+        <v>-1.68</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>MORNL1</t>
+          <t>SNOWYGJP</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Energy Brix Complex Power Station</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>Fossil</t>
-        </is>
-      </c>
-      <c r="D162" s="3" t="n">
-        <v>25</v>
-      </c>
+          <t>Jindabyne Pump At Guthega</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="n"/>
+      <c r="D162" s="2" t="inlineStr"/>
       <c r="E162" s="4" t="n">
-        <v>0.9799</v>
-      </c>
-      <c r="F162" s="4" t="inlineStr"/>
-      <c r="G162" s="4" t="inlineStr"/>
-      <c r="H162" s="4" t="inlineStr"/>
-      <c r="I162" s="4" t="inlineStr"/>
-      <c r="J162" s="4" t="inlineStr"/>
-      <c r="K162" s="4" t="inlineStr"/>
-      <c r="L162" s="4" t="inlineStr"/>
-      <c r="M162" s="4" t="inlineStr"/>
-      <c r="N162" s="4" t="inlineStr"/>
-      <c r="O162" s="4" t="inlineStr"/>
-      <c r="P162" s="4" t="inlineStr"/>
-      <c r="Q162" s="4" t="inlineStr"/>
-      <c r="R162" s="5" t="inlineStr"/>
+        <v>1.138</v>
+      </c>
+      <c r="F162" s="4" t="n">
+        <v>1.1115</v>
+      </c>
+      <c r="G162" s="4" t="n">
+        <v>1.0474</v>
+      </c>
+      <c r="H162" s="4" t="n">
+        <v>1.0124</v>
+      </c>
+      <c r="I162" s="4" t="n">
+        <v>1.0211</v>
+      </c>
+      <c r="J162" s="4" t="n">
+        <v>1.1231</v>
+      </c>
+      <c r="K162" s="4" t="n">
+        <v>1.135</v>
+      </c>
+      <c r="L162" s="4" t="n">
+        <v>1.0914</v>
+      </c>
+      <c r="M162" s="4" t="n">
+        <v>1.0783</v>
+      </c>
+      <c r="N162" s="4" t="n">
+        <v>1.093</v>
+      </c>
+      <c r="O162" s="4" t="n">
+        <v>1.0606</v>
+      </c>
+      <c r="P162" s="4" t="n">
+        <v>1.0587</v>
+      </c>
+      <c r="Q162" s="4" t="n">
+        <v>-0.0019</v>
+      </c>
+      <c r="R162" s="5" t="n">
+        <v>-0.18</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>APS</t>
+          <t>MORNL1</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>ANGELSEA POWER STATION</t>
+          <t>Energy Brix Complex Power Station</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -9466,10 +9584,10 @@
         </is>
       </c>
       <c r="D163" s="3" t="n">
-        <v>165</v>
+        <v>25</v>
       </c>
       <c r="E163" s="4" t="n">
-        <v>0.9915</v>
+        <v>0.9799</v>
       </c>
       <c r="F163" s="4" t="inlineStr"/>
       <c r="G163" s="4" t="inlineStr"/>
@@ -9488,20 +9606,24 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>MOR2</t>
+          <t>APS</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>Energy Brix Complex Power Station</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D164" s="2" t="inlineStr"/>
+          <t>ANGELSEA POWER STATION</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D164" s="3" t="n">
+        <v>165</v>
+      </c>
       <c r="E164" s="4" t="n">
-        <v>0.9732</v>
+        <v>0.9915</v>
       </c>
       <c r="F164" s="4" t="inlineStr"/>
       <c r="G164" s="4" t="inlineStr"/>
@@ -9584,28 +9706,22 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>HWPS6</t>
+          <t>MOR2</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>Hazelwood Power Station</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>Fossil</t>
-        </is>
-      </c>
-      <c r="D167" s="3" t="n">
-        <v>200</v>
-      </c>
+          <t>Energy Brix Complex Power Station</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D167" s="2" t="inlineStr"/>
       <c r="E167" s="4" t="n">
-        <v>0.9723000000000001</v>
-      </c>
-      <c r="F167" s="4" t="n">
-        <v>0.9701</v>
-      </c>
+        <v>0.9732</v>
+      </c>
+      <c r="F167" s="4" t="inlineStr"/>
       <c r="G167" s="4" t="inlineStr"/>
       <c r="H167" s="4" t="inlineStr"/>
       <c r="I167" s="4" t="inlineStr"/>
@@ -9622,7 +9738,7 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>HWPS2</t>
+          <t>HWPS8</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
@@ -9636,7 +9752,7 @@
         </is>
       </c>
       <c r="D168" s="3" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="E168" s="4" t="n">
         <v>0.9723000000000001</v>
@@ -9660,7 +9776,7 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>HWPS1</t>
+          <t>HWPS7</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
@@ -9674,7 +9790,7 @@
         </is>
       </c>
       <c r="D169" s="3" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="E169" s="4" t="n">
         <v>0.9723000000000001</v>
@@ -9698,7 +9814,7 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>HWPNL1</t>
+          <t>HWPS6</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
@@ -9712,7 +9828,7 @@
         </is>
       </c>
       <c r="D170" s="3" t="n">
-        <v>25</v>
+        <v>200</v>
       </c>
       <c r="E170" s="4" t="n">
         <v>0.9723000000000001</v>
@@ -9736,7 +9852,7 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>HWPS7</t>
+          <t>HWPS5</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
@@ -9774,7 +9890,7 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>HWPS5</t>
+          <t>HWPS4</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
@@ -9812,7 +9928,7 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>HWPS4</t>
+          <t>HWPS3</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
@@ -9850,7 +9966,7 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>HWPS8</t>
+          <t>HWPS2</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
@@ -9864,7 +9980,7 @@
         </is>
       </c>
       <c r="D174" s="3" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="E174" s="4" t="n">
         <v>0.9723000000000001</v>
@@ -9888,7 +10004,7 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>HWPS3</t>
+          <t>HWPS1</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
@@ -9902,7 +10018,7 @@
         </is>
       </c>
       <c r="D175" s="3" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="E175" s="4" t="n">
         <v>0.9723000000000001</v>
@@ -9926,31 +10042,29 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>MORNW</t>
+          <t>HWPNL1</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>Mornington Waste Disposal Facility</t>
+          <t>Hazelwood Power Station</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>Other Renewable</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D176" s="3" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="E176" s="4" t="n">
-        <v>0.9923999999999999</v>
+        <v>0.9723000000000001</v>
       </c>
       <c r="F176" s="4" t="n">
-        <v>0.9925</v>
-      </c>
-      <c r="G176" s="4" t="n">
-        <v>0.9963</v>
-      </c>
+        <v>0.9701</v>
+      </c>
+      <c r="G176" s="4" t="inlineStr"/>
       <c r="H176" s="4" t="inlineStr"/>
       <c r="I176" s="4" t="inlineStr"/>
       <c r="J176" s="4" t="inlineStr"/>
@@ -10006,12 +10120,12 @@
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>CORIO1</t>
+          <t>MORNW</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Corio Landfill Gas Power Station</t>
+          <t>Mornington Waste Disposal Facility</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
@@ -10023,29 +10137,19 @@
         <v>1</v>
       </c>
       <c r="E178" s="4" t="n">
-        <v>0.9987</v>
+        <v>0.9923999999999999</v>
       </c>
       <c r="F178" s="4" t="n">
-        <v>1.0048</v>
+        <v>0.9925</v>
       </c>
       <c r="G178" s="4" t="n">
-        <v>1.0055</v>
-      </c>
-      <c r="H178" s="4" t="n">
-        <v>1.0002</v>
-      </c>
-      <c r="I178" s="4" t="n">
-        <v>0.9908</v>
-      </c>
-      <c r="J178" s="4" t="n">
-        <v>0.9913999999999999</v>
-      </c>
-      <c r="K178" s="4" t="n">
-        <v>0.9918</v>
-      </c>
-      <c r="L178" s="4" t="n">
-        <v>0.9933</v>
-      </c>
+        <v>0.9963</v>
+      </c>
+      <c r="H178" s="4" t="inlineStr"/>
+      <c r="I178" s="4" t="inlineStr"/>
+      <c r="J178" s="4" t="inlineStr"/>
+      <c r="K178" s="4" t="inlineStr"/>
+      <c r="L178" s="4" t="inlineStr"/>
       <c r="M178" s="4" t="inlineStr"/>
       <c r="N178" s="4" t="inlineStr"/>
       <c r="O178" s="4" t="inlineStr"/>
@@ -10056,41 +10160,45 @@
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>BERWICK</t>
+          <t>CORIO1</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>Berwick Power Plant</t>
-        </is>
-      </c>
-      <c r="C179" s="2" t="inlineStr"/>
+          <t>Corio Landfill Gas Power Station</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>Other Renewable</t>
+        </is>
+      </c>
       <c r="D179" s="3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E179" s="4" t="n">
-        <v>0.9923</v>
+        <v>0.9987</v>
       </c>
       <c r="F179" s="4" t="n">
-        <v>0.9923</v>
+        <v>1.0048</v>
       </c>
       <c r="G179" s="4" t="n">
-        <v>0.9923</v>
+        <v>1.0055</v>
       </c>
       <c r="H179" s="4" t="n">
-        <v>0.9923</v>
+        <v>1.0002</v>
       </c>
       <c r="I179" s="4" t="n">
-        <v>0.9923</v>
+        <v>0.9908</v>
       </c>
       <c r="J179" s="4" t="n">
-        <v>0.9923</v>
+        <v>0.9913999999999999</v>
       </c>
       <c r="K179" s="4" t="n">
-        <v>0.9923</v>
+        <v>0.9918</v>
       </c>
       <c r="L179" s="4" t="n">
-        <v>0.9923</v>
+        <v>0.9933</v>
       </c>
       <c r="M179" s="4" t="inlineStr"/>
       <c r="N179" s="4" t="inlineStr"/>
@@ -10102,49 +10210,43 @@
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>SVALE1</t>
+          <t>BERWICK</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Springvale Landfill Gas Power Station</t>
-        </is>
-      </c>
-      <c r="C180" s="2" t="inlineStr">
-        <is>
-          <t>Other Renewable</t>
-        </is>
-      </c>
+          <t>Berwick Power Plant</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr"/>
       <c r="D180" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E180" s="4" t="n">
-        <v>0.997</v>
+        <v>0.9923</v>
       </c>
       <c r="F180" s="4" t="n">
-        <v>0.9972</v>
+        <v>0.9923</v>
       </c>
       <c r="G180" s="4" t="n">
-        <v>0.9989</v>
+        <v>0.9923</v>
       </c>
       <c r="H180" s="4" t="n">
-        <v>0.9986</v>
+        <v>0.9923</v>
       </c>
       <c r="I180" s="4" t="n">
-        <v>0.9987</v>
+        <v>0.9923</v>
       </c>
       <c r="J180" s="4" t="n">
-        <v>0.9984</v>
+        <v>0.9923</v>
       </c>
       <c r="K180" s="4" t="n">
-        <v>0.9957</v>
+        <v>0.9923</v>
       </c>
       <c r="L180" s="4" t="n">
-        <v>0.9972</v>
-      </c>
-      <c r="M180" s="4" t="n">
-        <v>1.0001</v>
-      </c>
+        <v>0.9923</v>
+      </c>
+      <c r="M180" s="4" t="inlineStr"/>
       <c r="N180" s="4" t="inlineStr"/>
       <c r="O180" s="4" t="inlineStr"/>
       <c r="P180" s="4" t="inlineStr"/>
@@ -10206,46 +10308,50 @@
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>GANNBG1</t>
+          <t>SVALE1</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>Gannawarra Energy Storage System</t>
+          <t>Springvale Landfill Gas Power Station</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Other Renewable</t>
         </is>
       </c>
       <c r="D182" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="E182" s="4" t="inlineStr"/>
-      <c r="F182" s="4" t="inlineStr"/>
-      <c r="G182" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="E182" s="4" t="n">
+        <v>0.997</v>
+      </c>
+      <c r="F182" s="4" t="n">
+        <v>0.9972</v>
+      </c>
+      <c r="G182" s="4" t="n">
+        <v>0.9989</v>
+      </c>
       <c r="H182" s="4" t="n">
-        <v>1.007</v>
+        <v>0.9986</v>
       </c>
       <c r="I182" s="4" t="n">
-        <v>0.9643</v>
+        <v>0.9987</v>
       </c>
       <c r="J182" s="4" t="n">
-        <v>0.9792999999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="K182" s="4" t="n">
-        <v>0.9772999999999999</v>
+        <v>0.9957</v>
       </c>
       <c r="L182" s="4" t="n">
-        <v>1.0026</v>
+        <v>0.9972</v>
       </c>
       <c r="M182" s="4" t="n">
-        <v>1.029</v>
-      </c>
-      <c r="N182" s="4" t="n">
-        <v>1.0155</v>
-      </c>
+        <v>1.0001</v>
+      </c>
+      <c r="N182" s="4" t="inlineStr"/>
       <c r="O182" s="4" t="inlineStr"/>
       <c r="P182" s="4" t="inlineStr"/>
       <c r="Q182" s="4" t="inlineStr"/>
@@ -10254,41 +10360,39 @@
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>FNWF1</t>
+          <t>VBBG1</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>Ferguson North Wind Farm</t>
+          <t>Victorian Big Battery</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D183" s="3" t="n">
-        <v>4</v>
+        <v>360</v>
       </c>
       <c r="E183" s="4" t="inlineStr"/>
       <c r="F183" s="4" t="inlineStr"/>
       <c r="G183" s="4" t="inlineStr"/>
       <c r="H183" s="4" t="inlineStr"/>
       <c r="I183" s="4" t="inlineStr"/>
-      <c r="J183" s="4" t="n">
-        <v>1.0079</v>
-      </c>
+      <c r="J183" s="4" t="inlineStr"/>
       <c r="K183" s="4" t="n">
-        <v>1.0035</v>
+        <v>0.982</v>
       </c>
       <c r="L183" s="4" t="n">
-        <v>0.9972</v>
+        <v>0.9848</v>
       </c>
       <c r="M183" s="4" t="n">
-        <v>0.9933</v>
+        <v>0.9885</v>
       </c>
       <c r="N183" s="4" t="n">
-        <v>0.9993</v>
+        <v>0.9879</v>
       </c>
       <c r="O183" s="4" t="inlineStr"/>
       <c r="P183" s="4" t="inlineStr"/>
@@ -10298,12 +10402,12 @@
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>VBBG1</t>
+          <t>GANNBG1</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>Victorian Big Battery</t>
+          <t>Gannawarra Energy Storage System</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
@@ -10312,25 +10416,31 @@
         </is>
       </c>
       <c r="D184" s="3" t="n">
-        <v>360</v>
+        <v>30</v>
       </c>
       <c r="E184" s="4" t="inlineStr"/>
       <c r="F184" s="4" t="inlineStr"/>
       <c r="G184" s="4" t="inlineStr"/>
-      <c r="H184" s="4" t="inlineStr"/>
-      <c r="I184" s="4" t="inlineStr"/>
-      <c r="J184" s="4" t="inlineStr"/>
+      <c r="H184" s="4" t="n">
+        <v>1.007</v>
+      </c>
+      <c r="I184" s="4" t="n">
+        <v>0.9643</v>
+      </c>
+      <c r="J184" s="4" t="n">
+        <v>0.9792999999999999</v>
+      </c>
       <c r="K184" s="4" t="n">
-        <v>0.982</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="L184" s="4" t="n">
-        <v>0.9848</v>
+        <v>1.0026</v>
       </c>
       <c r="M184" s="4" t="n">
-        <v>0.9885</v>
+        <v>1.029</v>
       </c>
       <c r="N184" s="4" t="n">
-        <v>0.9879</v>
+        <v>1.0155</v>
       </c>
       <c r="O184" s="4" t="inlineStr"/>
       <c r="P184" s="4" t="inlineStr"/>
@@ -10340,12 +10450,12 @@
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>HBESSG1</t>
+          <t>BULBESG1</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>Hazelwood Battery Energy Storage System</t>
+          <t>Bulgana Green Power Hub</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
@@ -10354,7 +10464,7 @@
         </is>
       </c>
       <c r="D185" s="3" t="n">
-        <v>200</v>
+        <v>24</v>
       </c>
       <c r="E185" s="4" t="inlineStr"/>
       <c r="F185" s="4" t="inlineStr"/>
@@ -10362,15 +10472,17 @@
       <c r="H185" s="4" t="inlineStr"/>
       <c r="I185" s="4" t="inlineStr"/>
       <c r="J185" s="4" t="inlineStr"/>
-      <c r="K185" s="4" t="inlineStr"/>
+      <c r="K185" s="4" t="n">
+        <v>0.8949</v>
+      </c>
       <c r="L185" s="4" t="n">
-        <v>0.9785</v>
+        <v>0.8839</v>
       </c>
       <c r="M185" s="4" t="n">
-        <v>0.9789</v>
+        <v>0.8821</v>
       </c>
       <c r="N185" s="4" t="n">
-        <v>0.9804</v>
+        <v>0.8733</v>
       </c>
       <c r="O185" s="4" t="inlineStr"/>
       <c r="P185" s="4" t="inlineStr"/>
@@ -10380,12 +10492,12 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>BALBG1</t>
+          <t>HBESSG1</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>Ballarat Battery Energy Storage System</t>
+          <t>Hazelwood Battery Energy Storage System</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
@@ -10394,31 +10506,23 @@
         </is>
       </c>
       <c r="D186" s="3" t="n">
-        <v>30</v>
+        <v>200</v>
       </c>
       <c r="E186" s="4" t="inlineStr"/>
       <c r="F186" s="4" t="inlineStr"/>
       <c r="G186" s="4" t="inlineStr"/>
-      <c r="H186" s="4" t="n">
-        <v>0.9948</v>
-      </c>
-      <c r="I186" s="4" t="n">
-        <v>0.9634</v>
-      </c>
-      <c r="J186" s="4" t="n">
-        <v>0.9643</v>
-      </c>
-      <c r="K186" s="4" t="n">
-        <v>0.9573</v>
-      </c>
+      <c r="H186" s="4" t="inlineStr"/>
+      <c r="I186" s="4" t="inlineStr"/>
+      <c r="J186" s="4" t="inlineStr"/>
+      <c r="K186" s="4" t="inlineStr"/>
       <c r="L186" s="4" t="n">
-        <v>0.9663</v>
+        <v>0.9785</v>
       </c>
       <c r="M186" s="4" t="n">
-        <v>0.9756</v>
+        <v>0.9789</v>
       </c>
       <c r="N186" s="4" t="n">
-        <v>0.9713000000000001</v>
+        <v>0.9804</v>
       </c>
       <c r="O186" s="4" t="inlineStr"/>
       <c r="P186" s="4" t="inlineStr"/>
@@ -10428,12 +10532,12 @@
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>PIBESSG1</t>
+          <t>BALBG1</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>Phillip Island BESS</t>
+          <t>Ballarat Battery Energy Storage System</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
@@ -10442,23 +10546,31 @@
         </is>
       </c>
       <c r="D187" s="3" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="E187" s="4" t="inlineStr"/>
       <c r="F187" s="4" t="inlineStr"/>
       <c r="G187" s="4" t="inlineStr"/>
-      <c r="H187" s="4" t="inlineStr"/>
-      <c r="I187" s="4" t="inlineStr"/>
-      <c r="J187" s="4" t="inlineStr"/>
-      <c r="K187" s="4" t="inlineStr"/>
+      <c r="H187" s="4" t="n">
+        <v>0.9948</v>
+      </c>
+      <c r="I187" s="4" t="n">
+        <v>0.9634</v>
+      </c>
+      <c r="J187" s="4" t="n">
+        <v>0.9643</v>
+      </c>
+      <c r="K187" s="4" t="n">
+        <v>0.9573</v>
+      </c>
       <c r="L187" s="4" t="n">
-        <v>0.9977</v>
+        <v>0.9663</v>
       </c>
       <c r="M187" s="4" t="n">
-        <v>0.9825</v>
+        <v>0.9756</v>
       </c>
       <c r="N187" s="4" t="n">
-        <v>0.9848</v>
+        <v>0.9713000000000001</v>
       </c>
       <c r="O187" s="4" t="inlineStr"/>
       <c r="P187" s="4" t="inlineStr"/>
@@ -10468,12 +10580,12 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>BULBESG1</t>
+          <t>PIBESSG1</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>Bulgana Green Power Hub</t>
+          <t>Phillip Island BESS</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
@@ -10482,7 +10594,7 @@
         </is>
       </c>
       <c r="D188" s="3" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E188" s="4" t="inlineStr"/>
       <c r="F188" s="4" t="inlineStr"/>
@@ -10490,17 +10602,15 @@
       <c r="H188" s="4" t="inlineStr"/>
       <c r="I188" s="4" t="inlineStr"/>
       <c r="J188" s="4" t="inlineStr"/>
-      <c r="K188" s="4" t="n">
-        <v>0.8949</v>
-      </c>
+      <c r="K188" s="4" t="inlineStr"/>
       <c r="L188" s="4" t="n">
-        <v>0.8839</v>
+        <v>0.9977</v>
       </c>
       <c r="M188" s="4" t="n">
-        <v>0.8821</v>
+        <v>0.9825</v>
       </c>
       <c r="N188" s="4" t="n">
-        <v>0.8733</v>
+        <v>0.9848</v>
       </c>
       <c r="O188" s="4" t="inlineStr"/>
       <c r="P188" s="4" t="inlineStr"/>
@@ -10510,12 +10620,12 @@
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>CHPSTWF1</t>
+          <t>FNWF1</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>Chepstowe Wind Farm</t>
+          <t>Ferguson North Wind Farm</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
@@ -10524,41 +10634,29 @@
         </is>
       </c>
       <c r="D189" s="3" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="E189" s="4" t="n">
-        <v>1.0207</v>
-      </c>
-      <c r="F189" s="4" t="n">
-        <v>1.0209</v>
-      </c>
-      <c r="G189" s="4" t="n">
-        <v>1.016</v>
-      </c>
-      <c r="H189" s="4" t="n">
-        <v>1.0016</v>
-      </c>
-      <c r="I189" s="4" t="n">
-        <v>0.9716</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="E189" s="4" t="inlineStr"/>
+      <c r="F189" s="4" t="inlineStr"/>
+      <c r="G189" s="4" t="inlineStr"/>
+      <c r="H189" s="4" t="inlineStr"/>
+      <c r="I189" s="4" t="inlineStr"/>
       <c r="J189" s="4" t="n">
-        <v>0.9711</v>
+        <v>1.0079</v>
       </c>
       <c r="K189" s="4" t="n">
-        <v>0.9699</v>
+        <v>1.0035</v>
       </c>
       <c r="L189" s="4" t="n">
-        <v>0.9699</v>
+        <v>0.9972</v>
       </c>
       <c r="M189" s="4" t="n">
-        <v>0.9759</v>
+        <v>0.9933</v>
       </c>
       <c r="N189" s="4" t="n">
-        <v>0.9718</v>
-      </c>
-      <c r="O189" s="4" t="n">
-        <v>0.9825</v>
-      </c>
+        <v>0.9993</v>
+      </c>
+      <c r="O189" s="4" t="inlineStr"/>
       <c r="P189" s="4" t="inlineStr"/>
       <c r="Q189" s="4" t="inlineStr"/>
       <c r="R189" s="5" t="inlineStr"/>
@@ -10566,21 +10664,21 @@
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>BBASEHOS</t>
+          <t>CHPSTWF1</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>Ballarat Base Hospital Plant</t>
+          <t>Chepstowe Wind Farm</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D190" s="3" t="n">
-        <v>1</v>
+        <v>6.15</v>
       </c>
       <c r="E190" s="4" t="n">
         <v>1.0207</v>
@@ -10618,6 +10716,62 @@
       <c r="P190" s="4" t="inlineStr"/>
       <c r="Q190" s="4" t="inlineStr"/>
       <c r="R190" s="5" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>BBASEHOS</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>Ballarat Base Hospital Plant</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D191" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E191" s="4" t="n">
+        <v>1.0207</v>
+      </c>
+      <c r="F191" s="4" t="n">
+        <v>1.0209</v>
+      </c>
+      <c r="G191" s="4" t="n">
+        <v>1.016</v>
+      </c>
+      <c r="H191" s="4" t="n">
+        <v>1.0016</v>
+      </c>
+      <c r="I191" s="4" t="n">
+        <v>0.9716</v>
+      </c>
+      <c r="J191" s="4" t="n">
+        <v>0.9711</v>
+      </c>
+      <c r="K191" s="4" t="n">
+        <v>0.9699</v>
+      </c>
+      <c r="L191" s="4" t="n">
+        <v>0.9699</v>
+      </c>
+      <c r="M191" s="4" t="n">
+        <v>0.9759</v>
+      </c>
+      <c r="N191" s="4" t="n">
+        <v>0.9718</v>
+      </c>
+      <c r="O191" s="4" t="n">
+        <v>0.9825</v>
+      </c>
+      <c r="P191" s="4" t="inlineStr"/>
+      <c r="Q191" s="4" t="inlineStr"/>
+      <c r="R191" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10630,7 +10784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M190"/>
+  <dimension ref="A1:M191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10751,21 +10905,15 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MUWAWF1</t>
+          <t>MUWAWF2</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr"/>
       <c r="C3" s="4" t="inlineStr"/>
       <c r="D3" s="4" t="inlineStr"/>
-      <c r="E3" s="4" t="n">
-        <v>0.9549</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>0.8885</v>
-      </c>
-      <c r="G3" s="4" t="n">
-        <v>0.8885</v>
-      </c>
+      <c r="E3" s="4" t="inlineStr"/>
+      <c r="F3" s="4" t="inlineStr"/>
+      <c r="G3" s="4" t="inlineStr"/>
       <c r="H3" s="4" t="n">
         <v>0.8883</v>
       </c>
@@ -10788,15 +10936,21 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>MUWAWF2</t>
+          <t>MUWAWF1</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr"/>
       <c r="C4" s="4" t="inlineStr"/>
       <c r="D4" s="4" t="inlineStr"/>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="n">
+        <v>0.9549</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>0.8885</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>0.8885</v>
+      </c>
       <c r="H4" s="4" t="n">
         <v>0.8883</v>
       </c>
@@ -10866,8 +11020,12 @@
       <c r="H6" s="4" t="inlineStr"/>
       <c r="I6" s="4" t="inlineStr"/>
       <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr"/>
+      <c r="K6" s="4" t="n">
+        <v>0.8733</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>0.8907</v>
+      </c>
       <c r="M6" s="4" t="n">
         <v>0.8868</v>
       </c>
@@ -11192,30 +11350,18 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>NUMURSF1</t>
+          <t>WUNUSF1</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr"/>
       <c r="C16" s="4" t="inlineStr"/>
       <c r="D16" s="4" t="inlineStr"/>
-      <c r="E16" s="4" t="n">
-        <v>0.982</v>
-      </c>
-      <c r="F16" s="4" t="n">
-        <v>0.9896</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>0.9945000000000001</v>
-      </c>
-      <c r="H16" s="4" t="n">
-        <v>0.9963</v>
-      </c>
-      <c r="I16" s="4" t="n">
-        <v>0.9715</v>
-      </c>
-      <c r="J16" s="4" t="n">
-        <v>0.9738</v>
-      </c>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr"/>
+      <c r="G16" s="4" t="inlineStr"/>
+      <c r="H16" s="4" t="inlineStr"/>
+      <c r="I16" s="4" t="inlineStr"/>
+      <c r="J16" s="4" t="inlineStr"/>
       <c r="K16" s="4" t="n">
         <v>0.9477</v>
       </c>
@@ -11229,18 +11375,30 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>WUNUSF1</t>
+          <t>NUMURSF1</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr"/>
       <c r="C17" s="4" t="inlineStr"/>
       <c r="D17" s="4" t="inlineStr"/>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr"/>
-      <c r="G17" s="4" t="inlineStr"/>
-      <c r="H17" s="4" t="inlineStr"/>
-      <c r="I17" s="4" t="inlineStr"/>
-      <c r="J17" s="4" t="inlineStr"/>
+      <c r="E17" s="4" t="n">
+        <v>0.982</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>0.9896</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>0.9945000000000001</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>0.9963</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>0.9715</v>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v>0.9738</v>
+      </c>
       <c r="K17" s="4" t="n">
         <v>0.9477</v>
       </c>
@@ -11302,7 +11460,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>WINTSF1</t>
+          <t>GLRWNSF1</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr"/>
@@ -11335,7 +11493,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>GLRWNSF1</t>
+          <t>WINTSF1</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr"/>
@@ -11441,20 +11599,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>GANNSF1</t>
+          <t>COHUNSF1</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr"/>
       <c r="C25" s="4" t="inlineStr"/>
-      <c r="D25" s="4" t="n">
-        <v>1.044</v>
-      </c>
-      <c r="E25" s="4" t="n">
-        <v>0.9729</v>
-      </c>
-      <c r="F25" s="4" t="n">
-        <v>0.8994</v>
-      </c>
+      <c r="D25" s="4" t="inlineStr"/>
+      <c r="E25" s="4" t="inlineStr"/>
+      <c r="F25" s="4" t="inlineStr"/>
       <c r="G25" s="4" t="n">
         <v>0.8863</v>
       </c>
@@ -11480,14 +11632,20 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>COHUNSF1</t>
+          <t>GANNSF1</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr"/>
       <c r="C26" s="4" t="inlineStr"/>
-      <c r="D26" s="4" t="inlineStr"/>
-      <c r="E26" s="4" t="inlineStr"/>
-      <c r="F26" s="4" t="inlineStr"/>
+      <c r="D26" s="4" t="n">
+        <v>1.044</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>0.9729</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>0.8994</v>
+      </c>
       <c r="G26" s="4" t="n">
         <v>0.8863</v>
       </c>
@@ -11608,7 +11766,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>BRYB2WF2</t>
+          <t>BRYB1WF1</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr"/>
@@ -11616,8 +11774,12 @@
       <c r="D30" s="4" t="inlineStr"/>
       <c r="E30" s="4" t="inlineStr"/>
       <c r="F30" s="4" t="inlineStr"/>
-      <c r="G30" s="4" t="inlineStr"/>
-      <c r="H30" s="4" t="inlineStr"/>
+      <c r="G30" s="4" t="n">
+        <v>0.9482</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>0.9431</v>
+      </c>
       <c r="I30" s="4" t="n">
         <v>0.9496</v>
       </c>
@@ -11637,7 +11799,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>BRYB1WF1</t>
+          <t>BRYB2WF2</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr"/>
@@ -11645,12 +11807,8 @@
       <c r="D31" s="4" t="inlineStr"/>
       <c r="E31" s="4" t="inlineStr"/>
       <c r="F31" s="4" t="inlineStr"/>
-      <c r="G31" s="4" t="n">
-        <v>0.9482</v>
-      </c>
-      <c r="H31" s="4" t="n">
-        <v>0.9431</v>
-      </c>
+      <c r="G31" s="4" t="inlineStr"/>
+      <c r="H31" s="4" t="inlineStr"/>
       <c r="I31" s="4" t="n">
         <v>0.9496</v>
       </c>
@@ -11853,39 +12011,19 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>MERCER01</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="n">
-        <v>1.0033</v>
-      </c>
-      <c r="C37" s="4" t="n">
-        <v>1.0048</v>
-      </c>
-      <c r="D37" s="4" t="n">
-        <v>1.001</v>
-      </c>
-      <c r="E37" s="4" t="n">
-        <v>0.9909</v>
-      </c>
-      <c r="F37" s="4" t="n">
-        <v>0.965</v>
-      </c>
-      <c r="G37" s="4" t="n">
-        <v>0.9500999999999999</v>
-      </c>
-      <c r="H37" s="4" t="n">
-        <v>0.9459</v>
-      </c>
-      <c r="I37" s="4" t="n">
-        <v>0.948</v>
-      </c>
-      <c r="J37" s="4" t="n">
-        <v>0.9576</v>
-      </c>
-      <c r="K37" s="4" t="n">
-        <v>0.9475</v>
-      </c>
+          <t>MOORABS1</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr"/>
+      <c r="C37" s="4" t="inlineStr"/>
+      <c r="D37" s="4" t="inlineStr"/>
+      <c r="E37" s="4" t="inlineStr"/>
+      <c r="F37" s="4" t="inlineStr"/>
+      <c r="G37" s="4" t="inlineStr"/>
+      <c r="H37" s="4" t="inlineStr"/>
+      <c r="I37" s="4" t="inlineStr"/>
+      <c r="J37" s="4" t="inlineStr"/>
+      <c r="K37" s="4" t="inlineStr"/>
       <c r="L37" s="4" t="n">
         <v>0.9569</v>
       </c>
@@ -11896,13 +12034,21 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>ELAINWF1</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr"/>
-      <c r="C38" s="4" t="inlineStr"/>
-      <c r="D38" s="4" t="inlineStr"/>
-      <c r="E38" s="4" t="inlineStr"/>
+          <t>MERCER01</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="n">
+        <v>1.0033</v>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>1.0048</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>1.001</v>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>0.9909</v>
+      </c>
       <c r="F38" s="4" t="n">
         <v>0.965</v>
       </c>
@@ -11931,20 +12077,34 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>MOORABS1</t>
+          <t>ELAINWF1</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr"/>
       <c r="C39" s="4" t="inlineStr"/>
       <c r="D39" s="4" t="inlineStr"/>
       <c r="E39" s="4" t="inlineStr"/>
-      <c r="F39" s="4" t="inlineStr"/>
-      <c r="G39" s="4" t="inlineStr"/>
-      <c r="H39" s="4" t="inlineStr"/>
-      <c r="I39" s="4" t="inlineStr"/>
-      <c r="J39" s="4" t="inlineStr"/>
-      <c r="K39" s="4" t="inlineStr"/>
-      <c r="L39" s="4" t="inlineStr"/>
+      <c r="F39" s="4" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>0.9500999999999999</v>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>0.9459</v>
+      </c>
+      <c r="I39" s="4" t="n">
+        <v>0.948</v>
+      </c>
+      <c r="J39" s="4" t="n">
+        <v>0.9576</v>
+      </c>
+      <c r="K39" s="4" t="n">
+        <v>0.9475</v>
+      </c>
+      <c r="L39" s="4" t="n">
+        <v>0.9569</v>
+      </c>
       <c r="M39" s="4" t="n">
         <v>0.9556</v>
       </c>
@@ -11952,7 +12112,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>MURAYNL1</t>
+          <t>MURRAY</t>
         </is>
       </c>
       <c r="B40" s="4" t="n">
@@ -11995,7 +12155,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>MURAYNL2</t>
+          <t>MURAYNL1</t>
         </is>
       </c>
       <c r="B41" s="4" t="n">
@@ -12081,7 +12241,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>MURRAY</t>
+          <t>MURAYNL2</t>
         </is>
       </c>
       <c r="B43" s="4" t="n">
@@ -12480,8 +12640,12 @@
       <c r="H52" s="4" t="inlineStr"/>
       <c r="I52" s="4" t="inlineStr"/>
       <c r="J52" s="4" t="inlineStr"/>
-      <c r="K52" s="4" t="inlineStr"/>
-      <c r="L52" s="4" t="inlineStr"/>
+      <c r="K52" s="4" t="n">
+        <v>0.9605</v>
+      </c>
+      <c r="L52" s="4" t="n">
+        <v>0.9766</v>
+      </c>
       <c r="M52" s="4" t="n">
         <v>0.9761</v>
       </c>
@@ -12489,23 +12653,23 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>CHALLHWF</t>
+          <t>HEPWIND1</t>
         </is>
       </c>
       <c r="B53" s="4" t="n">
-        <v>1.0988</v>
+        <v>1.0207</v>
       </c>
       <c r="C53" s="4" t="n">
-        <v>1.0988</v>
+        <v>1.0209</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>1.0988</v>
+        <v>1.016</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>0.9957</v>
+        <v>1.0016</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>0.9193</v>
+        <v>0.9716</v>
       </c>
       <c r="G53" s="4" t="n">
         <v>0.9711</v>
@@ -12571,19 +12735,23 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>YSWF1</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr"/>
-      <c r="C55" s="4" t="inlineStr"/>
+          <t>CHALLHWF</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="n">
+        <v>1.0988</v>
+      </c>
+      <c r="C55" s="4" t="n">
+        <v>1.0988</v>
+      </c>
       <c r="D55" s="4" t="n">
-        <v>1.016</v>
+        <v>1.0988</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>1.0016</v>
+        <v>0.9957</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>0.9716</v>
+        <v>0.9193</v>
       </c>
       <c r="G55" s="4" t="n">
         <v>0.9711</v>
@@ -12610,15 +12778,11 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>HEPWIND1</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="n">
-        <v>1.0207</v>
-      </c>
-      <c r="C56" s="4" t="n">
-        <v>1.0209</v>
-      </c>
+          <t>YSWF1</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr"/>
+      <c r="C56" s="4" t="inlineStr"/>
       <c r="D56" s="4" t="n">
         <v>1.016</v>
       </c>
@@ -12665,8 +12829,12 @@
       <c r="H57" s="4" t="inlineStr"/>
       <c r="I57" s="4" t="inlineStr"/>
       <c r="J57" s="4" t="inlineStr"/>
-      <c r="K57" s="4" t="inlineStr"/>
-      <c r="L57" s="4" t="inlineStr"/>
+      <c r="K57" s="4" t="n">
+        <v>0.9836</v>
+      </c>
+      <c r="L57" s="4" t="n">
+        <v>0.9704</v>
+      </c>
       <c r="M57" s="4" t="n">
         <v>0.9794</v>
       </c>
@@ -12674,7 +12842,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>MURR2-1</t>
+          <t>MURR1-10</t>
         </is>
       </c>
       <c r="B58" s="4" t="n">
@@ -12717,7 +12885,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>MURR1-9</t>
+          <t>MURR1-1</t>
         </is>
       </c>
       <c r="B59" s="4" t="n">
@@ -12760,7 +12928,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>MURR1-10</t>
+          <t>MURR1-8</t>
         </is>
       </c>
       <c r="B60" s="4" t="n">
@@ -12803,7 +12971,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>MURR1-7</t>
+          <t>MURR2-4</t>
         </is>
       </c>
       <c r="B61" s="4" t="n">
@@ -12846,7 +13014,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>MURR2-2</t>
+          <t>MURR1-2</t>
         </is>
       </c>
       <c r="B62" s="4" t="n">
@@ -12889,7 +13057,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>MURR1-8</t>
+          <t>MURR2-3</t>
         </is>
       </c>
       <c r="B63" s="4" t="n">
@@ -12932,7 +13100,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>MURR2-3</t>
+          <t>MURR1-3</t>
         </is>
       </c>
       <c r="B64" s="4" t="n">
@@ -12975,7 +13143,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>MURR1-3</t>
+          <t>MURR2-1</t>
         </is>
       </c>
       <c r="B65" s="4" t="n">
@@ -13018,7 +13186,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>MURR1-6</t>
+          <t>MURR1-5</t>
         </is>
       </c>
       <c r="B66" s="4" t="n">
@@ -13061,7 +13229,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>MURR1-5</t>
+          <t>MURR1-6</t>
         </is>
       </c>
       <c r="B67" s="4" t="n">
@@ -13104,7 +13272,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>MURR1-1</t>
+          <t>MURR1-7</t>
         </is>
       </c>
       <c r="B68" s="4" t="n">
@@ -13147,7 +13315,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>MURR1-2</t>
+          <t>MURR1-9</t>
         </is>
       </c>
       <c r="B69" s="4" t="n">
@@ -13190,7 +13358,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>MURR1-4</t>
+          <t>MURR2-2</t>
         </is>
       </c>
       <c r="B70" s="4" t="n">
@@ -13233,7 +13401,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>MURR2-4</t>
+          <t>MURR1-4</t>
         </is>
       </c>
       <c r="B71" s="4" t="n">
@@ -13276,7 +13444,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>GPWFEST1</t>
+          <t>GPWFEST3</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr"/>
@@ -13326,7 +13494,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>GPWFEST3</t>
+          <t>GPWFEST1</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr"/>
@@ -13378,7 +13546,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>JLB03</t>
+          <t>JLA02</t>
         </is>
       </c>
       <c r="B76" s="4" t="n">
@@ -13421,7 +13589,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>JLB02</t>
+          <t>JLA04</t>
         </is>
       </c>
       <c r="B77" s="4" t="n">
@@ -13464,7 +13632,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>JLB01</t>
+          <t>JLA01</t>
         </is>
       </c>
       <c r="B78" s="4" t="n">
@@ -13507,7 +13675,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>JLA03</t>
+          <t>JLB01</t>
         </is>
       </c>
       <c r="B79" s="4" t="n">
@@ -13550,7 +13718,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>JLA04</t>
+          <t>JLA03</t>
         </is>
       </c>
       <c r="B80" s="4" t="n">
@@ -13593,7 +13761,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>JLA01</t>
+          <t>JLB03</t>
         </is>
       </c>
       <c r="B81" s="4" t="n">
@@ -13636,21 +13804,41 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>GPWFWST2</t>
-        </is>
-      </c>
-      <c r="B82" s="4" t="inlineStr"/>
-      <c r="C82" s="4" t="inlineStr"/>
-      <c r="D82" s="4" t="inlineStr"/>
-      <c r="E82" s="4" t="inlineStr"/>
-      <c r="F82" s="4" t="inlineStr"/>
-      <c r="G82" s="4" t="inlineStr"/>
-      <c r="H82" s="4" t="inlineStr"/>
-      <c r="I82" s="4" t="inlineStr"/>
-      <c r="J82" s="4" t="inlineStr"/>
-      <c r="K82" s="4" t="inlineStr"/>
+          <t>JLB02</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="n">
+        <v>0.9667</v>
+      </c>
+      <c r="C82" s="4" t="n">
+        <v>0.9641</v>
+      </c>
+      <c r="D82" s="4" t="n">
+        <v>0.983</v>
+      </c>
+      <c r="E82" s="4" t="n">
+        <v>0.9782999999999999</v>
+      </c>
+      <c r="F82" s="4" t="n">
+        <v>0.9731</v>
+      </c>
+      <c r="G82" s="4" t="n">
+        <v>0.9734</v>
+      </c>
+      <c r="H82" s="4" t="n">
+        <v>0.9755</v>
+      </c>
+      <c r="I82" s="4" t="n">
+        <v>0.9727</v>
+      </c>
+      <c r="J82" s="4" t="n">
+        <v>0.9764</v>
+      </c>
+      <c r="K82" s="4" t="n">
+        <v>0.9789</v>
+      </c>
       <c r="L82" s="4" t="n">
-        <v>0.9837</v>
+        <v>0.9768</v>
       </c>
       <c r="M82" s="4" t="n">
         <v>0.9823</v>
@@ -13682,41 +13870,21 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>JLA02</t>
-        </is>
-      </c>
-      <c r="B84" s="4" t="n">
-        <v>0.9667</v>
-      </c>
-      <c r="C84" s="4" t="n">
-        <v>0.9641</v>
-      </c>
-      <c r="D84" s="4" t="n">
-        <v>0.983</v>
-      </c>
-      <c r="E84" s="4" t="n">
-        <v>0.9782999999999999</v>
-      </c>
-      <c r="F84" s="4" t="n">
-        <v>0.9731</v>
-      </c>
-      <c r="G84" s="4" t="n">
-        <v>0.9734</v>
-      </c>
-      <c r="H84" s="4" t="n">
-        <v>0.9755</v>
-      </c>
-      <c r="I84" s="4" t="n">
-        <v>0.9727</v>
-      </c>
-      <c r="J84" s="4" t="n">
-        <v>0.9764</v>
-      </c>
-      <c r="K84" s="4" t="n">
-        <v>0.9789</v>
-      </c>
+          <t>GPWFWST2</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr"/>
+      <c r="C84" s="4" t="inlineStr"/>
+      <c r="D84" s="4" t="inlineStr"/>
+      <c r="E84" s="4" t="inlineStr"/>
+      <c r="F84" s="4" t="inlineStr"/>
+      <c r="G84" s="4" t="inlineStr"/>
+      <c r="H84" s="4" t="inlineStr"/>
+      <c r="I84" s="4" t="inlineStr"/>
+      <c r="J84" s="4" t="inlineStr"/>
+      <c r="K84" s="4" t="inlineStr"/>
       <c r="L84" s="4" t="n">
-        <v>0.9768</v>
+        <v>0.9837</v>
       </c>
       <c r="M84" s="4" t="n">
         <v>0.9823</v>
@@ -13768,30 +13936,26 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>DUNDWF1</t>
+          <t>STOCKYD1</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr"/>
       <c r="C86" s="4" t="inlineStr"/>
       <c r="D86" s="4" t="inlineStr"/>
       <c r="E86" s="4" t="inlineStr"/>
-      <c r="F86" s="4" t="n">
+      <c r="F86" s="4" t="inlineStr"/>
+      <c r="G86" s="4" t="inlineStr"/>
+      <c r="H86" s="4" t="n">
+        <v>0.9782</v>
+      </c>
+      <c r="I86" s="4" t="n">
+        <v>0.9799</v>
+      </c>
+      <c r="J86" s="4" t="n">
+        <v>0.9869</v>
+      </c>
+      <c r="K86" s="4" t="n">
         <v>0.9812</v>
-      </c>
-      <c r="G86" s="4" t="n">
-        <v>0.979</v>
-      </c>
-      <c r="H86" s="4" t="n">
-        <v>0.9789</v>
-      </c>
-      <c r="I86" s="4" t="n">
-        <v>0.9824000000000001</v>
-      </c>
-      <c r="J86" s="4" t="n">
-        <v>0.987</v>
-      </c>
-      <c r="K86" s="4" t="n">
-        <v>0.981</v>
       </c>
       <c r="L86" s="4" t="n">
         <v>0.9845</v>
@@ -13803,7 +13967,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>DUNDWF2</t>
+          <t>DUNDWF3</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr"/>
@@ -13838,7 +14002,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>DUNDWF3</t>
+          <t>DUNDWF2</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr"/>
@@ -13873,26 +14037,30 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>STOCKYD1</t>
+          <t>DUNDWF1</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr"/>
       <c r="C89" s="4" t="inlineStr"/>
       <c r="D89" s="4" t="inlineStr"/>
       <c r="E89" s="4" t="inlineStr"/>
-      <c r="F89" s="4" t="inlineStr"/>
-      <c r="G89" s="4" t="inlineStr"/>
+      <c r="F89" s="4" t="n">
+        <v>0.9812</v>
+      </c>
+      <c r="G89" s="4" t="n">
+        <v>0.979</v>
+      </c>
       <c r="H89" s="4" t="n">
-        <v>0.9782</v>
+        <v>0.9789</v>
       </c>
       <c r="I89" s="4" t="n">
-        <v>0.9799</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="J89" s="4" t="n">
-        <v>0.9869</v>
+        <v>0.987</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>0.9812</v>
+        <v>0.981</v>
       </c>
       <c r="L89" s="4" t="n">
         <v>0.9845</v>
@@ -13929,7 +14097,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>LYA1</t>
+          <t>VPGS1</t>
         </is>
       </c>
       <c r="B91" s="4" t="n">
@@ -13972,7 +14140,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>LYNL1</t>
+          <t>VPGS2</t>
         </is>
       </c>
       <c r="B92" s="4" t="n">
@@ -14015,7 +14183,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>LYA4</t>
+          <t>VPGS6</t>
         </is>
       </c>
       <c r="B93" s="4" t="n">
@@ -14058,7 +14226,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>LYA3</t>
+          <t>VPGS5</t>
         </is>
       </c>
       <c r="B94" s="4" t="n">
@@ -14101,7 +14269,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>LYA2</t>
+          <t>VPGS3</t>
         </is>
       </c>
       <c r="B95" s="4" t="n">
@@ -14144,7 +14312,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>LOYYB1</t>
+          <t>LYNL1</t>
         </is>
       </c>
       <c r="B96" s="4" t="n">
@@ -14187,7 +14355,7 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>LOYYB2</t>
+          <t>VPGS4</t>
         </is>
       </c>
       <c r="B97" s="4" t="n">
@@ -14230,7 +14398,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>VPGS2</t>
+          <t>LYA4</t>
         </is>
       </c>
       <c r="B98" s="4" t="n">
@@ -14273,7 +14441,7 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>VPGS4</t>
+          <t>LOYYB2</t>
         </is>
       </c>
       <c r="B99" s="4" t="n">
@@ -14316,7 +14484,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>VPGS6</t>
+          <t>LYA1</t>
         </is>
       </c>
       <c r="B100" s="4" t="n">
@@ -14359,7 +14527,7 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>VPGS5</t>
+          <t>LYA2</t>
         </is>
       </c>
       <c r="B101" s="4" t="n">
@@ -14402,7 +14570,7 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>VPGS1</t>
+          <t>LYA3</t>
         </is>
       </c>
       <c r="B102" s="4" t="n">
@@ -14445,7 +14613,7 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>VPGS3</t>
+          <t>LOYYB1</t>
         </is>
       </c>
       <c r="B103" s="4" t="n">
@@ -14531,7 +14699,7 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>EILDON1</t>
+          <t>EILDON2</t>
         </is>
       </c>
       <c r="B105" s="4" t="n">
@@ -14574,7 +14742,7 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>EILDON2</t>
+          <t>EILDON1</t>
         </is>
       </c>
       <c r="B106" s="4" t="n">
@@ -14630,7 +14798,9 @@
       <c r="I107" s="4" t="inlineStr"/>
       <c r="J107" s="4" t="inlineStr"/>
       <c r="K107" s="4" t="inlineStr"/>
-      <c r="L107" s="4" t="inlineStr"/>
+      <c r="L107" s="4" t="n">
+        <v>0.9951</v>
+      </c>
       <c r="M107" s="4" t="n">
         <v>0.9862</v>
       </c>
@@ -14736,8 +14906,12 @@
       <c r="H110" s="4" t="inlineStr"/>
       <c r="I110" s="4" t="inlineStr"/>
       <c r="J110" s="4" t="inlineStr"/>
-      <c r="K110" s="4" t="inlineStr"/>
-      <c r="L110" s="4" t="inlineStr"/>
+      <c r="K110" s="4" t="n">
+        <v>0.9864000000000001</v>
+      </c>
+      <c r="L110" s="4" t="n">
+        <v>0.9873</v>
+      </c>
       <c r="M110" s="4" t="n">
         <v>0.9873</v>
       </c>
@@ -14882,8 +15056,12 @@
       <c r="H114" s="4" t="inlineStr"/>
       <c r="I114" s="4" t="inlineStr"/>
       <c r="J114" s="4" t="inlineStr"/>
-      <c r="K114" s="4" t="inlineStr"/>
-      <c r="L114" s="4" t="inlineStr"/>
+      <c r="K114" s="4" t="n">
+        <v>0.9858</v>
+      </c>
+      <c r="L114" s="4" t="n">
+        <v>0.9918</v>
+      </c>
       <c r="M114" s="4" t="n">
         <v>0.9897</v>
       </c>
@@ -14903,8 +15081,12 @@
       <c r="H115" s="4" t="inlineStr"/>
       <c r="I115" s="4" t="inlineStr"/>
       <c r="J115" s="4" t="inlineStr"/>
-      <c r="K115" s="4" t="inlineStr"/>
-      <c r="L115" s="4" t="inlineStr"/>
+      <c r="K115" s="4" t="n">
+        <v>0.9597</v>
+      </c>
+      <c r="L115" s="4" t="n">
+        <v>0.9857</v>
+      </c>
       <c r="M115" s="4" t="n">
         <v>0.9919</v>
       </c>
@@ -14912,7 +15094,7 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>TGNSS1</t>
+          <t>GLENMAG1</t>
         </is>
       </c>
       <c r="B116" s="4" t="n">
@@ -14955,20 +15137,42 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>PIBESS1</t>
-        </is>
-      </c>
-      <c r="B117" s="4" t="inlineStr"/>
-      <c r="C117" s="4" t="inlineStr"/>
-      <c r="D117" s="4" t="inlineStr"/>
-      <c r="E117" s="4" t="inlineStr"/>
-      <c r="F117" s="4" t="inlineStr"/>
-      <c r="G117" s="4" t="inlineStr"/>
-      <c r="H117" s="4" t="inlineStr"/>
-      <c r="I117" s="4" t="inlineStr"/>
-      <c r="J117" s="4" t="inlineStr"/>
-      <c r="K117" s="4" t="inlineStr"/>
-      <c r="L117" s="4" t="inlineStr"/>
+          <t>TOORAWF</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="n">
+        <v>0.9799</v>
+      </c>
+      <c r="C117" s="4" t="n">
+        <v>0.9759</v>
+      </c>
+      <c r="D117" s="4" t="n">
+        <v>0.9886</v>
+      </c>
+      <c r="E117" s="4" t="n">
+        <v>0.9879</v>
+      </c>
+      <c r="F117" s="4" t="n">
+        <v>0.9938</v>
+      </c>
+      <c r="G117" s="4" t="n">
+        <v>0.9955000000000001</v>
+      </c>
+      <c r="H117" s="4" t="n">
+        <v>0.9936</v>
+      </c>
+      <c r="I117" s="4" t="n">
+        <v>0.9977</v>
+      </c>
+      <c r="J117" s="4" t="n">
+        <v>0.9825</v>
+      </c>
+      <c r="K117" s="4" t="n">
+        <v>0.9848</v>
+      </c>
+      <c r="L117" s="4" t="n">
+        <v>0.9862</v>
+      </c>
       <c r="M117" s="4" t="n">
         <v>0.992</v>
       </c>
@@ -15019,36 +15223,18 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>GLENMAG1</t>
-        </is>
-      </c>
-      <c r="B119" s="4" t="n">
-        <v>0.9799</v>
-      </c>
-      <c r="C119" s="4" t="n">
-        <v>0.9759</v>
-      </c>
-      <c r="D119" s="4" t="n">
-        <v>0.9886</v>
-      </c>
-      <c r="E119" s="4" t="n">
-        <v>0.9879</v>
-      </c>
-      <c r="F119" s="4" t="n">
-        <v>0.9938</v>
-      </c>
-      <c r="G119" s="4" t="n">
-        <v>0.9955000000000001</v>
-      </c>
-      <c r="H119" s="4" t="n">
-        <v>0.9936</v>
-      </c>
-      <c r="I119" s="4" t="n">
-        <v>0.9977</v>
-      </c>
-      <c r="J119" s="4" t="n">
-        <v>0.9825</v>
-      </c>
+          <t>PIBESS1</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr"/>
+      <c r="C119" s="4" t="inlineStr"/>
+      <c r="D119" s="4" t="inlineStr"/>
+      <c r="E119" s="4" t="inlineStr"/>
+      <c r="F119" s="4" t="inlineStr"/>
+      <c r="G119" s="4" t="inlineStr"/>
+      <c r="H119" s="4" t="inlineStr"/>
+      <c r="I119" s="4" t="inlineStr"/>
+      <c r="J119" s="4" t="inlineStr"/>
       <c r="K119" s="4" t="n">
         <v>0.9848</v>
       </c>
@@ -15062,7 +15248,7 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>TOORAWF</t>
+          <t>WONWP</t>
         </is>
       </c>
       <c r="B120" s="4" t="n">
@@ -15148,7 +15334,7 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>WONWP</t>
+          <t>TGNSS1</t>
         </is>
       </c>
       <c r="B122" s="4" t="n">
@@ -15203,8 +15389,12 @@
       <c r="H123" s="4" t="inlineStr"/>
       <c r="I123" s="4" t="inlineStr"/>
       <c r="J123" s="4" t="inlineStr"/>
-      <c r="K123" s="4" t="inlineStr"/>
-      <c r="L123" s="4" t="inlineStr"/>
+      <c r="K123" s="4" t="n">
+        <v>0.9889</v>
+      </c>
+      <c r="L123" s="4" t="n">
+        <v>0.9902</v>
+      </c>
       <c r="M123" s="4" t="n">
         <v>0.9933999999999999</v>
       </c>
@@ -15212,127 +15402,105 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>WILLHOV1</t>
-        </is>
-      </c>
-      <c r="B124" s="4" t="n">
-        <v>1.048</v>
-      </c>
-      <c r="C124" s="4" t="n">
-        <v>1.0235</v>
-      </c>
-      <c r="D124" s="4" t="n">
-        <v>0.9621</v>
-      </c>
-      <c r="E124" s="4" t="n">
-        <v>0.9712</v>
-      </c>
-      <c r="F124" s="4" t="n">
-        <v>1.0188</v>
-      </c>
-      <c r="G124" s="4" t="n">
-        <v>1.0274</v>
-      </c>
-      <c r="H124" s="4" t="n">
-        <v>1.0299</v>
-      </c>
-      <c r="I124" s="4" t="n">
-        <v>1.0182</v>
-      </c>
-      <c r="J124" s="4" t="n">
-        <v>1.0233</v>
-      </c>
-      <c r="K124" s="4" t="n">
-        <v>1.016</v>
-      </c>
+          <t>MLB01</t>
+        </is>
+      </c>
+      <c r="B124" s="4" t="inlineStr"/>
+      <c r="C124" s="4" t="inlineStr"/>
+      <c r="D124" s="4" t="inlineStr"/>
+      <c r="E124" s="4" t="inlineStr"/>
+      <c r="F124" s="4" t="inlineStr"/>
+      <c r="G124" s="4" t="inlineStr"/>
+      <c r="H124" s="4" t="inlineStr"/>
+      <c r="I124" s="4" t="inlineStr"/>
+      <c r="J124" s="4" t="inlineStr"/>
+      <c r="K124" s="4" t="inlineStr"/>
       <c r="L124" s="4" t="n">
-        <v>1.0135</v>
+        <v>0.9945000000000001</v>
       </c>
       <c r="M124" s="4" t="n">
-        <v>0.9945000000000001</v>
+        <v>0.994</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>MREHA3</t>
-        </is>
-      </c>
-      <c r="B125" s="4" t="inlineStr"/>
-      <c r="C125" s="4" t="inlineStr"/>
-      <c r="D125" s="4" t="inlineStr"/>
-      <c r="E125" s="4" t="inlineStr"/>
-      <c r="F125" s="4" t="inlineStr"/>
-      <c r="G125" s="4" t="inlineStr"/>
-      <c r="H125" s="4" t="inlineStr"/>
-      <c r="I125" s="4" t="inlineStr"/>
-      <c r="J125" s="4" t="inlineStr"/>
-      <c r="K125" s="4" t="inlineStr"/>
-      <c r="L125" s="4" t="inlineStr"/>
+          <t>WILLHOV1</t>
+        </is>
+      </c>
+      <c r="B125" s="4" t="n">
+        <v>1.048</v>
+      </c>
+      <c r="C125" s="4" t="n">
+        <v>1.0235</v>
+      </c>
+      <c r="D125" s="4" t="n">
+        <v>0.9621</v>
+      </c>
+      <c r="E125" s="4" t="n">
+        <v>0.9712</v>
+      </c>
+      <c r="F125" s="4" t="n">
+        <v>1.0188</v>
+      </c>
+      <c r="G125" s="4" t="n">
+        <v>1.0274</v>
+      </c>
+      <c r="H125" s="4" t="n">
+        <v>1.0299</v>
+      </c>
+      <c r="I125" s="4" t="n">
+        <v>1.0182</v>
+      </c>
+      <c r="J125" s="4" t="n">
+        <v>1.0233</v>
+      </c>
+      <c r="K125" s="4" t="n">
+        <v>1.016</v>
+      </c>
+      <c r="L125" s="4" t="n">
+        <v>1.0135</v>
+      </c>
       <c r="M125" s="4" t="n">
-        <v>0.9947</v>
+        <v>0.9945000000000001</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>CODRNGTON</t>
-        </is>
-      </c>
-      <c r="B126" s="4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="C126" s="4" t="n">
-        <v>1.0339</v>
-      </c>
-      <c r="D126" s="4" t="n">
-        <v>1.0322</v>
-      </c>
-      <c r="E126" s="4" t="n">
-        <v>1.0149</v>
-      </c>
-      <c r="F126" s="4" t="n">
-        <v>1.0019</v>
-      </c>
-      <c r="G126" s="4" t="n">
-        <v>1.0063</v>
-      </c>
-      <c r="H126" s="4" t="n">
-        <v>1.0035</v>
-      </c>
-      <c r="I126" s="4" t="n">
-        <v>0.9972</v>
-      </c>
-      <c r="J126" s="4" t="n">
-        <v>0.9933</v>
-      </c>
-      <c r="K126" s="4" t="n">
-        <v>0.9993</v>
-      </c>
+          <t>MREHA3</t>
+        </is>
+      </c>
+      <c r="B126" s="4" t="inlineStr"/>
+      <c r="C126" s="4" t="inlineStr"/>
+      <c r="D126" s="4" t="inlineStr"/>
+      <c r="E126" s="4" t="inlineStr"/>
+      <c r="F126" s="4" t="inlineStr"/>
+      <c r="G126" s="4" t="inlineStr"/>
+      <c r="H126" s="4" t="inlineStr"/>
+      <c r="I126" s="4" t="inlineStr"/>
+      <c r="J126" s="4" t="inlineStr"/>
+      <c r="K126" s="4" t="inlineStr"/>
       <c r="L126" s="4" t="n">
-        <v>1.0018</v>
+        <v>0.9957</v>
       </c>
       <c r="M126" s="4" t="n">
-        <v>0.9949</v>
+        <v>0.9947</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>TIMWEST</t>
+          <t>FSWF1</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr"/>
       <c r="C127" s="4" t="inlineStr"/>
       <c r="D127" s="4" t="inlineStr"/>
-      <c r="E127" s="4" t="n">
-        <v>1.0149</v>
-      </c>
-      <c r="F127" s="4" t="n">
-        <v>1.0019</v>
-      </c>
+      <c r="E127" s="4" t="inlineStr"/>
+      <c r="F127" s="4" t="inlineStr"/>
       <c r="G127" s="4" t="n">
-        <v>1.0063</v>
+        <v>1.0079</v>
       </c>
       <c r="H127" s="4" t="n">
         <v>1.0035</v>
@@ -15356,16 +15524,26 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>FSWF1</t>
-        </is>
-      </c>
-      <c r="B128" s="4" t="inlineStr"/>
-      <c r="C128" s="4" t="inlineStr"/>
-      <c r="D128" s="4" t="inlineStr"/>
-      <c r="E128" s="4" t="inlineStr"/>
-      <c r="F128" s="4" t="inlineStr"/>
+          <t>OAKLAND1</t>
+        </is>
+      </c>
+      <c r="B128" s="4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="C128" s="4" t="n">
+        <v>1.0339</v>
+      </c>
+      <c r="D128" s="4" t="n">
+        <v>1.0322</v>
+      </c>
+      <c r="E128" s="4" t="n">
+        <v>1.0149</v>
+      </c>
+      <c r="F128" s="4" t="n">
+        <v>1.0019</v>
+      </c>
       <c r="G128" s="4" t="n">
-        <v>1.0079</v>
+        <v>1.0063</v>
       </c>
       <c r="H128" s="4" t="n">
         <v>1.0035</v>
@@ -15389,7 +15567,7 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>YAMBUKWF</t>
+          <t>MLWF1</t>
         </is>
       </c>
       <c r="B129" s="4" t="n">
@@ -15432,7 +15610,7 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>MLWF1</t>
+          <t>YAMBUKWF</t>
         </is>
       </c>
       <c r="B130" s="4" t="n">
@@ -15475,7 +15653,7 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>OAKLAND1</t>
+          <t>CODRNGTON</t>
         </is>
       </c>
       <c r="B131" s="4" t="n">
@@ -15518,22 +15696,38 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>MREHA1</t>
+          <t>TIMWEST</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr"/>
       <c r="C132" s="4" t="inlineStr"/>
       <c r="D132" s="4" t="inlineStr"/>
-      <c r="E132" s="4" t="inlineStr"/>
-      <c r="F132" s="4" t="inlineStr"/>
-      <c r="G132" s="4" t="inlineStr"/>
-      <c r="H132" s="4" t="inlineStr"/>
-      <c r="I132" s="4" t="inlineStr"/>
-      <c r="J132" s="4" t="inlineStr"/>
-      <c r="K132" s="4" t="inlineStr"/>
-      <c r="L132" s="4" t="inlineStr"/>
+      <c r="E132" s="4" t="n">
+        <v>1.0149</v>
+      </c>
+      <c r="F132" s="4" t="n">
+        <v>1.0019</v>
+      </c>
+      <c r="G132" s="4" t="n">
+        <v>1.0063</v>
+      </c>
+      <c r="H132" s="4" t="n">
+        <v>1.0035</v>
+      </c>
+      <c r="I132" s="4" t="n">
+        <v>0.9972</v>
+      </c>
+      <c r="J132" s="4" t="n">
+        <v>0.9933</v>
+      </c>
+      <c r="K132" s="4" t="n">
+        <v>0.9993</v>
+      </c>
+      <c r="L132" s="4" t="n">
+        <v>1.0018</v>
+      </c>
       <c r="M132" s="4" t="n">
-        <v>0.9951</v>
+        <v>0.9949</v>
       </c>
     </row>
     <row r="133">
@@ -15551,8 +15745,12 @@
       <c r="H133" s="4" t="inlineStr"/>
       <c r="I133" s="4" t="inlineStr"/>
       <c r="J133" s="4" t="inlineStr"/>
-      <c r="K133" s="4" t="inlineStr"/>
-      <c r="L133" s="4" t="inlineStr"/>
+      <c r="K133" s="4" t="n">
+        <v>0.993</v>
+      </c>
+      <c r="L133" s="4" t="n">
+        <v>0.9955000000000001</v>
+      </c>
       <c r="M133" s="4" t="n">
         <v>0.9951</v>
       </c>
@@ -15560,44 +15758,26 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>MORTLK11</t>
-        </is>
-      </c>
-      <c r="B134" s="4" t="n">
-        <v>0.9942</v>
-      </c>
-      <c r="C134" s="4" t="n">
-        <v>1.0015</v>
-      </c>
-      <c r="D134" s="4" t="n">
-        <v>1.005</v>
-      </c>
-      <c r="E134" s="4" t="n">
-        <v>0.9961</v>
-      </c>
-      <c r="F134" s="4" t="n">
-        <v>0.9852</v>
-      </c>
-      <c r="G134" s="4" t="n">
-        <v>0.9845</v>
-      </c>
-      <c r="H134" s="4" t="n">
-        <v>0.9865</v>
-      </c>
-      <c r="I134" s="4" t="n">
-        <v>0.9901</v>
-      </c>
-      <c r="J134" s="4" t="n">
-        <v>0.9927</v>
-      </c>
+          <t>MREHA1</t>
+        </is>
+      </c>
+      <c r="B134" s="4" t="inlineStr"/>
+      <c r="C134" s="4" t="inlineStr"/>
+      <c r="D134" s="4" t="inlineStr"/>
+      <c r="E134" s="4" t="inlineStr"/>
+      <c r="F134" s="4" t="inlineStr"/>
+      <c r="G134" s="4" t="inlineStr"/>
+      <c r="H134" s="4" t="inlineStr"/>
+      <c r="I134" s="4" t="inlineStr"/>
+      <c r="J134" s="4" t="inlineStr"/>
       <c r="K134" s="4" t="n">
-        <v>0.9913999999999999</v>
+        <v>0.993</v>
       </c>
       <c r="L134" s="4" t="n">
-        <v>0.9969</v>
+        <v>0.9955000000000001</v>
       </c>
       <c r="M134" s="4" t="n">
-        <v>0.9955000000000001</v>
+        <v>0.9951</v>
       </c>
     </row>
     <row r="135">
@@ -15646,62 +15826,66 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>RANGEB1</t>
-        </is>
-      </c>
-      <c r="B136" s="4" t="inlineStr"/>
-      <c r="C136" s="4" t="inlineStr"/>
-      <c r="D136" s="4" t="inlineStr"/>
-      <c r="E136" s="4" t="inlineStr"/>
-      <c r="F136" s="4" t="inlineStr"/>
-      <c r="G136" s="4" t="inlineStr"/>
-      <c r="H136" s="4" t="inlineStr"/>
-      <c r="I136" s="4" t="inlineStr"/>
-      <c r="J136" s="4" t="inlineStr"/>
-      <c r="K136" s="4" t="inlineStr"/>
-      <c r="L136" s="4" t="inlineStr"/>
+          <t>MORTLK11</t>
+        </is>
+      </c>
+      <c r="B136" s="4" t="n">
+        <v>0.9942</v>
+      </c>
+      <c r="C136" s="4" t="n">
+        <v>1.0015</v>
+      </c>
+      <c r="D136" s="4" t="n">
+        <v>1.005</v>
+      </c>
+      <c r="E136" s="4" t="n">
+        <v>0.9961</v>
+      </c>
+      <c r="F136" s="4" t="n">
+        <v>0.9852</v>
+      </c>
+      <c r="G136" s="4" t="n">
+        <v>0.9845</v>
+      </c>
+      <c r="H136" s="4" t="n">
+        <v>0.9865</v>
+      </c>
+      <c r="I136" s="4" t="n">
+        <v>0.9901</v>
+      </c>
+      <c r="J136" s="4" t="n">
+        <v>0.9927</v>
+      </c>
+      <c r="K136" s="4" t="n">
+        <v>0.9913999999999999</v>
+      </c>
+      <c r="L136" s="4" t="n">
+        <v>0.9969</v>
+      </c>
       <c r="M136" s="4" t="n">
-        <v>0.9957</v>
+        <v>0.9955000000000001</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>NPS</t>
-        </is>
-      </c>
-      <c r="B137" s="4" t="n">
-        <v>0.9952</v>
-      </c>
-      <c r="C137" s="4" t="n">
-        <v>0.9939</v>
-      </c>
-      <c r="D137" s="4" t="n">
-        <v>0.999</v>
-      </c>
-      <c r="E137" s="4" t="n">
-        <v>0.9962</v>
-      </c>
-      <c r="F137" s="4" t="n">
-        <v>0.9922</v>
-      </c>
-      <c r="G137" s="4" t="n">
-        <v>0.9913999999999999</v>
-      </c>
-      <c r="H137" s="4" t="n">
-        <v>0.9926</v>
-      </c>
-      <c r="I137" s="4" t="n">
-        <v>0.9919</v>
-      </c>
-      <c r="J137" s="4" t="n">
-        <v>0.9937</v>
-      </c>
+          <t>RANGEB1</t>
+        </is>
+      </c>
+      <c r="B137" s="4" t="inlineStr"/>
+      <c r="C137" s="4" t="inlineStr"/>
+      <c r="D137" s="4" t="inlineStr"/>
+      <c r="E137" s="4" t="inlineStr"/>
+      <c r="F137" s="4" t="inlineStr"/>
+      <c r="G137" s="4" t="inlineStr"/>
+      <c r="H137" s="4" t="inlineStr"/>
+      <c r="I137" s="4" t="inlineStr"/>
+      <c r="J137" s="4" t="inlineStr"/>
       <c r="K137" s="4" t="n">
-        <v>0.9941</v>
+        <v>0.9955000000000001</v>
       </c>
       <c r="L137" s="4" t="n">
-        <v>0.9943</v>
+        <v>0.9961</v>
       </c>
       <c r="M137" s="4" t="n">
         <v>0.9957</v>
@@ -15710,50 +15894,50 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>HALAMRD1</t>
+          <t>NPS</t>
         </is>
       </c>
       <c r="B138" s="4" t="n">
-        <v>0.9931</v>
+        <v>0.9952</v>
       </c>
       <c r="C138" s="4" t="n">
-        <v>0.9932</v>
+        <v>0.9939</v>
       </c>
       <c r="D138" s="4" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="E138" s="4" t="n">
         <v>0.9962</v>
       </c>
-      <c r="E138" s="4" t="n">
-        <v>0.9956</v>
-      </c>
       <c r="F138" s="4" t="n">
-        <v>0.9944</v>
+        <v>0.9922</v>
       </c>
       <c r="G138" s="4" t="n">
-        <v>0.9948</v>
+        <v>0.9913999999999999</v>
       </c>
       <c r="H138" s="4" t="n">
-        <v>0.9944</v>
+        <v>0.9926</v>
       </c>
       <c r="I138" s="4" t="n">
-        <v>0.9962</v>
+        <v>0.9919</v>
       </c>
       <c r="J138" s="4" t="n">
+        <v>0.9937</v>
+      </c>
+      <c r="K138" s="4" t="n">
+        <v>0.9941</v>
+      </c>
+      <c r="L138" s="4" t="n">
+        <v>0.9943</v>
+      </c>
+      <c r="M138" s="4" t="n">
         <v>0.9957</v>
-      </c>
-      <c r="K138" s="4" t="n">
-        <v>0.9954</v>
-      </c>
-      <c r="L138" s="4" t="n">
-        <v>0.9955000000000001</v>
-      </c>
-      <c r="M138" s="4" t="n">
-        <v>0.9959</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>HLMSEW01</t>
+          <t>HALAMRD1</t>
         </is>
       </c>
       <c r="B139" s="4" t="n">
@@ -15775,98 +15959,114 @@
         <v>0.9948</v>
       </c>
       <c r="H139" s="4" t="n">
-        <v>0.9921</v>
+        <v>0.9944</v>
       </c>
       <c r="I139" s="4" t="n">
-        <v>0.9935</v>
+        <v>0.9962</v>
       </c>
       <c r="J139" s="4" t="n">
-        <v>0.9956</v>
+        <v>0.9957</v>
       </c>
       <c r="K139" s="4" t="n">
+        <v>0.9954</v>
+      </c>
+      <c r="L139" s="4" t="n">
         <v>0.9955000000000001</v>
       </c>
-      <c r="L139" s="4" t="n">
-        <v>0.996</v>
-      </c>
       <c r="M139" s="4" t="n">
-        <v>0.9961</v>
+        <v>0.9959</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>AGLSOM</t>
+          <t>HLMSEW01</t>
         </is>
       </c>
       <c r="B140" s="4" t="n">
-        <v>0.9946</v>
+        <v>0.9931</v>
       </c>
       <c r="C140" s="4" t="n">
-        <v>0.9949</v>
+        <v>0.9932</v>
       </c>
       <c r="D140" s="4" t="n">
-        <v>0.9968</v>
+        <v>0.9962</v>
       </c>
       <c r="E140" s="4" t="n">
-        <v>0.9963</v>
+        <v>0.9956</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>0.9915</v>
+        <v>0.9944</v>
       </c>
       <c r="G140" s="4" t="n">
-        <v>0.9923999999999999</v>
+        <v>0.9948</v>
       </c>
       <c r="H140" s="4" t="n">
-        <v>0.9932</v>
+        <v>0.9921</v>
       </c>
       <c r="I140" s="4" t="n">
-        <v>0.9923999999999999</v>
+        <v>0.9935</v>
       </c>
       <c r="J140" s="4" t="n">
+        <v>0.9956</v>
+      </c>
+      <c r="K140" s="4" t="n">
+        <v>0.9955000000000001</v>
+      </c>
+      <c r="L140" s="4" t="n">
         <v>0.996</v>
       </c>
-      <c r="K140" s="4" t="n">
-        <v>0.9962</v>
-      </c>
-      <c r="L140" s="4" t="n">
-        <v>0.9965000000000001</v>
-      </c>
       <c r="M140" s="4" t="n">
-        <v>0.9968</v>
+        <v>0.9961</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>HASTING1</t>
-        </is>
-      </c>
-      <c r="B141" s="4" t="inlineStr"/>
-      <c r="C141" s="4" t="inlineStr"/>
-      <c r="D141" s="4" t="inlineStr"/>
-      <c r="E141" s="4" t="inlineStr"/>
-      <c r="F141" s="4" t="inlineStr"/>
-      <c r="G141" s="4" t="inlineStr"/>
-      <c r="H141" s="4" t="inlineStr"/>
-      <c r="I141" s="4" t="inlineStr"/>
+          <t>AGLSOM</t>
+        </is>
+      </c>
+      <c r="B141" s="4" t="n">
+        <v>0.9946</v>
+      </c>
+      <c r="C141" s="4" t="n">
+        <v>0.9949</v>
+      </c>
+      <c r="D141" s="4" t="n">
+        <v>0.9968</v>
+      </c>
+      <c r="E141" s="4" t="n">
+        <v>0.9963</v>
+      </c>
+      <c r="F141" s="4" t="n">
+        <v>0.9915</v>
+      </c>
+      <c r="G141" s="4" t="n">
+        <v>0.9923999999999999</v>
+      </c>
+      <c r="H141" s="4" t="n">
+        <v>0.9932</v>
+      </c>
+      <c r="I141" s="4" t="n">
+        <v>0.9923999999999999</v>
+      </c>
       <c r="J141" s="4" t="n">
         <v>0.996</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>0.9959</v>
+        <v>0.9962</v>
       </c>
       <c r="L141" s="4" t="n">
-        <v>0.9964</v>
+        <v>0.9965000000000001</v>
       </c>
       <c r="M141" s="4" t="n">
-        <v>0.9969</v>
+        <v>0.9968</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>HASTING2</t>
+          <t>HASTING3</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr"/>
@@ -15893,7 +16093,7 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>HASTING3</t>
+          <t>HASTING2</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr"/>
@@ -15920,7 +16120,7 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>MRNBESS1</t>
+          <t>HASTING1</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr"/>
@@ -15931,105 +16131,91 @@
       <c r="G144" s="4" t="inlineStr"/>
       <c r="H144" s="4" t="inlineStr"/>
       <c r="I144" s="4" t="inlineStr"/>
-      <c r="J144" s="4" t="inlineStr"/>
-      <c r="K144" s="4" t="inlineStr"/>
-      <c r="L144" s="4" t="inlineStr"/>
+      <c r="J144" s="4" t="n">
+        <v>0.996</v>
+      </c>
+      <c r="K144" s="4" t="n">
+        <v>0.9959</v>
+      </c>
+      <c r="L144" s="4" t="n">
+        <v>0.9964</v>
+      </c>
       <c r="M144" s="4" t="n">
-        <v>0.9971</v>
+        <v>0.9969</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>CHYTWF1</t>
+          <t>MRNBESS1</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr"/>
       <c r="C145" s="4" t="inlineStr"/>
       <c r="D145" s="4" t="inlineStr"/>
       <c r="E145" s="4" t="inlineStr"/>
-      <c r="F145" s="4" t="n">
-        <v>0.9944</v>
-      </c>
-      <c r="G145" s="4" t="n">
-        <v>0.9958</v>
-      </c>
-      <c r="H145" s="4" t="n">
-        <v>0.9959</v>
-      </c>
-      <c r="I145" s="4" t="n">
-        <v>0.9955000000000001</v>
-      </c>
-      <c r="J145" s="4" t="n">
-        <v>0.9974</v>
-      </c>
-      <c r="K145" s="4" t="n">
-        <v>0.9976</v>
-      </c>
+      <c r="F145" s="4" t="inlineStr"/>
+      <c r="G145" s="4" t="inlineStr"/>
+      <c r="H145" s="4" t="inlineStr"/>
+      <c r="I145" s="4" t="inlineStr"/>
+      <c r="J145" s="4" t="inlineStr"/>
+      <c r="K145" s="4" t="inlineStr"/>
       <c r="L145" s="4" t="n">
-        <v>0.998</v>
+        <v>0.9984</v>
       </c>
       <c r="M145" s="4" t="n">
-        <v>0.9977</v>
+        <v>0.9971</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>WOLLERT1</t>
-        </is>
-      </c>
-      <c r="B146" s="4" t="n">
-        <v>0.9987</v>
-      </c>
-      <c r="C146" s="4" t="n">
-        <v>0.9985000000000001</v>
-      </c>
-      <c r="D146" s="4" t="n">
+          <t>CHYTWF1</t>
+        </is>
+      </c>
+      <c r="B146" s="4" t="inlineStr"/>
+      <c r="C146" s="4" t="inlineStr"/>
+      <c r="D146" s="4" t="inlineStr"/>
+      <c r="E146" s="4" t="inlineStr"/>
+      <c r="F146" s="4" t="n">
+        <v>0.9944</v>
+      </c>
+      <c r="G146" s="4" t="n">
+        <v>0.9958</v>
+      </c>
+      <c r="H146" s="4" t="n">
+        <v>0.9959</v>
+      </c>
+      <c r="I146" s="4" t="n">
+        <v>0.9955000000000001</v>
+      </c>
+      <c r="J146" s="4" t="n">
+        <v>0.9974</v>
+      </c>
+      <c r="K146" s="4" t="n">
+        <v>0.9976</v>
+      </c>
+      <c r="L146" s="4" t="n">
         <v>0.998</v>
       </c>
-      <c r="E146" s="4" t="n">
-        <v>0.9979</v>
-      </c>
-      <c r="F146" s="4" t="n">
-        <v>0.9941</v>
-      </c>
-      <c r="G146" s="4" t="n">
-        <v>0.9954</v>
-      </c>
-      <c r="H146" s="4" t="n">
-        <v>0.9956</v>
-      </c>
-      <c r="I146" s="4" t="n">
-        <v>0.9951</v>
-      </c>
-      <c r="J146" s="4" t="n">
-        <v>0.9975000000000001</v>
-      </c>
-      <c r="K146" s="4" t="n">
+      <c r="M146" s="4" t="n">
         <v>0.9977</v>
-      </c>
-      <c r="L146" s="4" t="n">
-        <v>0.9981</v>
-      </c>
-      <c r="M146" s="4" t="n">
-        <v>0.9978</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>RUBICON</t>
+          <t>WOLLERT1</t>
         </is>
       </c>
       <c r="B147" s="4" t="n">
-        <v>1</v>
+        <v>0.9987</v>
       </c>
       <c r="C147" s="4" t="n">
-        <v>1</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="D147" s="4" t="n">
-        <v>1</v>
+        <v>0.998</v>
       </c>
       <c r="E147" s="4" t="n">
         <v>0.9979</v>
@@ -16062,17 +16248,17 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>EILDON3</t>
+          <t>RUBICON</t>
         </is>
       </c>
       <c r="B148" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C148" s="4" t="n">
-        <v>0.9985000000000001</v>
+        <v>1</v>
       </c>
       <c r="D148" s="4" t="n">
-        <v>0.998</v>
+        <v>1</v>
       </c>
       <c r="E148" s="4" t="n">
         <v>0.9979</v>
@@ -16105,93 +16291,93 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>CLAYTON</t>
+          <t>EILDON3</t>
         </is>
       </c>
       <c r="B149" s="4" t="n">
-        <v>0.997</v>
+        <v>1</v>
       </c>
       <c r="C149" s="4" t="n">
-        <v>0.9972</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="D149" s="4" t="n">
-        <v>0.9989</v>
+        <v>0.998</v>
       </c>
       <c r="E149" s="4" t="n">
-        <v>0.9986</v>
+        <v>0.9979</v>
       </c>
       <c r="F149" s="4" t="n">
-        <v>0.9987</v>
+        <v>0.9941</v>
       </c>
       <c r="G149" s="4" t="n">
-        <v>0.9984</v>
+        <v>0.9954</v>
       </c>
       <c r="H149" s="4" t="n">
-        <v>0.9957</v>
+        <v>0.9956</v>
       </c>
       <c r="I149" s="4" t="n">
-        <v>0.9972</v>
+        <v>0.9951</v>
       </c>
       <c r="J149" s="4" t="n">
-        <v>1.0001</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="K149" s="4" t="n">
+        <v>0.9977</v>
+      </c>
+      <c r="L149" s="4" t="n">
+        <v>0.9981</v>
+      </c>
+      <c r="M149" s="4" t="n">
         <v>0.9978</v>
-      </c>
-      <c r="L149" s="4" t="n">
-        <v>0.9977</v>
-      </c>
-      <c r="M149" s="4" t="n">
-        <v>0.9982</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>LNGS1</t>
+          <t>CLAYTON</t>
         </is>
       </c>
       <c r="B150" s="4" t="n">
-        <v>0.9985000000000001</v>
+        <v>0.997</v>
       </c>
       <c r="C150" s="4" t="n">
-        <v>1.001</v>
+        <v>0.9972</v>
       </c>
       <c r="D150" s="4" t="n">
-        <v>1.0081</v>
+        <v>0.9989</v>
       </c>
       <c r="E150" s="4" t="n">
-        <v>1.0018</v>
+        <v>0.9986</v>
       </c>
       <c r="F150" s="4" t="n">
-        <v>0.9944</v>
+        <v>0.9987</v>
       </c>
       <c r="G150" s="4" t="n">
-        <v>0.991</v>
+        <v>0.9984</v>
       </c>
       <c r="H150" s="4" t="n">
-        <v>0.9936</v>
+        <v>0.9957</v>
       </c>
       <c r="I150" s="4" t="n">
-        <v>0.9949</v>
+        <v>0.9972</v>
       </c>
       <c r="J150" s="4" t="n">
-        <v>0.9979</v>
+        <v>1.0001</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>0.9975000000000001</v>
+        <v>0.9978</v>
       </c>
       <c r="L150" s="4" t="n">
+        <v>0.9977</v>
+      </c>
+      <c r="M150" s="4" t="n">
         <v>0.9982</v>
-      </c>
-      <c r="M150" s="4" t="n">
-        <v>0.9999</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>LNGS2</t>
+          <t>LNGS1</t>
         </is>
       </c>
       <c r="B151" s="4" t="n">
@@ -16234,210 +16420,216 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>DG_VIC1</t>
+          <t>LNGS2</t>
         </is>
       </c>
       <c r="B152" s="4" t="n">
-        <v>1</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="C152" s="4" t="n">
-        <v>1</v>
+        <v>1.001</v>
       </c>
       <c r="D152" s="4" t="n">
-        <v>1</v>
+        <v>1.0081</v>
       </c>
       <c r="E152" s="4" t="n">
-        <v>1</v>
+        <v>1.0018</v>
       </c>
       <c r="F152" s="4" t="n">
-        <v>1</v>
+        <v>0.9944</v>
       </c>
       <c r="G152" s="4" t="n">
-        <v>1</v>
+        <v>0.991</v>
       </c>
       <c r="H152" s="4" t="n">
-        <v>1</v>
+        <v>0.9936</v>
       </c>
       <c r="I152" s="4" t="n">
-        <v>1</v>
+        <v>0.9949</v>
       </c>
       <c r="J152" s="4" t="n">
-        <v>1</v>
+        <v>0.9979</v>
       </c>
       <c r="K152" s="4" t="n">
-        <v>1</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="L152" s="4" t="n">
-        <v>1</v>
+        <v>0.9982</v>
       </c>
       <c r="M152" s="4" t="n">
-        <v>1</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>PORTWF</t>
+          <t>DG_VIC1</t>
         </is>
       </c>
       <c r="B153" s="4" t="n">
-        <v>1.0033</v>
+        <v>1</v>
       </c>
       <c r="C153" s="4" t="n">
-        <v>1.0135</v>
+        <v>1</v>
       </c>
       <c r="D153" s="4" t="n">
-        <v>1.0121</v>
+        <v>1</v>
       </c>
       <c r="E153" s="4" t="n">
-        <v>1.0058</v>
+        <v>1</v>
       </c>
       <c r="F153" s="4" t="n">
-        <v>0.9922</v>
+        <v>1</v>
       </c>
       <c r="G153" s="4" t="n">
-        <v>0.9913</v>
+        <v>1</v>
       </c>
       <c r="H153" s="4" t="n">
-        <v>0.9908</v>
+        <v>1</v>
       </c>
       <c r="I153" s="4" t="n">
-        <v>0.9945000000000001</v>
+        <v>1</v>
       </c>
       <c r="J153" s="4" t="n">
-        <v>0.9983</v>
+        <v>1</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>0.9936</v>
+        <v>1</v>
       </c>
       <c r="L153" s="4" t="n">
-        <v>1.0003</v>
+        <v>1</v>
       </c>
       <c r="M153" s="4" t="n">
-        <v>1.0003</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>CLOVER</t>
+          <t>PORTWF</t>
         </is>
       </c>
       <c r="B154" s="4" t="n">
-        <v>1.0285</v>
+        <v>1.0033</v>
       </c>
       <c r="C154" s="4" t="n">
-        <v>1.0285</v>
+        <v>1.0135</v>
       </c>
       <c r="D154" s="4" t="n">
-        <v>1.0285</v>
+        <v>1.0121</v>
       </c>
       <c r="E154" s="4" t="n">
-        <v>0.9882</v>
+        <v>1.0058</v>
       </c>
       <c r="F154" s="4" t="n">
-        <v>1.0192</v>
+        <v>0.9922</v>
       </c>
       <c r="G154" s="4" t="n">
-        <v>1.0235</v>
+        <v>0.9913</v>
       </c>
       <c r="H154" s="4" t="n">
-        <v>1.0292</v>
+        <v>0.9908</v>
       </c>
       <c r="I154" s="4" t="n">
-        <v>1.019</v>
+        <v>0.9945000000000001</v>
       </c>
       <c r="J154" s="4" t="n">
-        <v>1.0335</v>
+        <v>0.9983</v>
       </c>
       <c r="K154" s="4" t="n">
-        <v>1.0284</v>
+        <v>0.9936</v>
       </c>
       <c r="L154" s="4" t="n">
-        <v>1.0191</v>
+        <v>1.0003</v>
       </c>
       <c r="M154" s="4" t="n">
-        <v>1.0012</v>
+        <v>1.0003</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>BROOKLYN</t>
+          <t>CLOVER</t>
         </is>
       </c>
       <c r="B155" s="4" t="n">
-        <v>1.0053</v>
+        <v>1.0285</v>
       </c>
       <c r="C155" s="4" t="n">
-        <v>1.0054</v>
+        <v>1.0285</v>
       </c>
       <c r="D155" s="4" t="n">
-        <v>1.0069</v>
+        <v>1.0285</v>
       </c>
       <c r="E155" s="4" t="n">
-        <v>1.0042</v>
+        <v>0.9882</v>
       </c>
       <c r="F155" s="4" t="n">
-        <v>1.0027</v>
+        <v>1.0192</v>
       </c>
       <c r="G155" s="4" t="n">
-        <v>1.0037</v>
+        <v>1.0235</v>
       </c>
       <c r="H155" s="4" t="n">
-        <v>1.0062</v>
+        <v>1.0292</v>
       </c>
       <c r="I155" s="4" t="n">
-        <v>1.0066</v>
+        <v>1.019</v>
       </c>
       <c r="J155" s="4" t="n">
-        <v>1.0032</v>
+        <v>1.0335</v>
       </c>
       <c r="K155" s="4" t="n">
-        <v>1.0053</v>
+        <v>1.0284</v>
       </c>
       <c r="L155" s="4" t="n">
-        <v>1.0062</v>
+        <v>1.0191</v>
       </c>
       <c r="M155" s="4" t="n">
-        <v>1.0029</v>
+        <v>1.0012</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>YAWWF1</t>
-        </is>
-      </c>
-      <c r="B156" s="4" t="inlineStr"/>
-      <c r="C156" s="4" t="inlineStr"/>
-      <c r="D156" s="4" t="inlineStr"/>
+          <t>BROOKLYN</t>
+        </is>
+      </c>
+      <c r="B156" s="4" t="n">
+        <v>1.0053</v>
+      </c>
+      <c r="C156" s="4" t="n">
+        <v>1.0054</v>
+      </c>
+      <c r="D156" s="4" t="n">
+        <v>1.0069</v>
+      </c>
       <c r="E156" s="4" t="n">
-        <v>1.0136</v>
+        <v>1.0042</v>
       </c>
       <c r="F156" s="4" t="n">
-        <v>1.0012</v>
+        <v>1.0027</v>
       </c>
       <c r="G156" s="4" t="n">
-        <v>1.0022</v>
+        <v>1.0037</v>
       </c>
       <c r="H156" s="4" t="n">
-        <v>1.0101</v>
+        <v>1.0062</v>
       </c>
       <c r="I156" s="4" t="n">
-        <v>1.0084</v>
+        <v>1.0066</v>
       </c>
       <c r="J156" s="4" t="n">
-        <v>1.0165</v>
+        <v>1.0032</v>
       </c>
       <c r="K156" s="4" t="n">
-        <v>1.0072</v>
+        <v>1.0053</v>
       </c>
       <c r="L156" s="4" t="n">
-        <v>1.0166</v>
+        <v>1.0062</v>
       </c>
       <c r="M156" s="4" t="n">
-        <v>1.0031</v>
+        <v>1.0029</v>
       </c>
     </row>
     <row r="157">
@@ -16486,50 +16678,44 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>YWNGAHYD</t>
-        </is>
-      </c>
-      <c r="B158" s="4" t="n">
-        <v>1.0639</v>
-      </c>
-      <c r="C158" s="4" t="n">
-        <v>1.0502</v>
-      </c>
-      <c r="D158" s="4" t="n">
-        <v>1.0037</v>
-      </c>
+          <t>YAWWF1</t>
+        </is>
+      </c>
+      <c r="B158" s="4" t="inlineStr"/>
+      <c r="C158" s="4" t="inlineStr"/>
+      <c r="D158" s="4" t="inlineStr"/>
       <c r="E158" s="4" t="n">
-        <v>1.0002</v>
+        <v>1.0136</v>
       </c>
       <c r="F158" s="4" t="n">
-        <v>1.0203</v>
+        <v>1.0012</v>
       </c>
       <c r="G158" s="4" t="n">
-        <v>1.0289</v>
+        <v>1.0022</v>
       </c>
       <c r="H158" s="4" t="n">
-        <v>1.0346</v>
+        <v>1.0101</v>
       </c>
       <c r="I158" s="4" t="n">
-        <v>1.0313</v>
+        <v>1.0084</v>
       </c>
       <c r="J158" s="4" t="n">
-        <v>1.041</v>
+        <v>1.0165</v>
       </c>
       <c r="K158" s="4" t="n">
-        <v>1.0372</v>
+        <v>1.0072</v>
       </c>
       <c r="L158" s="4" t="n">
-        <v>1.0315</v>
+        <v>1.0166</v>
       </c>
       <c r="M158" s="4" t="n">
-        <v>1.0142</v>
+        <v>1.0031</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>TATURA01</t>
+          <t>SHEP1</t>
         </is>
       </c>
       <c r="B159" s="4" t="n">
@@ -16572,7 +16758,7 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>SHEP1</t>
+          <t>YWNGAHYD</t>
         </is>
       </c>
       <c r="B160" s="4" t="n">
@@ -16615,75 +16801,97 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>SNOWYGJP</t>
+          <t>TATURA01</t>
         </is>
       </c>
       <c r="B161" s="4" t="n">
-        <v>1.138</v>
+        <v>1.0639</v>
       </c>
       <c r="C161" s="4" t="n">
-        <v>1.1115</v>
+        <v>1.0502</v>
       </c>
       <c r="D161" s="4" t="n">
-        <v>1.0474</v>
+        <v>1.0037</v>
       </c>
       <c r="E161" s="4" t="n">
-        <v>1.0124</v>
+        <v>1.0002</v>
       </c>
       <c r="F161" s="4" t="n">
-        <v>1.0211</v>
+        <v>1.0203</v>
       </c>
       <c r="G161" s="4" t="n">
-        <v>1.1231</v>
+        <v>1.0289</v>
       </c>
       <c r="H161" s="4" t="n">
-        <v>1.135</v>
+        <v>1.0346</v>
       </c>
       <c r="I161" s="4" t="n">
-        <v>1.0914</v>
+        <v>1.0313</v>
       </c>
       <c r="J161" s="4" t="n">
-        <v>1.0783</v>
+        <v>1.041</v>
       </c>
       <c r="K161" s="4" t="n">
-        <v>1.093</v>
+        <v>1.0372</v>
       </c>
       <c r="L161" s="4" t="n">
-        <v>1.0606</v>
+        <v>1.0315</v>
       </c>
       <c r="M161" s="4" t="n">
-        <v>1.0587</v>
+        <v>1.0142</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>MORNL1</t>
+          <t>SNOWYGJP</t>
         </is>
       </c>
       <c r="B162" s="4" t="n">
-        <v>0.9799</v>
-      </c>
-      <c r="C162" s="4" t="inlineStr"/>
-      <c r="D162" s="4" t="inlineStr"/>
-      <c r="E162" s="4" t="inlineStr"/>
-      <c r="F162" s="4" t="inlineStr"/>
-      <c r="G162" s="4" t="inlineStr"/>
-      <c r="H162" s="4" t="inlineStr"/>
-      <c r="I162" s="4" t="inlineStr"/>
-      <c r="J162" s="4" t="inlineStr"/>
-      <c r="K162" s="4" t="inlineStr"/>
-      <c r="L162" s="4" t="inlineStr"/>
-      <c r="M162" s="4" t="inlineStr"/>
+        <v>1.138</v>
+      </c>
+      <c r="C162" s="4" t="n">
+        <v>1.1115</v>
+      </c>
+      <c r="D162" s="4" t="n">
+        <v>1.0474</v>
+      </c>
+      <c r="E162" s="4" t="n">
+        <v>1.0124</v>
+      </c>
+      <c r="F162" s="4" t="n">
+        <v>1.0211</v>
+      </c>
+      <c r="G162" s="4" t="n">
+        <v>1.1231</v>
+      </c>
+      <c r="H162" s="4" t="n">
+        <v>1.135</v>
+      </c>
+      <c r="I162" s="4" t="n">
+        <v>1.0914</v>
+      </c>
+      <c r="J162" s="4" t="n">
+        <v>1.0783</v>
+      </c>
+      <c r="K162" s="4" t="n">
+        <v>1.093</v>
+      </c>
+      <c r="L162" s="4" t="n">
+        <v>1.0606</v>
+      </c>
+      <c r="M162" s="4" t="n">
+        <v>1.0587</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>APS</t>
+          <t>MORNL1</t>
         </is>
       </c>
       <c r="B163" s="4" t="n">
-        <v>0.9915</v>
+        <v>0.9799</v>
       </c>
       <c r="C163" s="4" t="inlineStr"/>
       <c r="D163" s="4" t="inlineStr"/>
@@ -16700,11 +16908,11 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>MOR2</t>
+          <t>APS</t>
         </is>
       </c>
       <c r="B164" s="4" t="n">
-        <v>0.9732</v>
+        <v>0.9915</v>
       </c>
       <c r="C164" s="4" t="inlineStr"/>
       <c r="D164" s="4" t="inlineStr"/>
@@ -16763,15 +16971,13 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>HWPS6</t>
+          <t>MOR2</t>
         </is>
       </c>
       <c r="B167" s="4" t="n">
-        <v>0.9723000000000001</v>
-      </c>
-      <c r="C167" s="4" t="n">
-        <v>0.9701</v>
-      </c>
+        <v>0.9732</v>
+      </c>
+      <c r="C167" s="4" t="inlineStr"/>
       <c r="D167" s="4" t="inlineStr"/>
       <c r="E167" s="4" t="inlineStr"/>
       <c r="F167" s="4" t="inlineStr"/>
@@ -16786,7 +16992,7 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>HWPS2</t>
+          <t>HWPS8</t>
         </is>
       </c>
       <c r="B168" s="4" t="n">
@@ -16809,7 +17015,7 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>HWPS1</t>
+          <t>HWPS7</t>
         </is>
       </c>
       <c r="B169" s="4" t="n">
@@ -16832,7 +17038,7 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>HWPNL1</t>
+          <t>HWPS6</t>
         </is>
       </c>
       <c r="B170" s="4" t="n">
@@ -16855,7 +17061,7 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>HWPS7</t>
+          <t>HWPS5</t>
         </is>
       </c>
       <c r="B171" s="4" t="n">
@@ -16878,7 +17084,7 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>HWPS5</t>
+          <t>HWPS4</t>
         </is>
       </c>
       <c r="B172" s="4" t="n">
@@ -16901,7 +17107,7 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>HWPS4</t>
+          <t>HWPS3</t>
         </is>
       </c>
       <c r="B173" s="4" t="n">
@@ -16924,7 +17130,7 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>HWPS8</t>
+          <t>HWPS2</t>
         </is>
       </c>
       <c r="B174" s="4" t="n">
@@ -16947,7 +17153,7 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>HWPS3</t>
+          <t>HWPS1</t>
         </is>
       </c>
       <c r="B175" s="4" t="n">
@@ -16970,18 +17176,16 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>MORNW</t>
+          <t>HWPNL1</t>
         </is>
       </c>
       <c r="B176" s="4" t="n">
-        <v>0.9923999999999999</v>
+        <v>0.9723000000000001</v>
       </c>
       <c r="C176" s="4" t="n">
-        <v>0.9925</v>
-      </c>
-      <c r="D176" s="4" t="n">
-        <v>0.9963</v>
-      </c>
+        <v>0.9701</v>
+      </c>
+      <c r="D176" s="4" t="inlineStr"/>
       <c r="E176" s="4" t="inlineStr"/>
       <c r="F176" s="4" t="inlineStr"/>
       <c r="G176" s="4" t="inlineStr"/>
@@ -17020,33 +17224,23 @@
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>CORIO1</t>
+          <t>MORNW</t>
         </is>
       </c>
       <c r="B178" s="4" t="n">
-        <v>0.9987</v>
+        <v>0.9923999999999999</v>
       </c>
       <c r="C178" s="4" t="n">
-        <v>1.0048</v>
+        <v>0.9925</v>
       </c>
       <c r="D178" s="4" t="n">
-        <v>1.0055</v>
-      </c>
-      <c r="E178" s="4" t="n">
-        <v>1.0002</v>
-      </c>
-      <c r="F178" s="4" t="n">
-        <v>0.9908</v>
-      </c>
-      <c r="G178" s="4" t="n">
-        <v>0.9913999999999999</v>
-      </c>
-      <c r="H178" s="4" t="n">
-        <v>0.9918</v>
-      </c>
-      <c r="I178" s="4" t="n">
-        <v>0.9933</v>
-      </c>
+        <v>0.9963</v>
+      </c>
+      <c r="E178" s="4" t="inlineStr"/>
+      <c r="F178" s="4" t="inlineStr"/>
+      <c r="G178" s="4" t="inlineStr"/>
+      <c r="H178" s="4" t="inlineStr"/>
+      <c r="I178" s="4" t="inlineStr"/>
       <c r="J178" s="4" t="inlineStr"/>
       <c r="K178" s="4" t="inlineStr"/>
       <c r="L178" s="4" t="inlineStr"/>
@@ -17055,32 +17249,32 @@
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>BERWICK</t>
+          <t>CORIO1</t>
         </is>
       </c>
       <c r="B179" s="4" t="n">
-        <v>0.9923</v>
+        <v>0.9987</v>
       </c>
       <c r="C179" s="4" t="n">
-        <v>0.9923</v>
+        <v>1.0048</v>
       </c>
       <c r="D179" s="4" t="n">
-        <v>0.9923</v>
+        <v>1.0055</v>
       </c>
       <c r="E179" s="4" t="n">
-        <v>0.9923</v>
+        <v>1.0002</v>
       </c>
       <c r="F179" s="4" t="n">
-        <v>0.9923</v>
+        <v>0.9908</v>
       </c>
       <c r="G179" s="4" t="n">
-        <v>0.9923</v>
+        <v>0.9913999999999999</v>
       </c>
       <c r="H179" s="4" t="n">
-        <v>0.9923</v>
+        <v>0.9918</v>
       </c>
       <c r="I179" s="4" t="n">
-        <v>0.9923</v>
+        <v>0.9933</v>
       </c>
       <c r="J179" s="4" t="inlineStr"/>
       <c r="K179" s="4" t="inlineStr"/>
@@ -17090,36 +17284,34 @@
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>SVALE1</t>
+          <t>BERWICK</t>
         </is>
       </c>
       <c r="B180" s="4" t="n">
-        <v>0.997</v>
+        <v>0.9923</v>
       </c>
       <c r="C180" s="4" t="n">
-        <v>0.9972</v>
+        <v>0.9923</v>
       </c>
       <c r="D180" s="4" t="n">
-        <v>0.9989</v>
+        <v>0.9923</v>
       </c>
       <c r="E180" s="4" t="n">
-        <v>0.9986</v>
+        <v>0.9923</v>
       </c>
       <c r="F180" s="4" t="n">
-        <v>0.9987</v>
+        <v>0.9923</v>
       </c>
       <c r="G180" s="4" t="n">
-        <v>0.9984</v>
+        <v>0.9923</v>
       </c>
       <c r="H180" s="4" t="n">
-        <v>0.9957</v>
+        <v>0.9923</v>
       </c>
       <c r="I180" s="4" t="n">
-        <v>0.9972</v>
-      </c>
-      <c r="J180" s="4" t="n">
-        <v>1.0001</v>
-      </c>
+        <v>0.9923</v>
+      </c>
+      <c r="J180" s="4" t="inlineStr"/>
       <c r="K180" s="4" t="inlineStr"/>
       <c r="L180" s="4" t="inlineStr"/>
       <c r="M180" s="4" t="inlineStr"/>
@@ -17164,40 +17356,44 @@
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>GANNBG1</t>
-        </is>
-      </c>
-      <c r="B182" s="4" t="inlineStr"/>
-      <c r="C182" s="4" t="inlineStr"/>
-      <c r="D182" s="4" t="inlineStr"/>
+          <t>SVALE1</t>
+        </is>
+      </c>
+      <c r="B182" s="4" t="n">
+        <v>0.997</v>
+      </c>
+      <c r="C182" s="4" t="n">
+        <v>0.9972</v>
+      </c>
+      <c r="D182" s="4" t="n">
+        <v>0.9989</v>
+      </c>
       <c r="E182" s="4" t="n">
-        <v>1.007</v>
+        <v>0.9986</v>
       </c>
       <c r="F182" s="4" t="n">
-        <v>0.9643</v>
+        <v>0.9987</v>
       </c>
       <c r="G182" s="4" t="n">
-        <v>0.9792999999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="H182" s="4" t="n">
-        <v>0.9772999999999999</v>
+        <v>0.9957</v>
       </c>
       <c r="I182" s="4" t="n">
-        <v>1.0026</v>
+        <v>0.9972</v>
       </c>
       <c r="J182" s="4" t="n">
-        <v>1.029</v>
-      </c>
-      <c r="K182" s="4" t="n">
-        <v>1.0155</v>
-      </c>
+        <v>1.0001</v>
+      </c>
+      <c r="K182" s="4" t="inlineStr"/>
       <c r="L182" s="4" t="inlineStr"/>
       <c r="M182" s="4" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>FNWF1</t>
+          <t>VBBG1</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr"/>
@@ -17205,20 +17401,18 @@
       <c r="D183" s="4" t="inlineStr"/>
       <c r="E183" s="4" t="inlineStr"/>
       <c r="F183" s="4" t="inlineStr"/>
-      <c r="G183" s="4" t="n">
-        <v>1.0079</v>
-      </c>
+      <c r="G183" s="4" t="inlineStr"/>
       <c r="H183" s="4" t="n">
-        <v>1.0035</v>
+        <v>0.982</v>
       </c>
       <c r="I183" s="4" t="n">
-        <v>0.9972</v>
+        <v>0.9848</v>
       </c>
       <c r="J183" s="4" t="n">
-        <v>0.9933</v>
+        <v>0.9885</v>
       </c>
       <c r="K183" s="4" t="n">
-        <v>0.9993</v>
+        <v>0.9879</v>
       </c>
       <c r="L183" s="4" t="inlineStr"/>
       <c r="M183" s="4" t="inlineStr"/>
@@ -17226,26 +17420,32 @@
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>VBBG1</t>
+          <t>GANNBG1</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr"/>
       <c r="C184" s="4" t="inlineStr"/>
       <c r="D184" s="4" t="inlineStr"/>
-      <c r="E184" s="4" t="inlineStr"/>
-      <c r="F184" s="4" t="inlineStr"/>
-      <c r="G184" s="4" t="inlineStr"/>
+      <c r="E184" s="4" t="n">
+        <v>1.007</v>
+      </c>
+      <c r="F184" s="4" t="n">
+        <v>0.9643</v>
+      </c>
+      <c r="G184" s="4" t="n">
+        <v>0.9792999999999999</v>
+      </c>
       <c r="H184" s="4" t="n">
-        <v>0.982</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="I184" s="4" t="n">
-        <v>0.9848</v>
+        <v>1.0026</v>
       </c>
       <c r="J184" s="4" t="n">
-        <v>0.9885</v>
+        <v>1.029</v>
       </c>
       <c r="K184" s="4" t="n">
-        <v>0.9879</v>
+        <v>1.0155</v>
       </c>
       <c r="L184" s="4" t="inlineStr"/>
       <c r="M184" s="4" t="inlineStr"/>
@@ -17253,7 +17453,7 @@
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>HBESSG1</t>
+          <t>BULBESG1</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr"/>
@@ -17262,15 +17462,17 @@
       <c r="E185" s="4" t="inlineStr"/>
       <c r="F185" s="4" t="inlineStr"/>
       <c r="G185" s="4" t="inlineStr"/>
-      <c r="H185" s="4" t="inlineStr"/>
+      <c r="H185" s="4" t="n">
+        <v>0.8949</v>
+      </c>
       <c r="I185" s="4" t="n">
-        <v>0.9785</v>
+        <v>0.8839</v>
       </c>
       <c r="J185" s="4" t="n">
-        <v>0.9789</v>
+        <v>0.8821</v>
       </c>
       <c r="K185" s="4" t="n">
-        <v>0.9804</v>
+        <v>0.8733</v>
       </c>
       <c r="L185" s="4" t="inlineStr"/>
       <c r="M185" s="4" t="inlineStr"/>
@@ -17278,32 +17480,24 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>BALBG1</t>
+          <t>HBESSG1</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr"/>
       <c r="C186" s="4" t="inlineStr"/>
       <c r="D186" s="4" t="inlineStr"/>
-      <c r="E186" s="4" t="n">
-        <v>0.9948</v>
-      </c>
-      <c r="F186" s="4" t="n">
-        <v>0.9634</v>
-      </c>
-      <c r="G186" s="4" t="n">
-        <v>0.9643</v>
-      </c>
-      <c r="H186" s="4" t="n">
-        <v>0.9573</v>
-      </c>
+      <c r="E186" s="4" t="inlineStr"/>
+      <c r="F186" s="4" t="inlineStr"/>
+      <c r="G186" s="4" t="inlineStr"/>
+      <c r="H186" s="4" t="inlineStr"/>
       <c r="I186" s="4" t="n">
-        <v>0.9663</v>
+        <v>0.9785</v>
       </c>
       <c r="J186" s="4" t="n">
-        <v>0.9756</v>
+        <v>0.9789</v>
       </c>
       <c r="K186" s="4" t="n">
-        <v>0.9713000000000001</v>
+        <v>0.9804</v>
       </c>
       <c r="L186" s="4" t="inlineStr"/>
       <c r="M186" s="4" t="inlineStr"/>
@@ -17311,24 +17505,32 @@
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>PIBESSG1</t>
+          <t>BALBG1</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr"/>
       <c r="C187" s="4" t="inlineStr"/>
       <c r="D187" s="4" t="inlineStr"/>
-      <c r="E187" s="4" t="inlineStr"/>
-      <c r="F187" s="4" t="inlineStr"/>
-      <c r="G187" s="4" t="inlineStr"/>
-      <c r="H187" s="4" t="inlineStr"/>
+      <c r="E187" s="4" t="n">
+        <v>0.9948</v>
+      </c>
+      <c r="F187" s="4" t="n">
+        <v>0.9634</v>
+      </c>
+      <c r="G187" s="4" t="n">
+        <v>0.9643</v>
+      </c>
+      <c r="H187" s="4" t="n">
+        <v>0.9573</v>
+      </c>
       <c r="I187" s="4" t="n">
-        <v>0.9977</v>
+        <v>0.9663</v>
       </c>
       <c r="J187" s="4" t="n">
-        <v>0.9825</v>
+        <v>0.9756</v>
       </c>
       <c r="K187" s="4" t="n">
-        <v>0.9848</v>
+        <v>0.9713000000000001</v>
       </c>
       <c r="L187" s="4" t="inlineStr"/>
       <c r="M187" s="4" t="inlineStr"/>
@@ -17336,7 +17538,7 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>BULBESG1</t>
+          <t>PIBESSG1</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr"/>
@@ -17345,17 +17547,15 @@
       <c r="E188" s="4" t="inlineStr"/>
       <c r="F188" s="4" t="inlineStr"/>
       <c r="G188" s="4" t="inlineStr"/>
-      <c r="H188" s="4" t="n">
-        <v>0.8949</v>
-      </c>
+      <c r="H188" s="4" t="inlineStr"/>
       <c r="I188" s="4" t="n">
-        <v>0.8839</v>
+        <v>0.9977</v>
       </c>
       <c r="J188" s="4" t="n">
-        <v>0.8821</v>
+        <v>0.9825</v>
       </c>
       <c r="K188" s="4" t="n">
-        <v>0.8733</v>
+        <v>0.9848</v>
       </c>
       <c r="L188" s="4" t="inlineStr"/>
       <c r="M188" s="4" t="inlineStr"/>
@@ -17363,48 +17563,36 @@
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>CHPSTWF1</t>
-        </is>
-      </c>
-      <c r="B189" s="4" t="n">
-        <v>1.0207</v>
-      </c>
-      <c r="C189" s="4" t="n">
-        <v>1.0209</v>
-      </c>
-      <c r="D189" s="4" t="n">
-        <v>1.016</v>
-      </c>
-      <c r="E189" s="4" t="n">
-        <v>1.0016</v>
-      </c>
-      <c r="F189" s="4" t="n">
-        <v>0.9716</v>
-      </c>
+          <t>FNWF1</t>
+        </is>
+      </c>
+      <c r="B189" s="4" t="inlineStr"/>
+      <c r="C189" s="4" t="inlineStr"/>
+      <c r="D189" s="4" t="inlineStr"/>
+      <c r="E189" s="4" t="inlineStr"/>
+      <c r="F189" s="4" t="inlineStr"/>
       <c r="G189" s="4" t="n">
-        <v>0.9711</v>
+        <v>1.0079</v>
       </c>
       <c r="H189" s="4" t="n">
-        <v>0.9699</v>
+        <v>1.0035</v>
       </c>
       <c r="I189" s="4" t="n">
-        <v>0.9699</v>
+        <v>0.9972</v>
       </c>
       <c r="J189" s="4" t="n">
-        <v>0.9759</v>
+        <v>0.9933</v>
       </c>
       <c r="K189" s="4" t="n">
-        <v>0.9718</v>
-      </c>
-      <c r="L189" s="4" t="n">
-        <v>0.9825</v>
-      </c>
+        <v>0.9993</v>
+      </c>
+      <c r="L189" s="4" t="inlineStr"/>
       <c r="M189" s="4" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>BBASEHOS</t>
+          <t>CHPSTWF1</t>
         </is>
       </c>
       <c r="B190" s="4" t="n">
@@ -17442,8 +17630,49 @@
       </c>
       <c r="M190" s="4" t="inlineStr"/>
     </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>BBASEHOS</t>
+        </is>
+      </c>
+      <c r="B191" s="4" t="n">
+        <v>1.0207</v>
+      </c>
+      <c r="C191" s="4" t="n">
+        <v>1.0209</v>
+      </c>
+      <c r="D191" s="4" t="n">
+        <v>1.016</v>
+      </c>
+      <c r="E191" s="4" t="n">
+        <v>1.0016</v>
+      </c>
+      <c r="F191" s="4" t="n">
+        <v>0.9716</v>
+      </c>
+      <c r="G191" s="4" t="n">
+        <v>0.9711</v>
+      </c>
+      <c r="H191" s="4" t="n">
+        <v>0.9699</v>
+      </c>
+      <c r="I191" s="4" t="n">
+        <v>0.9699</v>
+      </c>
+      <c r="J191" s="4" t="n">
+        <v>0.9759</v>
+      </c>
+      <c r="K191" s="4" t="n">
+        <v>0.9718</v>
+      </c>
+      <c r="L191" s="4" t="n">
+        <v>0.9825</v>
+      </c>
+      <c r="M191" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B190">
+  <conditionalFormatting sqref="B2:B191">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -17455,7 +17684,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C190">
+  <conditionalFormatting sqref="C2:C191">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -17467,7 +17696,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D190">
+  <conditionalFormatting sqref="D2:D191">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -17479,7 +17708,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E190">
+  <conditionalFormatting sqref="E2:E191">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -17491,7 +17720,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F190">
+  <conditionalFormatting sqref="F2:F191">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -17503,7 +17732,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G190">
+  <conditionalFormatting sqref="G2:G191">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -17515,7 +17744,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H190">
+  <conditionalFormatting sqref="H2:H191">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -17527,7 +17756,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I190">
+  <conditionalFormatting sqref="I2:I191">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -17539,7 +17768,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J190">
+  <conditionalFormatting sqref="J2:J191">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -17551,7 +17780,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K190">
+  <conditionalFormatting sqref="K2:K191">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
@@ -17563,7 +17792,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L190">
+  <conditionalFormatting sqref="L2:L191">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
@@ -17575,7 +17804,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M190">
+  <conditionalFormatting sqref="M2:M191">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
@@ -17714,7 +17943,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>MURRAY</t>
+          <t>MURAYNL2</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -17743,7 +17972,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>MURAYNL2</t>
+          <t>MURAYNL1</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -17772,7 +18001,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>MURAYNL1</t>
+          <t>MURRAY</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -17801,12 +18030,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>NUMURSF1</t>
+          <t>WUNUSF1</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Numurkah Solar Farm</t>
+          <t>Wunghnu Solar Farm</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -17830,12 +18059,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>WUNUSF1</t>
+          <t>NUMURSF1</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Wunghnu Solar Farm</t>
+          <t>Numurkah Solar Farm</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -17975,12 +18204,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>GLRWNSF1</t>
+          <t>WINTSF1</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Glenrowan West Solar Farm</t>
+          <t>Winton Solar Farm</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -18004,12 +18233,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>WINTSF1</t>
+          <t>GLRWNSF1</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Winton Solar Farm</t>
+          <t>Glenrowan West Solar Farm</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -18091,7 +18320,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>WKIEWA2</t>
+          <t>WKIEWA1</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -18120,7 +18349,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>WKIEWA1</t>
+          <t>WKIEWA2</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -18149,17 +18378,17 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>SHEP1</t>
+          <t>YWNGAHYD</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Shepparton Wastewater Treatment Facility</t>
+          <t>Yarrawonga Hydro Power Station</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Other Renewable</t>
+          <t>Hydro</t>
         </is>
       </c>
       <c r="D20" s="4" t="n">
@@ -18178,17 +18407,17 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>YWNGAHYD</t>
+          <t>TATURA01</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Yarrawonga Hydro Power Station</t>
+          <t>Tatura Biomass Generator</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Hydro</t>
+          <t>Other Renewable</t>
         </is>
       </c>
       <c r="D21" s="4" t="n">
@@ -18207,12 +18436,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>TATURA01</t>
+          <t>SHEP1</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Tatura Biomass Generator</t>
+          <t>Shepparton Wastewater Treatment Facility</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -18396,65 +18625,65 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>CRWARP1</t>
+          <t>KESSB1</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Carwarp Solar Farm</t>
+          <t>Koorangie Energy Storage System</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.8963</v>
+        <v>0.9794</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.8883</v>
+        <v>0.9704</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.008</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.9</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>BDL02</t>
+          <t>CRWARP1</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Bairnsdale Power Station</t>
+          <t>Carwarp Solar Farm</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.9893</v>
+        <v>0.8963</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.9816</v>
+        <v>0.8883</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.0077</v>
+        <v>0.008</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>BDL01</t>
+          <t>BDL02</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -18483,70 +18712,70 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>WONWP</t>
+          <t>BDL01</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Wonthaggi Wind Farm</t>
+          <t>Bairnsdale Power Station</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.992</v>
+        <v>0.9893</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.9862</v>
+        <v>0.9816</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.0058</v>
+        <v>0.0077</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.59</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>BALDHWF1</t>
+          <t>GANNB1</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Bald Hills Wind Farm</t>
+          <t>Gannawarra Energy Storage System</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.992</v>
+        <v>0.9919</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.9862</v>
+        <v>0.9857</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.0058</v>
+        <v>0.0062</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.59</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>TOORAWF</t>
+          <t>BALDHWF1</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Toora Wind Farm</t>
+          <t>Bald Hills Wind Farm</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -18570,17 +18799,17 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>GLENMAG1</t>
+          <t>WONWP</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Glenmaggie Hydro Power Station</t>
+          <t>Wonthaggi Wind Farm</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Hydro</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D37" s="4" t="n">
@@ -18599,12 +18828,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>LONGFORD</t>
+          <t>TGNSS1</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>LONGFORD PLANT</t>
+          <t>Traralgon Network Support Station</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -18628,12 +18857,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>TGNSS1</t>
+          <t>LONGFORD</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Traralgon Network Support Station</t>
+          <t>LONGFORD PLANT</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -18657,99 +18886,99 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>JLA01</t>
+          <t>TOORAWF</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Jeeralang "A" Power Station</t>
+          <t>Toora Wind Farm</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D40" s="4" t="n">
-        <v>0.9823</v>
+        <v>0.992</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>0.9768</v>
+        <v>0.9862</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>0.0055</v>
+        <v>0.0058</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>JLA02</t>
+          <t>PIBESS1</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Jeeralang "A" Power Station</t>
+          <t>Phillip Island BESS</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D41" s="4" t="n">
-        <v>0.9823</v>
+        <v>0.992</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>0.9768</v>
+        <v>0.9862</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>0.0055</v>
+        <v>0.0058</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>JLA03</t>
+          <t>GLENMAG1</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Jeeralang "A" Power Station</t>
+          <t>Glenmaggie Hydro Power Station</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Hydro</t>
         </is>
       </c>
       <c r="D42" s="4" t="n">
-        <v>0.9823</v>
+        <v>0.992</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>0.9768</v>
+        <v>0.9862</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>0.0055</v>
+        <v>0.0058</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>JLA04</t>
+          <t>JLB03</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Jeeralang "A" Power Station</t>
+          <t>Jeeralang "B" Power Station</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -18802,7 +19031,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>JLB03</t>
+          <t>JLB01</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -18831,12 +19060,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>JLB01</t>
+          <t>JLA04</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Jeeralang "B" Power Station</t>
+          <t>Jeeralang "A" Power Station</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">

--- a/outputs/VIC_mlf.xlsx
+++ b/outputs/VIC_mlf.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MLF Table" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Biggest Movers" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="MLF Table" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Biggest Movers" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -666,12 +666,12 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>MUWAWF2</t>
+          <t>MUWAWF1</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Murra Warra Wind Farm Stage 2</t>
+          <t>Murra Warra Wind Farm</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -680,14 +680,20 @@
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>209</v>
+        <v>231.8</v>
       </c>
       <c r="E3" s="5" t="inlineStr"/>
       <c r="F3" s="5" t="inlineStr"/>
       <c r="G3" s="5" t="inlineStr"/>
-      <c r="H3" s="5" t="inlineStr"/>
-      <c r="I3" s="5" t="inlineStr"/>
-      <c r="J3" s="5" t="inlineStr"/>
+      <c r="H3" s="5" t="n">
+        <v>0.9549</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>0.8885</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>0.8885</v>
+      </c>
       <c r="K3" s="5" t="n">
         <v>0.8883</v>
       </c>
@@ -721,12 +727,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>MUWAWF1</t>
+          <t>MUWAWF2</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Murra Warra Wind Farm</t>
+          <t>Murra Warra Wind Farm Stage 2</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -735,20 +741,14 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>231.8</v>
+        <v>209</v>
       </c>
       <c r="E4" s="5" t="inlineStr"/>
       <c r="F4" s="5" t="inlineStr"/>
       <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="n">
-        <v>0.9549</v>
-      </c>
-      <c r="I4" s="5" t="n">
-        <v>0.8885</v>
-      </c>
-      <c r="J4" s="5" t="n">
-        <v>0.8885</v>
-      </c>
+      <c r="H4" s="5" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="5" t="n">
         <v>0.8883</v>
       </c>
@@ -1193,12 +1193,12 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>YATSF1</t>
+          <t>KARSF1</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Yatpool Solar Farm</t>
+          <t>Karadoc Solar Farm</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -1207,13 +1207,17 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="E12" s="5" t="inlineStr"/>
       <c r="F12" s="5" t="inlineStr"/>
       <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="n">
+        <v>0.9472</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>0.8097</v>
+      </c>
       <c r="J12" s="5" t="n">
         <v>0.8045</v>
       </c>
@@ -1250,12 +1254,12 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>KARSF1</t>
+          <t>YATSF1</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Karadoc Solar Farm</t>
+          <t>Yatpool Solar Farm</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -1264,17 +1268,13 @@
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="E13" s="5" t="inlineStr"/>
       <c r="F13" s="5" t="inlineStr"/>
       <c r="G13" s="5" t="inlineStr"/>
-      <c r="H13" s="5" t="n">
-        <v>0.9472</v>
-      </c>
-      <c r="I13" s="5" t="n">
-        <v>0.8097</v>
-      </c>
+      <c r="H13" s="5" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr"/>
       <c r="J13" s="5" t="n">
         <v>0.8045</v>
       </c>
@@ -1311,12 +1311,12 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>BANN1</t>
+          <t>WEMENSF1</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Bannerton Solar Park</t>
+          <t>Wemen Solar Farm</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -1325,13 +1325,13 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="E14" s="5" t="inlineStr"/>
       <c r="F14" s="5" t="inlineStr"/>
       <c r="G14" s="5" t="inlineStr"/>
       <c r="H14" s="5" t="n">
-        <v>1.0062</v>
+        <v>0.9262</v>
       </c>
       <c r="I14" s="5" t="n">
         <v>0.8246</v>
@@ -1372,12 +1372,12 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>WEMENSF1</t>
+          <t>BANN1</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Wemen Solar Farm</t>
+          <t>Bannerton Solar Park</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -1386,13 +1386,13 @@
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="E15" s="5" t="inlineStr"/>
       <c r="F15" s="5" t="inlineStr"/>
       <c r="G15" s="5" t="inlineStr"/>
       <c r="H15" s="5" t="n">
-        <v>0.9262</v>
+        <v>1.0062</v>
       </c>
       <c r="I15" s="5" t="n">
         <v>0.8246</v>
@@ -1433,12 +1433,12 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>WUNUSF1</t>
+          <t>GIRGSF</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Wunghnu Solar Farm</t>
+          <t>Girgarre Solar Farm</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>93.5</v>
+        <v>93.31</v>
       </c>
       <c r="E16" s="5" t="inlineStr"/>
       <c r="F16" s="5" t="inlineStr"/>
@@ -1482,12 +1482,12 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>NUMURSF1</t>
+          <t>WUNUSF1</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Numurkah Solar Farm</t>
+          <t>Wunghnu Solar Farm</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -1496,29 +1496,17 @@
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>112</v>
+        <v>93.5</v>
       </c>
       <c r="E17" s="5" t="inlineStr"/>
       <c r="F17" s="5" t="inlineStr"/>
       <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="n">
-        <v>0.982</v>
-      </c>
-      <c r="I17" s="5" t="n">
-        <v>0.9896</v>
-      </c>
-      <c r="J17" s="5" t="n">
-        <v>0.9945000000000001</v>
-      </c>
-      <c r="K17" s="5" t="n">
-        <v>0.9963</v>
-      </c>
-      <c r="L17" s="5" t="n">
-        <v>0.9715</v>
-      </c>
-      <c r="M17" s="5" t="n">
-        <v>0.9738</v>
-      </c>
+      <c r="H17" s="5" t="inlineStr"/>
+      <c r="I17" s="5" t="inlineStr"/>
+      <c r="J17" s="5" t="inlineStr"/>
+      <c r="K17" s="5" t="inlineStr"/>
+      <c r="L17" s="5" t="inlineStr"/>
+      <c r="M17" s="5" t="inlineStr"/>
       <c r="N17" s="5" t="n">
         <v>0.9477</v>
       </c>
@@ -1543,12 +1531,12 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>GIRGSF</t>
+          <t>NUMURSF1</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Girgarre Solar Farm</t>
+          <t>Numurkah Solar Farm</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -1557,17 +1545,29 @@
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>93.31</v>
+        <v>112</v>
       </c>
       <c r="E18" s="5" t="inlineStr"/>
       <c r="F18" s="5" t="inlineStr"/>
       <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
-      <c r="L18" s="5" t="inlineStr"/>
-      <c r="M18" s="5" t="inlineStr"/>
+      <c r="H18" s="5" t="n">
+        <v>0.982</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>0.9896</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>0.9945000000000001</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>0.9963</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>0.9715</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>0.9738</v>
+      </c>
       <c r="N18" s="5" t="n">
         <v>0.9477</v>
       </c>
@@ -1898,12 +1898,12 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>COHUNSF1</t>
+          <t>GANNSF1</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Cohuna Solar Farm</t>
+          <t>Gannawarra Solar Farm</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -1912,13 +1912,19 @@
         </is>
       </c>
       <c r="D25" s="4" t="n">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="E25" s="5" t="inlineStr"/>
       <c r="F25" s="5" t="inlineStr"/>
-      <c r="G25" s="5" t="inlineStr"/>
-      <c r="H25" s="5" t="inlineStr"/>
-      <c r="I25" s="5" t="inlineStr"/>
+      <c r="G25" s="5" t="n">
+        <v>1.044</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>0.9729</v>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>0.8994</v>
+      </c>
       <c r="J25" s="5" t="n">
         <v>0.8863</v>
       </c>
@@ -1955,12 +1961,12 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>GANNSF1</t>
+          <t>COHUNSF1</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Gannawarra Solar Farm</t>
+          <t>Cohuna Solar Farm</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -1969,19 +1975,13 @@
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="E26" s="5" t="inlineStr"/>
       <c r="F26" s="5" t="inlineStr"/>
-      <c r="G26" s="5" t="n">
-        <v>1.044</v>
-      </c>
-      <c r="H26" s="5" t="n">
-        <v>0.9729</v>
-      </c>
-      <c r="I26" s="5" t="n">
-        <v>0.8994</v>
-      </c>
+      <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr"/>
       <c r="J26" s="5" t="n">
         <v>0.8863</v>
       </c>
@@ -2185,12 +2185,12 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>BRYB2WF2</t>
+          <t>BRYB1WF1</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Berrybank 2 Wind Farm</t>
+          <t>Berrybank Wind Farm</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -2199,15 +2199,19 @@
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>109</v>
+        <v>180.6</v>
       </c>
       <c r="E30" s="5" t="inlineStr"/>
       <c r="F30" s="5" t="inlineStr"/>
       <c r="G30" s="5" t="inlineStr"/>
       <c r="H30" s="5" t="inlineStr"/>
       <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="J30" s="5" t="n">
+        <v>0.9482</v>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>0.9431</v>
+      </c>
       <c r="L30" s="5" t="n">
         <v>0.9496</v>
       </c>
@@ -2238,12 +2242,12 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>BRYB1WF1</t>
+          <t>BRYB2WF2</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Berrybank Wind Farm</t>
+          <t>Berrybank 2 Wind Farm</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -2252,19 +2256,15 @@
         </is>
       </c>
       <c r="D31" s="4" t="n">
-        <v>180.6</v>
+        <v>109</v>
       </c>
       <c r="E31" s="5" t="inlineStr"/>
       <c r="F31" s="5" t="inlineStr"/>
       <c r="G31" s="5" t="inlineStr"/>
       <c r="H31" s="5" t="inlineStr"/>
       <c r="I31" s="5" t="inlineStr"/>
-      <c r="J31" s="5" t="n">
-        <v>0.9482</v>
-      </c>
-      <c r="K31" s="5" t="n">
-        <v>0.9431</v>
-      </c>
+      <c r="J31" s="5" t="inlineStr"/>
+      <c r="K31" s="5" t="inlineStr"/>
       <c r="L31" s="5" t="n">
         <v>0.9496</v>
       </c>
@@ -2600,12 +2600,12 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>MOORAWF1</t>
+          <t>ELAINWF1</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Moorabool Wind Farm </t>
+          <t>Elaine Wind Farm</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -2614,13 +2614,15 @@
         </is>
       </c>
       <c r="D37" s="4" t="n">
-        <v>312</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="E37" s="5" t="inlineStr"/>
       <c r="F37" s="5" t="inlineStr"/>
       <c r="G37" s="5" t="inlineStr"/>
       <c r="H37" s="5" t="inlineStr"/>
-      <c r="I37" s="5" t="inlineStr"/>
+      <c r="I37" s="5" t="n">
+        <v>0.965</v>
+      </c>
       <c r="J37" s="5" t="n">
         <v>0.9500999999999999</v>
       </c>
@@ -2657,134 +2659,134 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>MOORABS1</t>
+          <t>MERCER01</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Moorabool Wind Farm </t>
+          <t>Mt Mercer Wind Farm</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D38" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E38" s="5" t="inlineStr"/>
-      <c r="F38" s="5" t="inlineStr"/>
-      <c r="G38" s="5" t="inlineStr"/>
-      <c r="H38" s="5" t="inlineStr"/>
-      <c r="I38" s="5" t="inlineStr"/>
-      <c r="J38" s="5" t="inlineStr"/>
-      <c r="K38" s="5" t="inlineStr"/>
-      <c r="L38" s="5" t="inlineStr"/>
-      <c r="M38" s="5" t="inlineStr"/>
-      <c r="N38" s="5" t="inlineStr"/>
+        <v>131.2</v>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>1.0033</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>1.0048</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>1.001</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>0.9909</v>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="J38" s="5" t="n">
+        <v>0.9500999999999999</v>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>0.9459</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>0.948</v>
+      </c>
+      <c r="M38" s="5" t="n">
+        <v>0.9576</v>
+      </c>
+      <c r="N38" s="5" t="n">
+        <v>0.9475</v>
+      </c>
       <c r="O38" s="5" t="inlineStr"/>
       <c r="P38" s="5" t="n">
         <v>0.9569</v>
       </c>
-      <c r="Q38" s="5" t="n">
-        <v>0.9569</v>
-      </c>
+      <c r="Q38" s="5" t="inlineStr"/>
       <c r="R38" s="5" t="n">
         <v>0.9556</v>
       </c>
-      <c r="S38" s="5" t="n">
-        <v>0.9556</v>
-      </c>
+      <c r="S38" s="5" t="inlineStr"/>
       <c r="T38" s="5" t="n">
         <v>-0.0013</v>
       </c>
       <c r="U38" s="6" t="n">
         <v>-0.14</v>
       </c>
-      <c r="V38" s="5" t="n">
-        <v>-0.0013</v>
-      </c>
-      <c r="W38" s="6" t="n">
-        <v>-0.14</v>
-      </c>
+      <c r="V38" s="5" t="inlineStr"/>
+      <c r="W38" s="6" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>MERCER01</t>
+          <t>MOORABS1</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Mt Mercer Wind Farm</t>
+          <t xml:space="preserve">Moorabool Wind Farm </t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D39" s="4" t="n">
-        <v>131.2</v>
-      </c>
-      <c r="E39" s="5" t="n">
-        <v>1.0033</v>
-      </c>
-      <c r="F39" s="5" t="n">
-        <v>1.0048</v>
-      </c>
-      <c r="G39" s="5" t="n">
-        <v>1.001</v>
-      </c>
-      <c r="H39" s="5" t="n">
-        <v>0.9909</v>
-      </c>
-      <c r="I39" s="5" t="n">
-        <v>0.965</v>
-      </c>
-      <c r="J39" s="5" t="n">
-        <v>0.9500999999999999</v>
-      </c>
-      <c r="K39" s="5" t="n">
-        <v>0.9459</v>
-      </c>
-      <c r="L39" s="5" t="n">
-        <v>0.948</v>
-      </c>
-      <c r="M39" s="5" t="n">
-        <v>0.9576</v>
-      </c>
-      <c r="N39" s="5" t="n">
-        <v>0.9475</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E39" s="5" t="inlineStr"/>
+      <c r="F39" s="5" t="inlineStr"/>
+      <c r="G39" s="5" t="inlineStr"/>
+      <c r="H39" s="5" t="inlineStr"/>
+      <c r="I39" s="5" t="inlineStr"/>
+      <c r="J39" s="5" t="inlineStr"/>
+      <c r="K39" s="5" t="inlineStr"/>
+      <c r="L39" s="5" t="inlineStr"/>
+      <c r="M39" s="5" t="inlineStr"/>
+      <c r="N39" s="5" t="inlineStr"/>
       <c r="O39" s="5" t="inlineStr"/>
       <c r="P39" s="5" t="n">
         <v>0.9569</v>
       </c>
-      <c r="Q39" s="5" t="inlineStr"/>
+      <c r="Q39" s="5" t="n">
+        <v>0.9569</v>
+      </c>
       <c r="R39" s="5" t="n">
         <v>0.9556</v>
       </c>
-      <c r="S39" s="5" t="inlineStr"/>
+      <c r="S39" s="5" t="n">
+        <v>0.9556</v>
+      </c>
       <c r="T39" s="5" t="n">
         <v>-0.0013</v>
       </c>
       <c r="U39" s="6" t="n">
         <v>-0.14</v>
       </c>
-      <c r="V39" s="5" t="inlineStr"/>
-      <c r="W39" s="6" t="inlineStr"/>
+      <c r="V39" s="5" t="n">
+        <v>-0.0013</v>
+      </c>
+      <c r="W39" s="6" t="n">
+        <v>-0.14</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>ELAINWF1</t>
+          <t>MOORAWF1</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Elaine Wind Farm</t>
+          <t xml:space="preserve">Moorabool Wind Farm </t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -2793,15 +2795,13 @@
         </is>
       </c>
       <c r="D40" s="4" t="n">
-        <v>83.59999999999999</v>
+        <v>312</v>
       </c>
       <c r="E40" s="5" t="inlineStr"/>
       <c r="F40" s="5" t="inlineStr"/>
       <c r="G40" s="5" t="inlineStr"/>
       <c r="H40" s="5" t="inlineStr"/>
-      <c r="I40" s="5" t="n">
-        <v>0.965</v>
-      </c>
+      <c r="I40" s="5" t="inlineStr"/>
       <c r="J40" s="5" t="n">
         <v>0.9500999999999999</v>
       </c>
@@ -2838,7 +2838,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>MURRAY</t>
+          <t>MURAYNL3</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="D41" s="4" t="n">
-        <v>1500</v>
+        <v>25</v>
       </c>
       <c r="E41" s="5" t="n">
         <v>0.9885</v>
@@ -2905,7 +2905,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>MURAYNL1</t>
+          <t>MURAYNL2</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -2972,7 +2972,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>MURAYNL3</t>
+          <t>MURAYNL1</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -3039,7 +3039,7 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>MURAYNL2</t>
+          <t>MURRAY</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="D44" s="4" t="n">
-        <v>25</v>
+        <v>1500</v>
       </c>
       <c r="E44" s="5" t="n">
         <v>0.9885</v>
@@ -3173,12 +3173,12 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>YWNL1</t>
+          <t>YWPS2</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>YALLOURN 'W' POWER STATION</t>
+          <t>Yallourn 'W' Power Station</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -3187,7 +3187,7 @@
         </is>
       </c>
       <c r="D46" s="4" t="n">
-        <v>25</v>
+        <v>360</v>
       </c>
       <c r="E46" s="5" t="n">
         <v>0.9563</v>
@@ -3240,7 +3240,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>YWPS2</t>
+          <t>YWPS3</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -3254,7 +3254,7 @@
         </is>
       </c>
       <c r="D47" s="4" t="n">
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="E47" s="5" t="n">
         <v>0.9563</v>
@@ -3307,12 +3307,12 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>YWPS3</t>
+          <t>YWNL1</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Yallourn 'W' Power Station</t>
+          <t>YALLOURN 'W' POWER STATION</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -3321,7 +3321,7 @@
         </is>
       </c>
       <c r="D48" s="4" t="n">
-        <v>380</v>
+        <v>25</v>
       </c>
       <c r="E48" s="5" t="n">
         <v>0.9563</v>
@@ -3441,12 +3441,12 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>BAPS</t>
+          <t>DARTM1</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Banimboola Power Station</t>
+          <t>Dartmouth Power Station</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="D50" s="4" t="n">
-        <v>12.85</v>
+        <v>185</v>
       </c>
       <c r="E50" s="5" t="n">
         <v>1.0004</v>
@@ -3508,12 +3508,12 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>DARTM1</t>
+          <t>BAPS</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Dartmouth Power Station</t>
+          <t>Banimboola Power Station</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -3522,7 +3522,7 @@
         </is>
       </c>
       <c r="D51" s="4" t="n">
-        <v>185</v>
+        <v>12.85</v>
       </c>
       <c r="E51" s="5" t="n">
         <v>1.0004</v>
@@ -3697,12 +3697,12 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>CHALLHWF</t>
+          <t>MAROOWF1</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Challicum Hills Wind Farm</t>
+          <t>Maroona Wind Farm</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -3711,22 +3711,18 @@
         </is>
       </c>
       <c r="D54" s="4" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="E54" s="5" t="n">
-        <v>1.0988</v>
-      </c>
-      <c r="F54" s="5" t="n">
-        <v>1.0988</v>
-      </c>
+        <v>6.8</v>
+      </c>
+      <c r="E54" s="5" t="inlineStr"/>
+      <c r="F54" s="5" t="inlineStr"/>
       <c r="G54" s="5" t="n">
-        <v>1.0988</v>
+        <v>1.016</v>
       </c>
       <c r="H54" s="5" t="n">
-        <v>0.9957</v>
+        <v>1.0016</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>0.9193</v>
+        <v>0.9716</v>
       </c>
       <c r="J54" s="5" t="n">
         <v>0.9711</v>
@@ -3764,12 +3760,12 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>YSWF1</t>
+          <t>HEPWIND1</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Yaloak South Wind Farm</t>
+          <t>Hepburn Community Wind Farm</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -3778,10 +3774,14 @@
         </is>
       </c>
       <c r="D55" s="4" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="E55" s="5" t="inlineStr"/>
-      <c r="F55" s="5" t="inlineStr"/>
+        <v>4.1</v>
+      </c>
+      <c r="E55" s="5" t="n">
+        <v>1.0207</v>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>1.0209</v>
+      </c>
       <c r="G55" s="5" t="n">
         <v>1.016</v>
       </c>
@@ -3827,12 +3827,12 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>MAROOWF1</t>
+          <t>CHALLHWF</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Maroona Wind Farm</t>
+          <t>Challicum Hills Wind Farm</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -3841,18 +3841,22 @@
         </is>
       </c>
       <c r="D56" s="4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="E56" s="5" t="inlineStr"/>
-      <c r="F56" s="5" t="inlineStr"/>
+        <v>52.5</v>
+      </c>
+      <c r="E56" s="5" t="n">
+        <v>1.0988</v>
+      </c>
+      <c r="F56" s="5" t="n">
+        <v>1.0988</v>
+      </c>
       <c r="G56" s="5" t="n">
-        <v>1.016</v>
+        <v>1.0988</v>
       </c>
       <c r="H56" s="5" t="n">
-        <v>1.0016</v>
+        <v>0.9957</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>0.9716</v>
+        <v>0.9193</v>
       </c>
       <c r="J56" s="5" t="n">
         <v>0.9711</v>
@@ -3890,12 +3894,12 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>HEPWIND1</t>
+          <t>YSWF1</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Hepburn Community Wind Farm</t>
+          <t>Yaloak South Wind Farm</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -3904,14 +3908,10 @@
         </is>
       </c>
       <c r="D57" s="4" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="E57" s="5" t="n">
-        <v>1.0207</v>
-      </c>
-      <c r="F57" s="5" t="n">
-        <v>1.0209</v>
-      </c>
+        <v>28.7</v>
+      </c>
+      <c r="E57" s="5" t="inlineStr"/>
+      <c r="F57" s="5" t="inlineStr"/>
       <c r="G57" s="5" t="n">
         <v>1.016</v>
       </c>
@@ -3957,7 +3957,7 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>MURR1-10</t>
+          <t>MURR1-1</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -4020,7 +4020,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>MURR1-1</t>
+          <t>MURR1-10</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -4083,7 +4083,7 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>MURR1-7</t>
+          <t>MURR1-2</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -4146,17 +4146,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>MURR2-4</t>
+          <t>MURR1-4</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>MURRAY2</t>
+          <t>MURRAY1</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr"/>
       <c r="D61" s="4" t="n">
-        <v>138</v>
+        <v>95</v>
       </c>
       <c r="E61" s="5" t="n">
         <v>0.98</v>
@@ -4209,7 +4209,7 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>MURR1-2</t>
+          <t>MURR1-3</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -4272,17 +4272,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>MURR2-3</t>
+          <t>MURR1-5</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>MURRAY2</t>
+          <t>MURRAY1</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr"/>
       <c r="D63" s="4" t="n">
-        <v>138</v>
+        <v>95</v>
       </c>
       <c r="E63" s="5" t="n">
         <v>0.98</v>
@@ -4335,7 +4335,7 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>MURR1-3</t>
+          <t>MURR1-6</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -4398,7 +4398,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>MURR1-9</t>
+          <t>MURR1-8</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -4461,7 +4461,7 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>MURR1-5</t>
+          <t>MURR1-7</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -4524,7 +4524,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>MURR1-6</t>
+          <t>MURR1-9</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -4587,17 +4587,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>MURR1-8</t>
+          <t>MURR2-1</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>MURRAY1</t>
+          <t>MURRAY2</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr"/>
       <c r="D68" s="4" t="n">
-        <v>95</v>
+        <v>138</v>
       </c>
       <c r="E68" s="5" t="n">
         <v>0.98</v>
@@ -4650,7 +4650,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>MURR2-1</t>
+          <t>MURR2-2</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -4713,7 +4713,7 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>MURR2-2</t>
+          <t>MURR2-3</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -4776,17 +4776,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>MURR1-4</t>
+          <t>MURR2-4</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>MURRAY1</t>
+          <t>MURRAY2</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr"/>
       <c r="D71" s="4" t="n">
-        <v>95</v>
+        <v>138</v>
       </c>
       <c r="E71" s="5" t="n">
         <v>0.98</v>
@@ -4898,7 +4898,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>GPWFEST3</t>
+          <t>GPWFEST2</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="D73" s="4" t="n">
-        <v>248</v>
+        <v>260.4</v>
       </c>
       <c r="E73" s="5" t="inlineStr"/>
       <c r="F73" s="5" t="inlineStr"/>
@@ -4947,7 +4947,7 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>GPWFEST2</t>
+          <t>GPWFEST3</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="D74" s="4" t="n">
-        <v>260.4</v>
+        <v>248</v>
       </c>
       <c r="E74" s="5" t="inlineStr"/>
       <c r="F74" s="5" t="inlineStr"/>
@@ -5096,55 +5096,35 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>JLA02</t>
+          <t>GPWFWST1</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>Jeeralang "A" Power Station</t>
+          <t>Golden Plains Wind Farm West</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D77" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="E77" s="5" t="n">
-        <v>0.9667</v>
-      </c>
-      <c r="F77" s="5" t="n">
-        <v>0.9641</v>
-      </c>
-      <c r="G77" s="5" t="n">
-        <v>0.983</v>
-      </c>
-      <c r="H77" s="5" t="n">
-        <v>0.9782999999999999</v>
-      </c>
-      <c r="I77" s="5" t="n">
-        <v>0.9731</v>
-      </c>
-      <c r="J77" s="5" t="n">
-        <v>0.9734</v>
-      </c>
-      <c r="K77" s="5" t="n">
-        <v>0.9755</v>
-      </c>
-      <c r="L77" s="5" t="n">
-        <v>0.9727</v>
-      </c>
-      <c r="M77" s="5" t="n">
-        <v>0.9764</v>
-      </c>
-      <c r="N77" s="5" t="n">
-        <v>0.9789</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="E77" s="5" t="inlineStr"/>
+      <c r="F77" s="5" t="inlineStr"/>
+      <c r="G77" s="5" t="inlineStr"/>
+      <c r="H77" s="5" t="inlineStr"/>
+      <c r="I77" s="5" t="inlineStr"/>
+      <c r="J77" s="5" t="inlineStr"/>
+      <c r="K77" s="5" t="inlineStr"/>
+      <c r="L77" s="5" t="inlineStr"/>
+      <c r="M77" s="5" t="inlineStr"/>
+      <c r="N77" s="5" t="inlineStr"/>
       <c r="O77" s="5" t="inlineStr"/>
       <c r="P77" s="5" t="n">
-        <v>0.9768</v>
+        <v>0.9837</v>
       </c>
       <c r="Q77" s="5" t="inlineStr"/>
       <c r="R77" s="5" t="n">
@@ -5152,10 +5132,10 @@
       </c>
       <c r="S77" s="5" t="inlineStr"/>
       <c r="T77" s="5" t="n">
-        <v>0.0055</v>
+        <v>-0.0014</v>
       </c>
       <c r="U77" s="6" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.14</v>
       </c>
       <c r="V77" s="5" t="inlineStr"/>
       <c r="W77" s="6" t="inlineStr"/>
@@ -5163,12 +5143,12 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>JLA03</t>
+          <t>JLB03</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>Jeeralang "A" Power Station</t>
+          <t>Jeeralang "B" Power Station</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -5177,7 +5157,7 @@
         </is>
       </c>
       <c r="D78" s="4" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="E78" s="5" t="n">
         <v>0.9667</v>
@@ -5230,12 +5210,12 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>JLA01</t>
+          <t>JLB01</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>Jeeralang "A" Power Station</t>
+          <t>Jeeralang "B" Power Station</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
@@ -5244,7 +5224,7 @@
         </is>
       </c>
       <c r="D79" s="4" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="E79" s="5" t="n">
         <v>0.9667</v>
@@ -5297,7 +5277,7 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>JLB01</t>
+          <t>JLB02</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -5431,12 +5411,12 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>JLB03</t>
+          <t>JLA03</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Jeeralang "B" Power Station</t>
+          <t>Jeeralang "A" Power Station</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -5445,7 +5425,7 @@
         </is>
       </c>
       <c r="D82" s="4" t="n">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="E82" s="5" t="n">
         <v>0.9667</v>
@@ -5498,35 +5478,55 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>GPWFWST1</t>
+          <t>JLA02</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>Golden Plains Wind Farm West</t>
+          <t>Jeeralang "A" Power Station</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D83" s="4" t="n">
-        <v>266</v>
-      </c>
-      <c r="E83" s="5" t="inlineStr"/>
-      <c r="F83" s="5" t="inlineStr"/>
-      <c r="G83" s="5" t="inlineStr"/>
-      <c r="H83" s="5" t="inlineStr"/>
-      <c r="I83" s="5" t="inlineStr"/>
-      <c r="J83" s="5" t="inlineStr"/>
-      <c r="K83" s="5" t="inlineStr"/>
-      <c r="L83" s="5" t="inlineStr"/>
-      <c r="M83" s="5" t="inlineStr"/>
-      <c r="N83" s="5" t="inlineStr"/>
+        <v>51</v>
+      </c>
+      <c r="E83" s="5" t="n">
+        <v>0.9667</v>
+      </c>
+      <c r="F83" s="5" t="n">
+        <v>0.9641</v>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>0.983</v>
+      </c>
+      <c r="H83" s="5" t="n">
+        <v>0.9782999999999999</v>
+      </c>
+      <c r="I83" s="5" t="n">
+        <v>0.9731</v>
+      </c>
+      <c r="J83" s="5" t="n">
+        <v>0.9734</v>
+      </c>
+      <c r="K83" s="5" t="n">
+        <v>0.9755</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>0.9727</v>
+      </c>
+      <c r="M83" s="5" t="n">
+        <v>0.9764</v>
+      </c>
+      <c r="N83" s="5" t="n">
+        <v>0.9789</v>
+      </c>
       <c r="O83" s="5" t="inlineStr"/>
       <c r="P83" s="5" t="n">
-        <v>0.9837</v>
+        <v>0.9768</v>
       </c>
       <c r="Q83" s="5" t="inlineStr"/>
       <c r="R83" s="5" t="n">
@@ -5534,10 +5534,10 @@
       </c>
       <c r="S83" s="5" t="inlineStr"/>
       <c r="T83" s="5" t="n">
-        <v>-0.0014</v>
+        <v>0.0055</v>
       </c>
       <c r="U83" s="6" t="n">
-        <v>-0.14</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="V83" s="5" t="inlineStr"/>
       <c r="W83" s="6" t="inlineStr"/>
@@ -5545,35 +5545,55 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>GPWFWST2</t>
+          <t>JLA01</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>Golden Plains Wind Farm West</t>
+          <t>Jeeralang "A" Power Station</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D84" s="4" t="n">
-        <v>310</v>
-      </c>
-      <c r="E84" s="5" t="inlineStr"/>
-      <c r="F84" s="5" t="inlineStr"/>
-      <c r="G84" s="5" t="inlineStr"/>
-      <c r="H84" s="5" t="inlineStr"/>
-      <c r="I84" s="5" t="inlineStr"/>
-      <c r="J84" s="5" t="inlineStr"/>
-      <c r="K84" s="5" t="inlineStr"/>
-      <c r="L84" s="5" t="inlineStr"/>
-      <c r="M84" s="5" t="inlineStr"/>
-      <c r="N84" s="5" t="inlineStr"/>
+        <v>51</v>
+      </c>
+      <c r="E84" s="5" t="n">
+        <v>0.9667</v>
+      </c>
+      <c r="F84" s="5" t="n">
+        <v>0.9641</v>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>0.983</v>
+      </c>
+      <c r="H84" s="5" t="n">
+        <v>0.9782999999999999</v>
+      </c>
+      <c r="I84" s="5" t="n">
+        <v>0.9731</v>
+      </c>
+      <c r="J84" s="5" t="n">
+        <v>0.9734</v>
+      </c>
+      <c r="K84" s="5" t="n">
+        <v>0.9755</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>0.9727</v>
+      </c>
+      <c r="M84" s="5" t="n">
+        <v>0.9764</v>
+      </c>
+      <c r="N84" s="5" t="n">
+        <v>0.9789</v>
+      </c>
       <c r="O84" s="5" t="inlineStr"/>
       <c r="P84" s="5" t="n">
-        <v>0.9837</v>
+        <v>0.9768</v>
       </c>
       <c r="Q84" s="5" t="inlineStr"/>
       <c r="R84" s="5" t="n">
@@ -5581,10 +5601,10 @@
       </c>
       <c r="S84" s="5" t="inlineStr"/>
       <c r="T84" s="5" t="n">
-        <v>-0.0014</v>
+        <v>0.0055</v>
       </c>
       <c r="U84" s="6" t="n">
-        <v>-0.14</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="V84" s="5" t="inlineStr"/>
       <c r="W84" s="6" t="inlineStr"/>
@@ -5592,55 +5612,35 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>JLB02</t>
+          <t>GPWFWST2</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>Jeeralang "B" Power Station</t>
+          <t>Golden Plains Wind Farm West</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D85" s="4" t="n">
-        <v>76</v>
-      </c>
-      <c r="E85" s="5" t="n">
-        <v>0.9667</v>
-      </c>
-      <c r="F85" s="5" t="n">
-        <v>0.9641</v>
-      </c>
-      <c r="G85" s="5" t="n">
-        <v>0.983</v>
-      </c>
-      <c r="H85" s="5" t="n">
-        <v>0.9782999999999999</v>
-      </c>
-      <c r="I85" s="5" t="n">
-        <v>0.9731</v>
-      </c>
-      <c r="J85" s="5" t="n">
-        <v>0.9734</v>
-      </c>
-      <c r="K85" s="5" t="n">
-        <v>0.9755</v>
-      </c>
-      <c r="L85" s="5" t="n">
-        <v>0.9727</v>
-      </c>
-      <c r="M85" s="5" t="n">
-        <v>0.9764</v>
-      </c>
-      <c r="N85" s="5" t="n">
-        <v>0.9789</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="E85" s="5" t="inlineStr"/>
+      <c r="F85" s="5" t="inlineStr"/>
+      <c r="G85" s="5" t="inlineStr"/>
+      <c r="H85" s="5" t="inlineStr"/>
+      <c r="I85" s="5" t="inlineStr"/>
+      <c r="J85" s="5" t="inlineStr"/>
+      <c r="K85" s="5" t="inlineStr"/>
+      <c r="L85" s="5" t="inlineStr"/>
+      <c r="M85" s="5" t="inlineStr"/>
+      <c r="N85" s="5" t="inlineStr"/>
       <c r="O85" s="5" t="inlineStr"/>
       <c r="P85" s="5" t="n">
-        <v>0.9768</v>
+        <v>0.9837</v>
       </c>
       <c r="Q85" s="5" t="inlineStr"/>
       <c r="R85" s="5" t="n">
@@ -5648,10 +5648,10 @@
       </c>
       <c r="S85" s="5" t="inlineStr"/>
       <c r="T85" s="5" t="n">
-        <v>0.0055</v>
+        <v>-0.0014</v>
       </c>
       <c r="U85" s="6" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.14</v>
       </c>
       <c r="V85" s="5" t="inlineStr"/>
       <c r="W85" s="6" t="inlineStr"/>
@@ -5726,12 +5726,12 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>STOCKYD1</t>
+          <t>DUNDWF2</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>Stockyard Hill Wind Farm</t>
+          <t>Dundonnell Wind Farm</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -5740,25 +5740,29 @@
         </is>
       </c>
       <c r="D87" s="4" t="n">
-        <v>531</v>
+        <v>46</v>
       </c>
       <c r="E87" s="5" t="inlineStr"/>
       <c r="F87" s="5" t="inlineStr"/>
       <c r="G87" s="5" t="inlineStr"/>
       <c r="H87" s="5" t="inlineStr"/>
-      <c r="I87" s="5" t="inlineStr"/>
-      <c r="J87" s="5" t="inlineStr"/>
+      <c r="I87" s="5" t="n">
+        <v>0.9812</v>
+      </c>
+      <c r="J87" s="5" t="n">
+        <v>0.979</v>
+      </c>
       <c r="K87" s="5" t="n">
-        <v>0.9782</v>
+        <v>0.9789</v>
       </c>
       <c r="L87" s="5" t="n">
-        <v>0.9799</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="M87" s="5" t="n">
-        <v>0.9869</v>
+        <v>0.987</v>
       </c>
       <c r="N87" s="5" t="n">
-        <v>0.9812</v>
+        <v>0.981</v>
       </c>
       <c r="O87" s="5" t="inlineStr"/>
       <c r="P87" s="5" t="n">
@@ -5840,7 +5844,7 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>DUNDWF2</t>
+          <t>DUNDWF1</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -5854,7 +5858,7 @@
         </is>
       </c>
       <c r="D89" s="4" t="n">
-        <v>46</v>
+        <v>168</v>
       </c>
       <c r="E89" s="5" t="inlineStr"/>
       <c r="F89" s="5" t="inlineStr"/>
@@ -5899,12 +5903,12 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>DUNDWF1</t>
+          <t>STOCKYD1</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>Dundonnell Wind Farm</t>
+          <t>Stockyard Hill Wind Farm</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
@@ -5913,29 +5917,25 @@
         </is>
       </c>
       <c r="D90" s="4" t="n">
-        <v>168</v>
+        <v>531</v>
       </c>
       <c r="E90" s="5" t="inlineStr"/>
       <c r="F90" s="5" t="inlineStr"/>
       <c r="G90" s="5" t="inlineStr"/>
       <c r="H90" s="5" t="inlineStr"/>
-      <c r="I90" s="5" t="n">
+      <c r="I90" s="5" t="inlineStr"/>
+      <c r="J90" s="5" t="inlineStr"/>
+      <c r="K90" s="5" t="n">
+        <v>0.9782</v>
+      </c>
+      <c r="L90" s="5" t="n">
+        <v>0.9799</v>
+      </c>
+      <c r="M90" s="5" t="n">
+        <v>0.9869</v>
+      </c>
+      <c r="N90" s="5" t="n">
         <v>0.9812</v>
-      </c>
-      <c r="J90" s="5" t="n">
-        <v>0.979</v>
-      </c>
-      <c r="K90" s="5" t="n">
-        <v>0.9789</v>
-      </c>
-      <c r="L90" s="5" t="n">
-        <v>0.9824000000000001</v>
-      </c>
-      <c r="M90" s="5" t="n">
-        <v>0.987</v>
-      </c>
-      <c r="N90" s="5" t="n">
-        <v>0.981</v>
       </c>
       <c r="O90" s="5" t="inlineStr"/>
       <c r="P90" s="5" t="n">
@@ -6007,7 +6007,7 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>VPGS5</t>
+          <t>VPGS1</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -6074,7 +6074,7 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>VPGS1</t>
+          <t>VPGS5</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -6208,12 +6208,12 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>VPGS6</t>
+          <t>LYA3</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>Valley Power Peaking Facility</t>
+          <t>Loy Yang A Power Station</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -6222,7 +6222,7 @@
         </is>
       </c>
       <c r="D95" s="4" t="n">
-        <v>50</v>
+        <v>560</v>
       </c>
       <c r="E95" s="5" t="n">
         <v>0.9742</v>
@@ -6275,12 +6275,12 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>VPGS4</t>
+          <t>LYA2</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>Valley Power Peaking Facility</t>
+          <t>Loy Yang A Power Station</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
@@ -6289,7 +6289,7 @@
         </is>
       </c>
       <c r="D96" s="4" t="n">
-        <v>50</v>
+        <v>530</v>
       </c>
       <c r="E96" s="5" t="n">
         <v>0.9742</v>
@@ -6342,12 +6342,12 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>LYNL1</t>
+          <t>VPGS3</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>LOY YANG A POWER STATION</t>
+          <t>Valley Power Peaking Facility</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
@@ -6356,7 +6356,7 @@
         </is>
       </c>
       <c r="D97" s="4" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E97" s="5" t="n">
         <v>0.9742</v>
@@ -6409,7 +6409,7 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>VPGS3</t>
+          <t>VPGS4</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -6476,7 +6476,7 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>LYA4</t>
+          <t>LYA1</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -6543,12 +6543,12 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>LOYYB2</t>
+          <t>VPGS6</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>Loy Yang B Power Station</t>
+          <t>Valley Power Peaking Facility</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
@@ -6557,7 +6557,7 @@
         </is>
       </c>
       <c r="D100" s="4" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="E100" s="5" t="n">
         <v>0.9742</v>
@@ -6610,12 +6610,12 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>LYA1</t>
+          <t>LYNL1</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>Loy Yang A Power Station</t>
+          <t>LOY YANG A POWER STATION</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
@@ -6624,7 +6624,7 @@
         </is>
       </c>
       <c r="D101" s="4" t="n">
-        <v>560</v>
+        <v>25</v>
       </c>
       <c r="E101" s="5" t="n">
         <v>0.9742</v>
@@ -6677,7 +6677,7 @@
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>LYA2</t>
+          <t>LYA4</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -6691,7 +6691,7 @@
         </is>
       </c>
       <c r="D102" s="4" t="n">
-        <v>530</v>
+        <v>560</v>
       </c>
       <c r="E102" s="5" t="n">
         <v>0.9742</v>
@@ -6744,12 +6744,12 @@
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>LYA3</t>
+          <t>LOYYB2</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>Loy Yang A Power Station</t>
+          <t>Loy Yang B Power Station</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
@@ -6758,7 +6758,7 @@
         </is>
       </c>
       <c r="D103" s="4" t="n">
-        <v>560</v>
+        <v>500</v>
       </c>
       <c r="E103" s="5" t="n">
         <v>0.9742</v>
@@ -6811,128 +6811,128 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>HBESS1</t>
+          <t>LOYYB1</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>Hazelwood Battery Energy Storage System</t>
+          <t>Loy Yang B Power Station</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D104" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="E104" s="5" t="inlineStr"/>
-      <c r="F104" s="5" t="inlineStr"/>
-      <c r="G104" s="5" t="inlineStr"/>
-      <c r="H104" s="5" t="inlineStr"/>
-      <c r="I104" s="5" t="inlineStr"/>
-      <c r="J104" s="5" t="inlineStr"/>
-      <c r="K104" s="5" t="inlineStr"/>
-      <c r="L104" s="5" t="inlineStr"/>
-      <c r="M104" s="5" t="inlineStr"/>
+        <v>500</v>
+      </c>
+      <c r="E104" s="5" t="n">
+        <v>0.9742</v>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>0.9723000000000001</v>
+      </c>
+      <c r="G104" s="5" t="n">
+        <v>0.9801</v>
+      </c>
+      <c r="H104" s="5" t="n">
+        <v>0.9798</v>
+      </c>
+      <c r="I104" s="5" t="n">
+        <v>0.9754</v>
+      </c>
+      <c r="J104" s="5" t="n">
+        <v>0.976</v>
+      </c>
+      <c r="K104" s="5" t="n">
+        <v>0.9759</v>
+      </c>
+      <c r="L104" s="5" t="n">
+        <v>0.9782999999999999</v>
+      </c>
+      <c r="M104" s="5" t="n">
+        <v>0.9782</v>
+      </c>
       <c r="N104" s="5" t="n">
-        <v>0.9864000000000001</v>
-      </c>
-      <c r="O104" s="5" t="n">
-        <v>0.9804</v>
-      </c>
+        <v>0.9809</v>
+      </c>
+      <c r="O104" s="5" t="inlineStr"/>
       <c r="P104" s="5" t="n">
-        <v>0.9873</v>
-      </c>
-      <c r="Q104" s="5" t="n">
-        <v>0.9802</v>
-      </c>
+        <v>0.9815</v>
+      </c>
+      <c r="Q104" s="5" t="inlineStr"/>
       <c r="R104" s="5" t="n">
         <v>0.9834000000000001</v>
       </c>
-      <c r="S104" s="5" t="n">
-        <v>0.9873</v>
-      </c>
+      <c r="S104" s="5" t="inlineStr"/>
       <c r="T104" s="5" t="n">
-        <v>-0.0039</v>
+        <v>0.0019</v>
       </c>
       <c r="U104" s="6" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="V104" s="5" t="n">
-        <v>0.0071</v>
-      </c>
-      <c r="W104" s="6" t="n">
-        <v>0.72</v>
-      </c>
+        <v>0.19</v>
+      </c>
+      <c r="V104" s="5" t="inlineStr"/>
+      <c r="W104" s="6" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>LOYYB1</t>
+          <t>HBESS1</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>Loy Yang B Power Station</t>
+          <t>Hazelwood Battery Energy Storage System</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D105" s="4" t="n">
-        <v>500</v>
-      </c>
-      <c r="E105" s="5" t="n">
-        <v>0.9742</v>
-      </c>
-      <c r="F105" s="5" t="n">
-        <v>0.9723000000000001</v>
-      </c>
-      <c r="G105" s="5" t="n">
-        <v>0.9801</v>
-      </c>
-      <c r="H105" s="5" t="n">
-        <v>0.9798</v>
-      </c>
-      <c r="I105" s="5" t="n">
-        <v>0.9754</v>
-      </c>
-      <c r="J105" s="5" t="n">
-        <v>0.976</v>
-      </c>
-      <c r="K105" s="5" t="n">
-        <v>0.9759</v>
-      </c>
-      <c r="L105" s="5" t="n">
-        <v>0.9782999999999999</v>
-      </c>
-      <c r="M105" s="5" t="n">
-        <v>0.9782</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="E105" s="5" t="inlineStr"/>
+      <c r="F105" s="5" t="inlineStr"/>
+      <c r="G105" s="5" t="inlineStr"/>
+      <c r="H105" s="5" t="inlineStr"/>
+      <c r="I105" s="5" t="inlineStr"/>
+      <c r="J105" s="5" t="inlineStr"/>
+      <c r="K105" s="5" t="inlineStr"/>
+      <c r="L105" s="5" t="inlineStr"/>
+      <c r="M105" s="5" t="inlineStr"/>
       <c r="N105" s="5" t="n">
-        <v>0.9809</v>
-      </c>
-      <c r="O105" s="5" t="inlineStr"/>
+        <v>0.9864000000000001</v>
+      </c>
+      <c r="O105" s="5" t="n">
+        <v>0.9804</v>
+      </c>
       <c r="P105" s="5" t="n">
-        <v>0.9815</v>
-      </c>
-      <c r="Q105" s="5" t="inlineStr"/>
+        <v>0.9873</v>
+      </c>
+      <c r="Q105" s="5" t="n">
+        <v>0.9802</v>
+      </c>
       <c r="R105" s="5" t="n">
         <v>0.9834000000000001</v>
       </c>
-      <c r="S105" s="5" t="inlineStr"/>
+      <c r="S105" s="5" t="n">
+        <v>0.9873</v>
+      </c>
       <c r="T105" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0039</v>
       </c>
       <c r="U105" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="V105" s="5" t="inlineStr"/>
-      <c r="W105" s="6" t="inlineStr"/>
+        <v>-0.4</v>
+      </c>
+      <c r="V105" s="5" t="n">
+        <v>0.0071</v>
+      </c>
+      <c r="W105" s="6" t="n">
+        <v>0.72</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
@@ -7697,12 +7697,12 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>MREHA2</t>
+          <t>MREHA1</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>Melbourne Renewable Energy Hub Connection A2</t>
+          <t>Melbourne Renewable Energy Hub Connection A1</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
@@ -7756,12 +7756,12 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>MREHA1</t>
+          <t>MREHA2</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>Melbourne Renewable Energy Hub Connection A1</t>
+          <t>Melbourne Renewable Energy Hub Connection A2</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
@@ -7870,138 +7870,138 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>PIBESS1</t>
+          <t>LONGFORD</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>Phillip Island BESS</t>
+          <t>LONGFORD PLANT</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D121" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="E121" s="5" t="inlineStr"/>
-      <c r="F121" s="5" t="inlineStr"/>
-      <c r="G121" s="5" t="inlineStr"/>
-      <c r="H121" s="5" t="inlineStr"/>
-      <c r="I121" s="5" t="inlineStr"/>
-      <c r="J121" s="5" t="inlineStr"/>
-      <c r="K121" s="5" t="inlineStr"/>
-      <c r="L121" s="5" t="inlineStr"/>
-      <c r="M121" s="5" t="inlineStr"/>
+        <v>44</v>
+      </c>
+      <c r="E121" s="5" t="n">
+        <v>0.9799</v>
+      </c>
+      <c r="F121" s="5" t="n">
+        <v>0.9759</v>
+      </c>
+      <c r="G121" s="5" t="n">
+        <v>0.9886</v>
+      </c>
+      <c r="H121" s="5" t="n">
+        <v>0.9879</v>
+      </c>
+      <c r="I121" s="5" t="n">
+        <v>0.9938</v>
+      </c>
+      <c r="J121" s="5" t="n">
+        <v>0.9955000000000001</v>
+      </c>
+      <c r="K121" s="5" t="n">
+        <v>0.9936</v>
+      </c>
+      <c r="L121" s="5" t="n">
+        <v>0.9977</v>
+      </c>
+      <c r="M121" s="5" t="n">
+        <v>0.9825</v>
+      </c>
       <c r="N121" s="5" t="n">
         <v>0.9848</v>
       </c>
-      <c r="O121" s="5" t="n">
-        <v>0.9848</v>
-      </c>
+      <c r="O121" s="5" t="inlineStr"/>
       <c r="P121" s="5" t="n">
         <v>0.9862</v>
       </c>
-      <c r="Q121" s="5" t="n">
-        <v>0.9862</v>
-      </c>
+      <c r="Q121" s="5" t="inlineStr"/>
       <c r="R121" s="5" t="n">
         <v>0.992</v>
       </c>
-      <c r="S121" s="5" t="n">
-        <v>0.992</v>
-      </c>
+      <c r="S121" s="5" t="inlineStr"/>
       <c r="T121" s="5" t="n">
         <v>0.0058</v>
       </c>
       <c r="U121" s="6" t="n">
         <v>0.59</v>
       </c>
-      <c r="V121" s="5" t="n">
-        <v>0.0058</v>
-      </c>
-      <c r="W121" s="6" t="n">
-        <v>0.59</v>
-      </c>
+      <c r="V121" s="5" t="inlineStr"/>
+      <c r="W121" s="6" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>GLENMAG1</t>
+          <t>PIBESS1</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>Glenmaggie Hydro Power Station</t>
+          <t>Phillip Island BESS</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>Hydro</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D122" s="4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="E122" s="5" t="n">
-        <v>0.9799</v>
-      </c>
-      <c r="F122" s="5" t="n">
-        <v>0.9759</v>
-      </c>
-      <c r="G122" s="5" t="n">
-        <v>0.9886</v>
-      </c>
-      <c r="H122" s="5" t="n">
-        <v>0.9879</v>
-      </c>
-      <c r="I122" s="5" t="n">
-        <v>0.9938</v>
-      </c>
-      <c r="J122" s="5" t="n">
-        <v>0.9955000000000001</v>
-      </c>
-      <c r="K122" s="5" t="n">
-        <v>0.9936</v>
-      </c>
-      <c r="L122" s="5" t="n">
-        <v>0.9977</v>
-      </c>
-      <c r="M122" s="5" t="n">
-        <v>0.9825</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="E122" s="5" t="inlineStr"/>
+      <c r="F122" s="5" t="inlineStr"/>
+      <c r="G122" s="5" t="inlineStr"/>
+      <c r="H122" s="5" t="inlineStr"/>
+      <c r="I122" s="5" t="inlineStr"/>
+      <c r="J122" s="5" t="inlineStr"/>
+      <c r="K122" s="5" t="inlineStr"/>
+      <c r="L122" s="5" t="inlineStr"/>
+      <c r="M122" s="5" t="inlineStr"/>
       <c r="N122" s="5" t="n">
         <v>0.9848</v>
       </c>
-      <c r="O122" s="5" t="inlineStr"/>
+      <c r="O122" s="5" t="n">
+        <v>0.9848</v>
+      </c>
       <c r="P122" s="5" t="n">
         <v>0.9862</v>
       </c>
-      <c r="Q122" s="5" t="inlineStr"/>
+      <c r="Q122" s="5" t="n">
+        <v>0.9862</v>
+      </c>
       <c r="R122" s="5" t="n">
         <v>0.992</v>
       </c>
-      <c r="S122" s="5" t="inlineStr"/>
+      <c r="S122" s="5" t="n">
+        <v>0.992</v>
+      </c>
       <c r="T122" s="5" t="n">
         <v>0.0058</v>
       </c>
       <c r="U122" s="6" t="n">
         <v>0.59</v>
       </c>
-      <c r="V122" s="5" t="inlineStr"/>
-      <c r="W122" s="6" t="inlineStr"/>
+      <c r="V122" s="5" t="n">
+        <v>0.0058</v>
+      </c>
+      <c r="W122" s="6" t="n">
+        <v>0.59</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>TOORAWF</t>
+          <t>WONWP</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>Toora Wind Farm</t>
+          <t>Wonthaggi Wind Farm</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
@@ -8010,7 +8010,7 @@
         </is>
       </c>
       <c r="D123" s="4" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E123" s="5" t="n">
         <v>0.9799</v>
@@ -8063,21 +8063,21 @@
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>WONWP</t>
+          <t>GLENMAG1</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>Wonthaggi Wind Farm</t>
+          <t>Glenmaggie Hydro Power Station</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Hydro</t>
         </is>
       </c>
       <c r="D124" s="4" t="n">
-        <v>12</v>
+        <v>3.8</v>
       </c>
       <c r="E124" s="5" t="n">
         <v>0.9799</v>
@@ -8130,21 +8130,21 @@
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>TGNSS1</t>
+          <t>TOORAWF</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>Traralgon Network Support Station</t>
+          <t>Toora Wind Farm</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D125" s="4" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E125" s="5" t="n">
         <v>0.9799</v>
@@ -8197,21 +8197,21 @@
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>LONGFORD</t>
+          <t>BALDHWF1</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>LONGFORD PLANT</t>
+          <t>Bald Hills Wind Farm</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D126" s="4" t="n">
-        <v>44</v>
+        <v>106.6</v>
       </c>
       <c r="E126" s="5" t="n">
         <v>0.9799</v>
@@ -8264,21 +8264,21 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>BALDHWF1</t>
+          <t>TGNSS1</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>Bald Hills Wind Farm</t>
+          <t>Traralgon Network Support Station</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D127" s="4" t="n">
-        <v>106.6</v>
+        <v>10</v>
       </c>
       <c r="E127" s="5" t="n">
         <v>0.9799</v>
@@ -8457,12 +8457,12 @@
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>CODRNGTON</t>
+          <t>YAMBUKWF</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>Codrington Wind Farm</t>
+          <t>Yambuk Wind Farm</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
@@ -8471,7 +8471,7 @@
         </is>
       </c>
       <c r="D130" s="4" t="n">
-        <v>18.2</v>
+        <v>30</v>
       </c>
       <c r="E130" s="5" t="n">
         <v>1.03</v>
@@ -8524,12 +8524,12 @@
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>YAMBUKWF</t>
+          <t>FSWF1</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>Yambuk Wind Farm</t>
+          <t>Ferguson South Wind Farm</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
@@ -8538,25 +8538,15 @@
         </is>
       </c>
       <c r="D131" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="E131" s="5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="F131" s="5" t="n">
-        <v>1.0339</v>
-      </c>
-      <c r="G131" s="5" t="n">
-        <v>1.0322</v>
-      </c>
-      <c r="H131" s="5" t="n">
-        <v>1.0149</v>
-      </c>
-      <c r="I131" s="5" t="n">
-        <v>1.0019</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="E131" s="5" t="inlineStr"/>
+      <c r="F131" s="5" t="inlineStr"/>
+      <c r="G131" s="5" t="inlineStr"/>
+      <c r="H131" s="5" t="inlineStr"/>
+      <c r="I131" s="5" t="inlineStr"/>
       <c r="J131" s="5" t="n">
-        <v>1.0063</v>
+        <v>1.0079</v>
       </c>
       <c r="K131" s="5" t="n">
         <v>1.0035</v>
@@ -8591,12 +8581,12 @@
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>TIMWEST</t>
+          <t>OAKLAND1</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>Timboon West Wind Farm</t>
+          <t>Oaklands Hill Wind Farm</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
@@ -8605,11 +8595,17 @@
         </is>
       </c>
       <c r="D132" s="4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="E132" s="5" t="inlineStr"/>
-      <c r="F132" s="5" t="inlineStr"/>
-      <c r="G132" s="5" t="inlineStr"/>
+        <v>67</v>
+      </c>
+      <c r="E132" s="5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="F132" s="5" t="n">
+        <v>1.0339</v>
+      </c>
+      <c r="G132" s="5" t="n">
+        <v>1.0322</v>
+      </c>
       <c r="H132" s="5" t="n">
         <v>1.0149</v>
       </c>
@@ -8652,12 +8648,12 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>OAKLAND1</t>
+          <t>CODRNGTON</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>Oaklands Hill Wind Farm</t>
+          <t>Codrington Wind Farm</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
@@ -8666,7 +8662,7 @@
         </is>
       </c>
       <c r="D133" s="4" t="n">
-        <v>67</v>
+        <v>18.2</v>
       </c>
       <c r="E133" s="5" t="n">
         <v>1.03</v>
@@ -8719,12 +8715,12 @@
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>FSWF1</t>
+          <t>MLWF1</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>Ferguson South Wind Farm</t>
+          <t>Mortons Lane Wind Farm</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
@@ -8733,15 +8729,25 @@
         </is>
       </c>
       <c r="D134" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="E134" s="5" t="inlineStr"/>
-      <c r="F134" s="5" t="inlineStr"/>
-      <c r="G134" s="5" t="inlineStr"/>
-      <c r="H134" s="5" t="inlineStr"/>
-      <c r="I134" s="5" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="E134" s="5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="F134" s="5" t="n">
+        <v>1.0339</v>
+      </c>
+      <c r="G134" s="5" t="n">
+        <v>1.0322</v>
+      </c>
+      <c r="H134" s="5" t="n">
+        <v>1.0149</v>
+      </c>
+      <c r="I134" s="5" t="n">
+        <v>1.0019</v>
+      </c>
       <c r="J134" s="5" t="n">
-        <v>1.0079</v>
+        <v>1.0063</v>
       </c>
       <c r="K134" s="5" t="n">
         <v>1.0035</v>
@@ -8776,12 +8782,12 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>MLWF1</t>
+          <t>TIMWEST</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>Mortons Lane Wind Farm</t>
+          <t>Timboon West Wind Farm</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
@@ -8790,17 +8796,11 @@
         </is>
       </c>
       <c r="D135" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="E135" s="5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="F135" s="5" t="n">
-        <v>1.0339</v>
-      </c>
-      <c r="G135" s="5" t="n">
-        <v>1.0322</v>
-      </c>
+        <v>7.2</v>
+      </c>
+      <c r="E135" s="5" t="inlineStr"/>
+      <c r="F135" s="5" t="inlineStr"/>
+      <c r="G135" s="5" t="inlineStr"/>
       <c r="H135" s="5" t="n">
         <v>1.0149</v>
       </c>
@@ -9292,7 +9292,7 @@
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>HASTING3</t>
+          <t>HASTING2</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
@@ -9300,13 +9300,9 @@
           <t>Hastings Generation Site</t>
         </is>
       </c>
-      <c r="C143" s="3" t="inlineStr">
-        <is>
-          <t>Fossil</t>
-        </is>
-      </c>
+      <c r="C143" s="3" t="inlineStr"/>
       <c r="D143" s="4" t="n">
-        <v>14.817</v>
+        <v>14</v>
       </c>
       <c r="E143" s="5" t="inlineStr"/>
       <c r="F143" s="5" t="inlineStr"/>
@@ -9343,7 +9339,7 @@
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>HASTING2</t>
+          <t>HASTING3</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -9351,9 +9347,13 @@
           <t>Hastings Generation Site</t>
         </is>
       </c>
-      <c r="C144" s="3" t="inlineStr"/>
+      <c r="C144" s="3" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
       <c r="D144" s="4" t="n">
-        <v>14</v>
+        <v>14.817</v>
       </c>
       <c r="E144" s="5" t="inlineStr"/>
       <c r="F144" s="5" t="inlineStr"/>
@@ -9449,30 +9449,30 @@
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>WOLLERT1</t>
+          <t>RUBICON</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>Wollert Renewable Energy Facility</t>
+          <t>Rubicon Mountain Streams Station</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>Other Renewable</t>
+          <t>Hydro</t>
         </is>
       </c>
       <c r="D146" s="4" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>0.9987</v>
+        <v>1</v>
       </c>
       <c r="F146" s="5" t="n">
-        <v>0.9985000000000001</v>
+        <v>1</v>
       </c>
       <c r="G146" s="5" t="n">
-        <v>0.998</v>
+        <v>1</v>
       </c>
       <c r="H146" s="5" t="n">
         <v>0.9979</v>
@@ -9516,12 +9516,12 @@
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>RUBICON</t>
+          <t>EILDON3</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>Rubicon Mountain Streams Station</t>
+          <t>Eildon Power Station</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
@@ -9530,16 +9530,16 @@
         </is>
       </c>
       <c r="D147" s="4" t="n">
-        <v>13</v>
+        <v>4.5</v>
       </c>
       <c r="E147" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F147" s="5" t="n">
-        <v>1</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="G147" s="5" t="n">
-        <v>1</v>
+        <v>0.998</v>
       </c>
       <c r="H147" s="5" t="n">
         <v>0.9979</v>
@@ -9583,24 +9583,24 @@
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>EILDON3</t>
+          <t>WOLLERT1</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>Eildon Power Station</t>
+          <t>Wollert Renewable Energy Facility</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>Hydro</t>
+          <t>Other Renewable</t>
         </is>
       </c>
       <c r="D148" s="4" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>1</v>
+        <v>0.9987</v>
       </c>
       <c r="F148" s="5" t="n">
         <v>0.9985000000000001</v>
@@ -9776,7 +9776,7 @@
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>LNGS2</t>
+          <t>LNGS1</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
@@ -9843,7 +9843,7 @@
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>LNGS1</t>
+          <t>LNGS2</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -10174,12 +10174,12 @@
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>YAWWF1</t>
+          <t>CBWF1</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>Yawong Wind Farm</t>
+          <t>Coonooer Bridge Wind Farm</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
@@ -10188,13 +10188,19 @@
         </is>
       </c>
       <c r="D157" s="4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="E157" s="5" t="inlineStr"/>
-      <c r="F157" s="5" t="inlineStr"/>
-      <c r="G157" s="5" t="inlineStr"/>
+        <v>19.8</v>
+      </c>
+      <c r="E157" s="5" t="n">
+        <v>1.0672</v>
+      </c>
+      <c r="F157" s="5" t="n">
+        <v>1.0664</v>
+      </c>
+      <c r="G157" s="5" t="n">
+        <v>1.0398</v>
+      </c>
       <c r="H157" s="5" t="n">
-        <v>1.0136</v>
+        <v>1.0139</v>
       </c>
       <c r="I157" s="5" t="n">
         <v>1.0012</v>
@@ -10235,12 +10241,12 @@
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>CBWF1</t>
+          <t>YAWWF1</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>Coonooer Bridge Wind Farm</t>
+          <t>Yawong Wind Farm</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
@@ -10249,19 +10255,13 @@
         </is>
       </c>
       <c r="D158" s="4" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="E158" s="5" t="n">
-        <v>1.0672</v>
-      </c>
-      <c r="F158" s="5" t="n">
-        <v>1.0664</v>
-      </c>
-      <c r="G158" s="5" t="n">
-        <v>1.0398</v>
-      </c>
+        <v>7.2</v>
+      </c>
+      <c r="E158" s="5" t="inlineStr"/>
+      <c r="F158" s="5" t="inlineStr"/>
+      <c r="G158" s="5" t="inlineStr"/>
       <c r="H158" s="5" t="n">
-        <v>1.0139</v>
+        <v>1.0136</v>
       </c>
       <c r="I158" s="5" t="n">
         <v>1.0012</v>
@@ -10302,12 +10302,12 @@
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
         <is>
-          <t>TATURA01</t>
+          <t>SHEP1</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>Tatura Biomass Generator</t>
+          <t>Shepparton Wastewater Treatment Facility</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
@@ -10369,12 +10369,12 @@
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>SHEP1</t>
+          <t>TATURA01</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>Shepparton Wastewater Treatment Facility</t>
+          <t>Tatura Biomass Generator</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
@@ -10511,8 +10511,14 @@
           <t>Jindabyne Pump At Guthega</t>
         </is>
       </c>
-      <c r="C162" s="3" t="n"/>
-      <c r="D162" s="3" t="inlineStr"/>
+      <c r="C162" s="3" t="inlineStr">
+        <is>
+          <t>Hydro</t>
+        </is>
+      </c>
+      <c r="D162" s="4" t="n">
+        <v>70</v>
+      </c>
       <c r="E162" s="5" t="n">
         <v>1.138</v>
       </c>
@@ -10564,12 +10570,12 @@
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>MORNL1</t>
+          <t>APS</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>Energy Brix Complex Power Station</t>
+          <t>ANGELSEA POWER STATION</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
@@ -10578,10 +10584,10 @@
         </is>
       </c>
       <c r="D163" s="4" t="n">
-        <v>25</v>
+        <v>165</v>
       </c>
       <c r="E163" s="5" t="n">
-        <v>0.9799</v>
+        <v>0.9915</v>
       </c>
       <c r="F163" s="5" t="inlineStr"/>
       <c r="G163" s="5" t="inlineStr"/>
@@ -10605,12 +10611,12 @@
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>APS</t>
+          <t>MORNL1</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>ANGELSEA POWER STATION</t>
+          <t>Energy Brix Complex Power Station</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
@@ -10619,10 +10625,10 @@
         </is>
       </c>
       <c r="D164" s="4" t="n">
-        <v>165</v>
+        <v>25</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>0.9915</v>
+        <v>0.9799</v>
       </c>
       <c r="F164" s="5" t="inlineStr"/>
       <c r="G164" s="5" t="inlineStr"/>
@@ -10683,7 +10689,7 @@
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>MOR3</t>
+          <t>MOR2</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
@@ -10720,7 +10726,7 @@
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
         <is>
-          <t>MOR2</t>
+          <t>MOR3</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
@@ -10843,7 +10849,7 @@
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>HWPS6</t>
+          <t>HWPNL1</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -10857,7 +10863,7 @@
         </is>
       </c>
       <c r="D170" s="4" t="n">
-        <v>200</v>
+        <v>25</v>
       </c>
       <c r="E170" s="5" t="n">
         <v>0.9723000000000001</v>
@@ -10886,7 +10892,7 @@
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
         <is>
-          <t>HWPS5</t>
+          <t>HWPS1</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
@@ -10900,7 +10906,7 @@
         </is>
       </c>
       <c r="D171" s="4" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="E171" s="5" t="n">
         <v>0.9723000000000001</v>
@@ -10929,7 +10935,7 @@
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>HWPS4</t>
+          <t>HWPS2</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -10943,7 +10949,7 @@
         </is>
       </c>
       <c r="D172" s="4" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="E172" s="5" t="n">
         <v>0.9723000000000001</v>
@@ -11015,7 +11021,7 @@
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>HWPS2</t>
+          <t>HWPS4</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -11029,7 +11035,7 @@
         </is>
       </c>
       <c r="D174" s="4" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="E174" s="5" t="n">
         <v>0.9723000000000001</v>
@@ -11058,7 +11064,7 @@
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
         <is>
-          <t>HWPS1</t>
+          <t>HWPS5</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
@@ -11072,7 +11078,7 @@
         </is>
       </c>
       <c r="D175" s="4" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="E175" s="5" t="n">
         <v>0.9723000000000001</v>
@@ -11101,7 +11107,7 @@
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>HWPNL1</t>
+          <t>HWPS6</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -11115,7 +11121,7 @@
         </is>
       </c>
       <c r="D176" s="4" t="n">
-        <v>25</v>
+        <v>200</v>
       </c>
       <c r="E176" s="5" t="n">
         <v>0.9723000000000001</v>
@@ -11144,12 +11150,12 @@
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
         <is>
-          <t>WYNDW</t>
+          <t>MORNW</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>Wyndham Waste Disposal Facility</t>
+          <t>Mornington Waste Disposal Facility</t>
         </is>
       </c>
       <c r="C177" s="3" t="inlineStr">
@@ -11161,13 +11167,13 @@
         <v>1</v>
       </c>
       <c r="E177" s="5" t="n">
-        <v>1.0032</v>
+        <v>0.9923999999999999</v>
       </c>
       <c r="F177" s="5" t="n">
-        <v>1.0068</v>
+        <v>0.9925</v>
       </c>
       <c r="G177" s="5" t="n">
-        <v>1.0084</v>
+        <v>0.9963</v>
       </c>
       <c r="H177" s="5" t="inlineStr"/>
       <c r="I177" s="5" t="inlineStr"/>
@@ -11189,12 +11195,12 @@
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>MORNW</t>
+          <t>WYNDW</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>Mornington Waste Disposal Facility</t>
+          <t>Wyndham Waste Disposal Facility</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
@@ -11206,13 +11212,13 @@
         <v>1</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>0.9923999999999999</v>
+        <v>1.0032</v>
       </c>
       <c r="F178" s="5" t="n">
-        <v>0.9925</v>
+        <v>1.0068</v>
       </c>
       <c r="G178" s="5" t="n">
-        <v>0.9963</v>
+        <v>1.0084</v>
       </c>
       <c r="H178" s="5" t="inlineStr"/>
       <c r="I178" s="5" t="inlineStr"/>
@@ -11340,12 +11346,12 @@
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t>BROADMDW</t>
+          <t>SVALE1</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>Broadmeadows Landfill Gas Power Station</t>
+          <t>Springvale Landfill Gas Power Station</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
@@ -11357,31 +11363,31 @@
         <v>5</v>
       </c>
       <c r="E181" s="5" t="n">
-        <v>1</v>
+        <v>0.997</v>
       </c>
       <c r="F181" s="5" t="n">
-        <v>1</v>
+        <v>0.9972</v>
       </c>
       <c r="G181" s="5" t="n">
-        <v>1</v>
+        <v>0.9989</v>
       </c>
       <c r="H181" s="5" t="n">
-        <v>1</v>
+        <v>0.9986</v>
       </c>
       <c r="I181" s="5" t="n">
-        <v>1</v>
+        <v>0.9987</v>
       </c>
       <c r="J181" s="5" t="n">
-        <v>1</v>
+        <v>0.9984</v>
       </c>
       <c r="K181" s="5" t="n">
-        <v>1</v>
+        <v>0.9957</v>
       </c>
       <c r="L181" s="5" t="n">
-        <v>1</v>
+        <v>0.9972</v>
       </c>
       <c r="M181" s="5" t="n">
-        <v>1</v>
+        <v>1.0001</v>
       </c>
       <c r="N181" s="5" t="inlineStr"/>
       <c r="O181" s="5" t="inlineStr"/>
@@ -11397,12 +11403,12 @@
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>SVALE1</t>
+          <t>BROADMDW</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>Springvale Landfill Gas Power Station</t>
+          <t>Broadmeadows Landfill Gas Power Station</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
@@ -11414,31 +11420,31 @@
         <v>5</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>0.997</v>
+        <v>1</v>
       </c>
       <c r="F182" s="5" t="n">
-        <v>0.9972</v>
+        <v>1</v>
       </c>
       <c r="G182" s="5" t="n">
-        <v>0.9989</v>
+        <v>1</v>
       </c>
       <c r="H182" s="5" t="n">
-        <v>0.9986</v>
+        <v>1</v>
       </c>
       <c r="I182" s="5" t="n">
-        <v>0.9987</v>
+        <v>1</v>
       </c>
       <c r="J182" s="5" t="n">
-        <v>0.9984</v>
+        <v>1</v>
       </c>
       <c r="K182" s="5" t="n">
-        <v>0.9957</v>
+        <v>1</v>
       </c>
       <c r="L182" s="5" t="n">
-        <v>0.9972</v>
+        <v>1</v>
       </c>
       <c r="M182" s="5" t="n">
-        <v>1.0001</v>
+        <v>1</v>
       </c>
       <c r="N182" s="5" t="inlineStr"/>
       <c r="O182" s="5" t="inlineStr"/>
@@ -11501,12 +11507,12 @@
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>GANNBG1</t>
+          <t>BULBESG1</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>Gannawarra Energy Storage System</t>
+          <t>Bulgana Green Power Hub</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
@@ -11515,31 +11521,25 @@
         </is>
       </c>
       <c r="D184" s="4" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E184" s="5" t="inlineStr"/>
       <c r="F184" s="5" t="inlineStr"/>
       <c r="G184" s="5" t="inlineStr"/>
-      <c r="H184" s="5" t="n">
-        <v>1.007</v>
-      </c>
-      <c r="I184" s="5" t="n">
-        <v>0.9643</v>
-      </c>
-      <c r="J184" s="5" t="n">
-        <v>0.9792999999999999</v>
-      </c>
+      <c r="H184" s="5" t="inlineStr"/>
+      <c r="I184" s="5" t="inlineStr"/>
+      <c r="J184" s="5" t="inlineStr"/>
       <c r="K184" s="5" t="n">
-        <v>0.9772999999999999</v>
+        <v>0.8949</v>
       </c>
       <c r="L184" s="5" t="n">
-        <v>1.0026</v>
+        <v>0.8839</v>
       </c>
       <c r="M184" s="5" t="n">
-        <v>1.029</v>
+        <v>0.8821</v>
       </c>
       <c r="N184" s="5" t="n">
-        <v>1.0155</v>
+        <v>0.8733</v>
       </c>
       <c r="O184" s="5" t="inlineStr"/>
       <c r="P184" s="5" t="inlineStr"/>
@@ -11554,12 +11554,12 @@
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
         <is>
-          <t>BULBESG1</t>
+          <t>HBESSG1</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>Bulgana Green Power Hub</t>
+          <t>Hazelwood Battery Energy Storage System</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
@@ -11568,7 +11568,7 @@
         </is>
       </c>
       <c r="D185" s="4" t="n">
-        <v>24</v>
+        <v>200</v>
       </c>
       <c r="E185" s="5" t="inlineStr"/>
       <c r="F185" s="5" t="inlineStr"/>
@@ -11576,17 +11576,15 @@
       <c r="H185" s="5" t="inlineStr"/>
       <c r="I185" s="5" t="inlineStr"/>
       <c r="J185" s="5" t="inlineStr"/>
-      <c r="K185" s="5" t="n">
-        <v>0.8949</v>
-      </c>
+      <c r="K185" s="5" t="inlineStr"/>
       <c r="L185" s="5" t="n">
-        <v>0.8839</v>
+        <v>0.9785</v>
       </c>
       <c r="M185" s="5" t="n">
-        <v>0.8821</v>
+        <v>0.9789</v>
       </c>
       <c r="N185" s="5" t="n">
-        <v>0.8733</v>
+        <v>0.9804</v>
       </c>
       <c r="O185" s="5" t="inlineStr"/>
       <c r="P185" s="5" t="inlineStr"/>
@@ -11601,37 +11599,41 @@
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t>HBESSG1</t>
+          <t>FNWF1</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>Hazelwood Battery Energy Storage System</t>
+          <t>Ferguson North Wind Farm</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D186" s="4" t="n">
-        <v>200</v>
+        <v>4</v>
       </c>
       <c r="E186" s="5" t="inlineStr"/>
       <c r="F186" s="5" t="inlineStr"/>
       <c r="G186" s="5" t="inlineStr"/>
       <c r="H186" s="5" t="inlineStr"/>
       <c r="I186" s="5" t="inlineStr"/>
-      <c r="J186" s="5" t="inlineStr"/>
-      <c r="K186" s="5" t="inlineStr"/>
+      <c r="J186" s="5" t="n">
+        <v>1.0079</v>
+      </c>
+      <c r="K186" s="5" t="n">
+        <v>1.0035</v>
+      </c>
       <c r="L186" s="5" t="n">
-        <v>0.9785</v>
+        <v>0.9972</v>
       </c>
       <c r="M186" s="5" t="n">
-        <v>0.9789</v>
+        <v>0.9933</v>
       </c>
       <c r="N186" s="5" t="n">
-        <v>0.9804</v>
+        <v>0.9993</v>
       </c>
       <c r="O186" s="5" t="inlineStr"/>
       <c r="P186" s="5" t="inlineStr"/>
@@ -11646,12 +11648,12 @@
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
         <is>
-          <t>BALBG1</t>
+          <t>GANNBG1</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>Ballarat Battery Energy Storage System</t>
+          <t>Gannawarra Energy Storage System</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
@@ -11666,25 +11668,25 @@
       <c r="F187" s="5" t="inlineStr"/>
       <c r="G187" s="5" t="inlineStr"/>
       <c r="H187" s="5" t="n">
-        <v>0.9948</v>
+        <v>1.007</v>
       </c>
       <c r="I187" s="5" t="n">
-        <v>0.9634</v>
+        <v>0.9643</v>
       </c>
       <c r="J187" s="5" t="n">
-        <v>0.9643</v>
+        <v>0.9792999999999999</v>
       </c>
       <c r="K187" s="5" t="n">
-        <v>0.9573</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="L187" s="5" t="n">
-        <v>0.9663</v>
+        <v>1.0026</v>
       </c>
       <c r="M187" s="5" t="n">
-        <v>0.9756</v>
+        <v>1.029</v>
       </c>
       <c r="N187" s="5" t="n">
-        <v>0.9713000000000001</v>
+        <v>1.0155</v>
       </c>
       <c r="O187" s="5" t="inlineStr"/>
       <c r="P187" s="5" t="inlineStr"/>
@@ -11744,41 +11746,45 @@
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
         <is>
-          <t>FNWF1</t>
+          <t>BALBG1</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
         <is>
-          <t>Ferguson North Wind Farm</t>
+          <t>Ballarat Battery Energy Storage System</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D189" s="4" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="E189" s="5" t="inlineStr"/>
       <c r="F189" s="5" t="inlineStr"/>
       <c r="G189" s="5" t="inlineStr"/>
-      <c r="H189" s="5" t="inlineStr"/>
-      <c r="I189" s="5" t="inlineStr"/>
+      <c r="H189" s="5" t="n">
+        <v>0.9948</v>
+      </c>
+      <c r="I189" s="5" t="n">
+        <v>0.9634</v>
+      </c>
       <c r="J189" s="5" t="n">
-        <v>1.0079</v>
+        <v>0.9643</v>
       </c>
       <c r="K189" s="5" t="n">
-        <v>1.0035</v>
+        <v>0.9573</v>
       </c>
       <c r="L189" s="5" t="n">
-        <v>0.9972</v>
+        <v>0.9663</v>
       </c>
       <c r="M189" s="5" t="n">
-        <v>0.9933</v>
+        <v>0.9756</v>
       </c>
       <c r="N189" s="5" t="n">
-        <v>0.9993</v>
+        <v>0.9713000000000001</v>
       </c>
       <c r="O189" s="5" t="inlineStr"/>
       <c r="P189" s="5" t="inlineStr"/>
@@ -11793,21 +11799,21 @@
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
         <is>
-          <t>CHPSTWF1</t>
+          <t>BBASEHOS</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>Chepstowe Wind Farm</t>
+          <t>Ballarat Base Hospital Plant</t>
         </is>
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D190" s="4" t="n">
-        <v>6.15</v>
+        <v>1</v>
       </c>
       <c r="E190" s="5" t="n">
         <v>1.0207</v>
@@ -11854,21 +11860,21 @@
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
         <is>
-          <t>BBASEHOS</t>
+          <t>CHPSTWF1</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>Ballarat Base Hospital Plant</t>
+          <t>Chepstowe Wind Farm</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D191" s="4" t="n">
-        <v>1</v>
+        <v>6.15</v>
       </c>
       <c r="E191" s="5" t="n">
         <v>1.0207</v>
@@ -12065,15 +12071,21 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>MUWAWF2</t>
+          <t>MUWAWF1</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr"/>
       <c r="C3" s="5" t="inlineStr"/>
       <c r="D3" s="5" t="inlineStr"/>
-      <c r="E3" s="5" t="inlineStr"/>
-      <c r="F3" s="5" t="inlineStr"/>
-      <c r="G3" s="5" t="inlineStr"/>
+      <c r="E3" s="5" t="n">
+        <v>0.9549</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>0.8885</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>0.8885</v>
+      </c>
       <c r="H3" s="5" t="n">
         <v>0.8883</v>
       </c>
@@ -12099,21 +12111,15 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>MUWAWF1</t>
+          <t>MUWAWF2</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr"/>
       <c r="C4" s="5" t="inlineStr"/>
       <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="n">
-        <v>0.9549</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>0.8885</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>0.8885</v>
-      </c>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr"/>
       <c r="H4" s="5" t="n">
         <v>0.8883</v>
       </c>
@@ -12399,14 +12405,18 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>YATSF1</t>
+          <t>KARSF1</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr"/>
       <c r="C12" s="5" t="inlineStr"/>
       <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="n">
+        <v>0.9472</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0.8097</v>
+      </c>
       <c r="G12" s="5" t="n">
         <v>0.8045</v>
       </c>
@@ -12435,18 +12445,14 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>KARSF1</t>
+          <t>YATSF1</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr"/>
       <c r="C13" s="5" t="inlineStr"/>
       <c r="D13" s="5" t="inlineStr"/>
-      <c r="E13" s="5" t="n">
-        <v>0.9472</v>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>0.8097</v>
-      </c>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="5" t="inlineStr"/>
       <c r="G13" s="5" t="n">
         <v>0.8045</v>
       </c>
@@ -12475,14 +12481,14 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>BANN1</t>
+          <t>WEMENSF1</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr"/>
       <c r="C14" s="5" t="inlineStr"/>
       <c r="D14" s="5" t="inlineStr"/>
       <c r="E14" s="5" t="n">
-        <v>1.0062</v>
+        <v>0.9262</v>
       </c>
       <c r="F14" s="5" t="n">
         <v>0.8246</v>
@@ -12515,14 +12521,14 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>WEMENSF1</t>
+          <t>BANN1</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr"/>
       <c r="C15" s="5" t="inlineStr"/>
       <c r="D15" s="5" t="inlineStr"/>
       <c r="E15" s="5" t="n">
-        <v>0.9262</v>
+        <v>1.0062</v>
       </c>
       <c r="F15" s="5" t="n">
         <v>0.8246</v>
@@ -12555,7 +12561,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>WUNUSF1</t>
+          <t>GIRGSF</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr"/>
@@ -12583,30 +12589,18 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>NUMURSF1</t>
+          <t>WUNUSF1</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr"/>
       <c r="C17" s="5" t="inlineStr"/>
       <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="n">
-        <v>0.982</v>
-      </c>
-      <c r="F17" s="5" t="n">
-        <v>0.9896</v>
-      </c>
-      <c r="G17" s="5" t="n">
-        <v>0.9945000000000001</v>
-      </c>
-      <c r="H17" s="5" t="n">
-        <v>0.9963</v>
-      </c>
-      <c r="I17" s="5" t="n">
-        <v>0.9715</v>
-      </c>
-      <c r="J17" s="5" t="n">
-        <v>0.9738</v>
-      </c>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr"/>
+      <c r="I17" s="5" t="inlineStr"/>
+      <c r="J17" s="5" t="inlineStr"/>
       <c r="K17" s="5" t="n">
         <v>0.9477</v>
       </c>
@@ -12623,18 +12617,30 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>GIRGSF</t>
+          <t>NUMURSF1</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr"/>
       <c r="C18" s="5" t="inlineStr"/>
       <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="n">
+        <v>0.982</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0.9896</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0.9945000000000001</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>0.9963</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>0.9715</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>0.9738</v>
+      </c>
       <c r="K18" s="5" t="n">
         <v>0.9477</v>
       </c>
@@ -12831,14 +12837,20 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>COHUNSF1</t>
+          <t>GANNSF1</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr"/>
       <c r="C25" s="5" t="inlineStr"/>
-      <c r="D25" s="5" t="inlineStr"/>
-      <c r="E25" s="5" t="inlineStr"/>
-      <c r="F25" s="5" t="inlineStr"/>
+      <c r="D25" s="5" t="n">
+        <v>1.044</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>0.9729</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>0.8994</v>
+      </c>
       <c r="G25" s="5" t="n">
         <v>0.8863</v>
       </c>
@@ -12867,20 +12879,14 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>GANNSF1</t>
+          <t>COHUNSF1</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr"/>
       <c r="C26" s="5" t="inlineStr"/>
-      <c r="D26" s="5" t="n">
-        <v>1.044</v>
-      </c>
-      <c r="E26" s="5" t="n">
-        <v>0.9729</v>
-      </c>
-      <c r="F26" s="5" t="n">
-        <v>0.8994</v>
-      </c>
+      <c r="D26" s="5" t="inlineStr"/>
+      <c r="E26" s="5" t="inlineStr"/>
+      <c r="F26" s="5" t="inlineStr"/>
       <c r="G26" s="5" t="n">
         <v>0.8863</v>
       </c>
@@ -13013,7 +13019,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>BRYB2WF2</t>
+          <t>BRYB1WF1</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr"/>
@@ -13021,8 +13027,12 @@
       <c r="D30" s="5" t="inlineStr"/>
       <c r="E30" s="5" t="inlineStr"/>
       <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
+      <c r="G30" s="5" t="n">
+        <v>0.9482</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>0.9431</v>
+      </c>
       <c r="I30" s="5" t="n">
         <v>0.9496</v>
       </c>
@@ -13045,7 +13055,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>BRYB1WF1</t>
+          <t>BRYB2WF2</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr"/>
@@ -13053,12 +13063,8 @@
       <c r="D31" s="5" t="inlineStr"/>
       <c r="E31" s="5" t="inlineStr"/>
       <c r="F31" s="5" t="inlineStr"/>
-      <c r="G31" s="5" t="n">
-        <v>0.9482</v>
-      </c>
-      <c r="H31" s="5" t="n">
-        <v>0.9431</v>
-      </c>
+      <c r="G31" s="5" t="inlineStr"/>
+      <c r="H31" s="5" t="inlineStr"/>
       <c r="I31" s="5" t="n">
         <v>0.9496</v>
       </c>
@@ -13277,14 +13283,16 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>MOORAWF1</t>
+          <t>ELAINWF1</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr"/>
       <c r="C37" s="5" t="inlineStr"/>
       <c r="D37" s="5" t="inlineStr"/>
       <c r="E37" s="5" t="inlineStr"/>
-      <c r="F37" s="5" t="inlineStr"/>
+      <c r="F37" s="5" t="n">
+        <v>0.965</v>
+      </c>
       <c r="G37" s="5" t="n">
         <v>0.9500999999999999</v>
       </c>
@@ -13313,92 +13321,90 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>MOORABS1</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr"/>
-      <c r="C38" s="5" t="inlineStr"/>
-      <c r="D38" s="5" t="inlineStr"/>
-      <c r="E38" s="5" t="inlineStr"/>
-      <c r="F38" s="5" t="inlineStr"/>
-      <c r="G38" s="5" t="inlineStr"/>
-      <c r="H38" s="5" t="inlineStr"/>
-      <c r="I38" s="5" t="inlineStr"/>
-      <c r="J38" s="5" t="inlineStr"/>
-      <c r="K38" s="5" t="inlineStr"/>
+          <t>MERCER01</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>1.0033</v>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>1.0048</v>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>1.001</v>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>0.9909</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>0.9500999999999999</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>0.9459</v>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>0.948</v>
+      </c>
+      <c r="J38" s="5" t="n">
+        <v>0.9576</v>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>0.9475</v>
+      </c>
       <c r="L38" s="5" t="inlineStr"/>
       <c r="M38" s="5" t="n">
         <v>0.9569</v>
       </c>
-      <c r="N38" s="5" t="n">
-        <v>0.9569</v>
-      </c>
+      <c r="N38" s="5" t="inlineStr"/>
       <c r="O38" s="5" t="n">
         <v>0.9556</v>
       </c>
-      <c r="P38" s="5" t="n">
-        <v>0.9556</v>
-      </c>
+      <c r="P38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>MERCER01</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="n">
-        <v>1.0033</v>
-      </c>
-      <c r="C39" s="5" t="n">
-        <v>1.0048</v>
-      </c>
-      <c r="D39" s="5" t="n">
-        <v>1.001</v>
-      </c>
-      <c r="E39" s="5" t="n">
-        <v>0.9909</v>
-      </c>
-      <c r="F39" s="5" t="n">
-        <v>0.965</v>
-      </c>
-      <c r="G39" s="5" t="n">
-        <v>0.9500999999999999</v>
-      </c>
-      <c r="H39" s="5" t="n">
-        <v>0.9459</v>
-      </c>
-      <c r="I39" s="5" t="n">
-        <v>0.948</v>
-      </c>
-      <c r="J39" s="5" t="n">
-        <v>0.9576</v>
-      </c>
-      <c r="K39" s="5" t="n">
-        <v>0.9475</v>
-      </c>
+          <t>MOORABS1</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr"/>
+      <c r="C39" s="5" t="inlineStr"/>
+      <c r="D39" s="5" t="inlineStr"/>
+      <c r="E39" s="5" t="inlineStr"/>
+      <c r="F39" s="5" t="inlineStr"/>
+      <c r="G39" s="5" t="inlineStr"/>
+      <c r="H39" s="5" t="inlineStr"/>
+      <c r="I39" s="5" t="inlineStr"/>
+      <c r="J39" s="5" t="inlineStr"/>
+      <c r="K39" s="5" t="inlineStr"/>
       <c r="L39" s="5" t="inlineStr"/>
       <c r="M39" s="5" t="n">
         <v>0.9569</v>
       </c>
-      <c r="N39" s="5" t="inlineStr"/>
+      <c r="N39" s="5" t="n">
+        <v>0.9569</v>
+      </c>
       <c r="O39" s="5" t="n">
         <v>0.9556</v>
       </c>
-      <c r="P39" s="5" t="inlineStr"/>
+      <c r="P39" s="5" t="n">
+        <v>0.9556</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>ELAINWF1</t>
+          <t>MOORAWF1</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr"/>
       <c r="C40" s="5" t="inlineStr"/>
       <c r="D40" s="5" t="inlineStr"/>
       <c r="E40" s="5" t="inlineStr"/>
-      <c r="F40" s="5" t="n">
-        <v>0.965</v>
-      </c>
+      <c r="F40" s="5" t="inlineStr"/>
       <c r="G40" s="5" t="n">
         <v>0.9500999999999999</v>
       </c>
@@ -13427,7 +13433,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>MURRAY</t>
+          <t>MURAYNL3</t>
         </is>
       </c>
       <c r="B41" s="5" t="n">
@@ -13473,7 +13479,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>MURAYNL1</t>
+          <t>MURAYNL2</t>
         </is>
       </c>
       <c r="B42" s="5" t="n">
@@ -13519,7 +13525,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>MURAYNL3</t>
+          <t>MURAYNL1</t>
         </is>
       </c>
       <c r="B43" s="5" t="n">
@@ -13565,7 +13571,7 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>MURAYNL2</t>
+          <t>MURRAY</t>
         </is>
       </c>
       <c r="B44" s="5" t="n">
@@ -13657,7 +13663,7 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>YWNL1</t>
+          <t>YWPS2</t>
         </is>
       </c>
       <c r="B46" s="5" t="n">
@@ -13703,7 +13709,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>YWPS2</t>
+          <t>YWPS3</t>
         </is>
       </c>
       <c r="B47" s="5" t="n">
@@ -13749,7 +13755,7 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>YWPS3</t>
+          <t>YWNL1</t>
         </is>
       </c>
       <c r="B48" s="5" t="n">
@@ -13841,7 +13847,7 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>BAPS</t>
+          <t>DARTM1</t>
         </is>
       </c>
       <c r="B50" s="5" t="n">
@@ -13887,7 +13893,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>DARTM1</t>
+          <t>BAPS</t>
         </is>
       </c>
       <c r="B51" s="5" t="n">
@@ -14009,23 +14015,19 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>CHALLHWF</t>
-        </is>
-      </c>
-      <c r="B54" s="5" t="n">
-        <v>1.0988</v>
-      </c>
-      <c r="C54" s="5" t="n">
-        <v>1.0988</v>
-      </c>
+          <t>MAROOWF1</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr"/>
+      <c r="C54" s="5" t="inlineStr"/>
       <c r="D54" s="5" t="n">
-        <v>1.0988</v>
+        <v>1.016</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>0.9957</v>
+        <v>1.0016</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>0.9193</v>
+        <v>0.9716</v>
       </c>
       <c r="G54" s="5" t="n">
         <v>0.9711</v>
@@ -14055,11 +14057,15 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>YSWF1</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="inlineStr"/>
-      <c r="C55" s="5" t="inlineStr"/>
+          <t>HEPWIND1</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>1.0207</v>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>1.0209</v>
+      </c>
       <c r="D55" s="5" t="n">
         <v>1.016</v>
       </c>
@@ -14097,19 +14103,23 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>MAROOWF1</t>
-        </is>
-      </c>
-      <c r="B56" s="5" t="inlineStr"/>
-      <c r="C56" s="5" t="inlineStr"/>
+          <t>CHALLHWF</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>1.0988</v>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>1.0988</v>
+      </c>
       <c r="D56" s="5" t="n">
-        <v>1.016</v>
+        <v>1.0988</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>1.0016</v>
+        <v>0.9957</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>0.9716</v>
+        <v>0.9193</v>
       </c>
       <c r="G56" s="5" t="n">
         <v>0.9711</v>
@@ -14139,15 +14149,11 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>HEPWIND1</t>
-        </is>
-      </c>
-      <c r="B57" s="5" t="n">
-        <v>1.0207</v>
-      </c>
-      <c r="C57" s="5" t="n">
-        <v>1.0209</v>
-      </c>
+          <t>YSWF1</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr"/>
+      <c r="C57" s="5" t="inlineStr"/>
       <c r="D57" s="5" t="n">
         <v>1.016</v>
       </c>
@@ -14185,7 +14191,7 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>MURR1-10</t>
+          <t>MURR1-1</t>
         </is>
       </c>
       <c r="B58" s="5" t="n">
@@ -14231,7 +14237,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>MURR1-1</t>
+          <t>MURR1-10</t>
         </is>
       </c>
       <c r="B59" s="5" t="n">
@@ -14277,7 +14283,7 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>MURR1-7</t>
+          <t>MURR1-2</t>
         </is>
       </c>
       <c r="B60" s="5" t="n">
@@ -14323,7 +14329,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>MURR2-4</t>
+          <t>MURR1-4</t>
         </is>
       </c>
       <c r="B61" s="5" t="n">
@@ -14369,7 +14375,7 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>MURR1-2</t>
+          <t>MURR1-3</t>
         </is>
       </c>
       <c r="B62" s="5" t="n">
@@ -14415,7 +14421,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>MURR2-3</t>
+          <t>MURR1-5</t>
         </is>
       </c>
       <c r="B63" s="5" t="n">
@@ -14461,7 +14467,7 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>MURR1-3</t>
+          <t>MURR1-6</t>
         </is>
       </c>
       <c r="B64" s="5" t="n">
@@ -14507,7 +14513,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>MURR1-9</t>
+          <t>MURR1-8</t>
         </is>
       </c>
       <c r="B65" s="5" t="n">
@@ -14553,7 +14559,7 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>MURR1-5</t>
+          <t>MURR1-7</t>
         </is>
       </c>
       <c r="B66" s="5" t="n">
@@ -14599,7 +14605,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>MURR1-6</t>
+          <t>MURR1-9</t>
         </is>
       </c>
       <c r="B67" s="5" t="n">
@@ -14645,7 +14651,7 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>MURR1-8</t>
+          <t>MURR2-1</t>
         </is>
       </c>
       <c r="B68" s="5" t="n">
@@ -14691,7 +14697,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>MURR2-1</t>
+          <t>MURR2-2</t>
         </is>
       </c>
       <c r="B69" s="5" t="n">
@@ -14737,7 +14743,7 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>MURR2-2</t>
+          <t>MURR2-3</t>
         </is>
       </c>
       <c r="B70" s="5" t="n">
@@ -14783,7 +14789,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>MURR1-4</t>
+          <t>MURR2-4</t>
         </is>
       </c>
       <c r="B71" s="5" t="n">
@@ -14863,7 +14869,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>GPWFEST3</t>
+          <t>GPWFEST2</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr"/>
@@ -14891,7 +14897,7 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>GPWFEST2</t>
+          <t>GPWFEST3</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr"/>
@@ -14977,42 +14983,22 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>JLA02</t>
-        </is>
-      </c>
-      <c r="B77" s="5" t="n">
-        <v>0.9667</v>
-      </c>
-      <c r="C77" s="5" t="n">
-        <v>0.9641</v>
-      </c>
-      <c r="D77" s="5" t="n">
-        <v>0.983</v>
-      </c>
-      <c r="E77" s="5" t="n">
-        <v>0.9782999999999999</v>
-      </c>
-      <c r="F77" s="5" t="n">
-        <v>0.9731</v>
-      </c>
-      <c r="G77" s="5" t="n">
-        <v>0.9734</v>
-      </c>
-      <c r="H77" s="5" t="n">
-        <v>0.9755</v>
-      </c>
-      <c r="I77" s="5" t="n">
-        <v>0.9727</v>
-      </c>
-      <c r="J77" s="5" t="n">
-        <v>0.9764</v>
-      </c>
-      <c r="K77" s="5" t="n">
-        <v>0.9789</v>
-      </c>
+          <t>GPWFWST1</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr"/>
+      <c r="C77" s="5" t="inlineStr"/>
+      <c r="D77" s="5" t="inlineStr"/>
+      <c r="E77" s="5" t="inlineStr"/>
+      <c r="F77" s="5" t="inlineStr"/>
+      <c r="G77" s="5" t="inlineStr"/>
+      <c r="H77" s="5" t="inlineStr"/>
+      <c r="I77" s="5" t="inlineStr"/>
+      <c r="J77" s="5" t="inlineStr"/>
+      <c r="K77" s="5" t="inlineStr"/>
       <c r="L77" s="5" t="inlineStr"/>
       <c r="M77" s="5" t="n">
-        <v>0.9768</v>
+        <v>0.9837</v>
       </c>
       <c r="N77" s="5" t="inlineStr"/>
       <c r="O77" s="5" t="n">
@@ -15023,7 +15009,7 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>JLA03</t>
+          <t>JLB03</t>
         </is>
       </c>
       <c r="B78" s="5" t="n">
@@ -15069,7 +15055,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>JLA01</t>
+          <t>JLB01</t>
         </is>
       </c>
       <c r="B79" s="5" t="n">
@@ -15115,7 +15101,7 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>JLB01</t>
+          <t>JLB02</t>
         </is>
       </c>
       <c r="B80" s="5" t="n">
@@ -15207,7 +15193,7 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>JLB03</t>
+          <t>JLA03</t>
         </is>
       </c>
       <c r="B82" s="5" t="n">
@@ -15253,22 +15239,42 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>GPWFWST1</t>
-        </is>
-      </c>
-      <c r="B83" s="5" t="inlineStr"/>
-      <c r="C83" s="5" t="inlineStr"/>
-      <c r="D83" s="5" t="inlineStr"/>
-      <c r="E83" s="5" t="inlineStr"/>
-      <c r="F83" s="5" t="inlineStr"/>
-      <c r="G83" s="5" t="inlineStr"/>
-      <c r="H83" s="5" t="inlineStr"/>
-      <c r="I83" s="5" t="inlineStr"/>
-      <c r="J83" s="5" t="inlineStr"/>
-      <c r="K83" s="5" t="inlineStr"/>
+          <t>JLA02</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="n">
+        <v>0.9667</v>
+      </c>
+      <c r="C83" s="5" t="n">
+        <v>0.9641</v>
+      </c>
+      <c r="D83" s="5" t="n">
+        <v>0.983</v>
+      </c>
+      <c r="E83" s="5" t="n">
+        <v>0.9782999999999999</v>
+      </c>
+      <c r="F83" s="5" t="n">
+        <v>0.9731</v>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>0.9734</v>
+      </c>
+      <c r="H83" s="5" t="n">
+        <v>0.9755</v>
+      </c>
+      <c r="I83" s="5" t="n">
+        <v>0.9727</v>
+      </c>
+      <c r="J83" s="5" t="n">
+        <v>0.9764</v>
+      </c>
+      <c r="K83" s="5" t="n">
+        <v>0.9789</v>
+      </c>
       <c r="L83" s="5" t="inlineStr"/>
       <c r="M83" s="5" t="n">
-        <v>0.9837</v>
+        <v>0.9768</v>
       </c>
       <c r="N83" s="5" t="inlineStr"/>
       <c r="O83" s="5" t="n">
@@ -15279,22 +15285,42 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>GPWFWST2</t>
-        </is>
-      </c>
-      <c r="B84" s="5" t="inlineStr"/>
-      <c r="C84" s="5" t="inlineStr"/>
-      <c r="D84" s="5" t="inlineStr"/>
-      <c r="E84" s="5" t="inlineStr"/>
-      <c r="F84" s="5" t="inlineStr"/>
-      <c r="G84" s="5" t="inlineStr"/>
-      <c r="H84" s="5" t="inlineStr"/>
-      <c r="I84" s="5" t="inlineStr"/>
-      <c r="J84" s="5" t="inlineStr"/>
-      <c r="K84" s="5" t="inlineStr"/>
+          <t>JLA01</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="n">
+        <v>0.9667</v>
+      </c>
+      <c r="C84" s="5" t="n">
+        <v>0.9641</v>
+      </c>
+      <c r="D84" s="5" t="n">
+        <v>0.983</v>
+      </c>
+      <c r="E84" s="5" t="n">
+        <v>0.9782999999999999</v>
+      </c>
+      <c r="F84" s="5" t="n">
+        <v>0.9731</v>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>0.9734</v>
+      </c>
+      <c r="H84" s="5" t="n">
+        <v>0.9755</v>
+      </c>
+      <c r="I84" s="5" t="n">
+        <v>0.9727</v>
+      </c>
+      <c r="J84" s="5" t="n">
+        <v>0.9764</v>
+      </c>
+      <c r="K84" s="5" t="n">
+        <v>0.9789</v>
+      </c>
       <c r="L84" s="5" t="inlineStr"/>
       <c r="M84" s="5" t="n">
-        <v>0.9837</v>
+        <v>0.9768</v>
       </c>
       <c r="N84" s="5" t="inlineStr"/>
       <c r="O84" s="5" t="n">
@@ -15305,42 +15331,22 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>JLB02</t>
-        </is>
-      </c>
-      <c r="B85" s="5" t="n">
-        <v>0.9667</v>
-      </c>
-      <c r="C85" s="5" t="n">
-        <v>0.9641</v>
-      </c>
-      <c r="D85" s="5" t="n">
-        <v>0.983</v>
-      </c>
-      <c r="E85" s="5" t="n">
-        <v>0.9782999999999999</v>
-      </c>
-      <c r="F85" s="5" t="n">
-        <v>0.9731</v>
-      </c>
-      <c r="G85" s="5" t="n">
-        <v>0.9734</v>
-      </c>
-      <c r="H85" s="5" t="n">
-        <v>0.9755</v>
-      </c>
-      <c r="I85" s="5" t="n">
-        <v>0.9727</v>
-      </c>
-      <c r="J85" s="5" t="n">
-        <v>0.9764</v>
-      </c>
-      <c r="K85" s="5" t="n">
-        <v>0.9789</v>
-      </c>
+          <t>GPWFWST2</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr"/>
+      <c r="C85" s="5" t="inlineStr"/>
+      <c r="D85" s="5" t="inlineStr"/>
+      <c r="E85" s="5" t="inlineStr"/>
+      <c r="F85" s="5" t="inlineStr"/>
+      <c r="G85" s="5" t="inlineStr"/>
+      <c r="H85" s="5" t="inlineStr"/>
+      <c r="I85" s="5" t="inlineStr"/>
+      <c r="J85" s="5" t="inlineStr"/>
+      <c r="K85" s="5" t="inlineStr"/>
       <c r="L85" s="5" t="inlineStr"/>
       <c r="M85" s="5" t="n">
-        <v>0.9768</v>
+        <v>0.9837</v>
       </c>
       <c r="N85" s="5" t="inlineStr"/>
       <c r="O85" s="5" t="n">
@@ -15397,26 +15403,30 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>STOCKYD1</t>
+          <t>DUNDWF2</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr"/>
       <c r="C87" s="5" t="inlineStr"/>
       <c r="D87" s="5" t="inlineStr"/>
       <c r="E87" s="5" t="inlineStr"/>
-      <c r="F87" s="5" t="inlineStr"/>
-      <c r="G87" s="5" t="inlineStr"/>
+      <c r="F87" s="5" t="n">
+        <v>0.9812</v>
+      </c>
+      <c r="G87" s="5" t="n">
+        <v>0.979</v>
+      </c>
       <c r="H87" s="5" t="n">
-        <v>0.9782</v>
+        <v>0.9789</v>
       </c>
       <c r="I87" s="5" t="n">
-        <v>0.9799</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="J87" s="5" t="n">
-        <v>0.9869</v>
+        <v>0.987</v>
       </c>
       <c r="K87" s="5" t="n">
-        <v>0.9812</v>
+        <v>0.981</v>
       </c>
       <c r="L87" s="5" t="inlineStr"/>
       <c r="M87" s="5" t="n">
@@ -15469,7 +15479,7 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>DUNDWF2</t>
+          <t>DUNDWF1</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr"/>
@@ -15507,30 +15517,26 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>DUNDWF1</t>
+          <t>STOCKYD1</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr"/>
       <c r="C90" s="5" t="inlineStr"/>
       <c r="D90" s="5" t="inlineStr"/>
       <c r="E90" s="5" t="inlineStr"/>
-      <c r="F90" s="5" t="n">
+      <c r="F90" s="5" t="inlineStr"/>
+      <c r="G90" s="5" t="inlineStr"/>
+      <c r="H90" s="5" t="n">
+        <v>0.9782</v>
+      </c>
+      <c r="I90" s="5" t="n">
+        <v>0.9799</v>
+      </c>
+      <c r="J90" s="5" t="n">
+        <v>0.9869</v>
+      </c>
+      <c r="K90" s="5" t="n">
         <v>0.9812</v>
-      </c>
-      <c r="G90" s="5" t="n">
-        <v>0.979</v>
-      </c>
-      <c r="H90" s="5" t="n">
-        <v>0.9789</v>
-      </c>
-      <c r="I90" s="5" t="n">
-        <v>0.9824000000000001</v>
-      </c>
-      <c r="J90" s="5" t="n">
-        <v>0.987</v>
-      </c>
-      <c r="K90" s="5" t="n">
-        <v>0.981</v>
       </c>
       <c r="L90" s="5" t="inlineStr"/>
       <c r="M90" s="5" t="n">
@@ -15573,7 +15579,7 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>VPGS5</t>
+          <t>VPGS1</t>
         </is>
       </c>
       <c r="B92" s="5" t="n">
@@ -15619,7 +15625,7 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>VPGS1</t>
+          <t>VPGS5</t>
         </is>
       </c>
       <c r="B93" s="5" t="n">
@@ -15711,7 +15717,7 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>VPGS6</t>
+          <t>LYA3</t>
         </is>
       </c>
       <c r="B95" s="5" t="n">
@@ -15757,7 +15763,7 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>VPGS4</t>
+          <t>LYA2</t>
         </is>
       </c>
       <c r="B96" s="5" t="n">
@@ -15803,7 +15809,7 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>LYNL1</t>
+          <t>VPGS3</t>
         </is>
       </c>
       <c r="B97" s="5" t="n">
@@ -15849,7 +15855,7 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>VPGS3</t>
+          <t>VPGS4</t>
         </is>
       </c>
       <c r="B98" s="5" t="n">
@@ -15895,7 +15901,7 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>LYA4</t>
+          <t>LYA1</t>
         </is>
       </c>
       <c r="B99" s="5" t="n">
@@ -15941,7 +15947,7 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>LOYYB2</t>
+          <t>VPGS6</t>
         </is>
       </c>
       <c r="B100" s="5" t="n">
@@ -15987,7 +15993,7 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>LYA1</t>
+          <t>LYNL1</t>
         </is>
       </c>
       <c r="B101" s="5" t="n">
@@ -16033,7 +16039,7 @@
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>LYA2</t>
+          <t>LYA4</t>
         </is>
       </c>
       <c r="B102" s="5" t="n">
@@ -16079,7 +16085,7 @@
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>LYA3</t>
+          <t>LOYYB2</t>
         </is>
       </c>
       <c r="B103" s="5" t="n">
@@ -16125,82 +16131,82 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>HBESS1</t>
-        </is>
-      </c>
-      <c r="B104" s="5" t="inlineStr"/>
-      <c r="C104" s="5" t="inlineStr"/>
-      <c r="D104" s="5" t="inlineStr"/>
-      <c r="E104" s="5" t="inlineStr"/>
-      <c r="F104" s="5" t="inlineStr"/>
-      <c r="G104" s="5" t="inlineStr"/>
-      <c r="H104" s="5" t="inlineStr"/>
-      <c r="I104" s="5" t="inlineStr"/>
-      <c r="J104" s="5" t="inlineStr"/>
+          <t>LOYYB1</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="n">
+        <v>0.9742</v>
+      </c>
+      <c r="C104" s="5" t="n">
+        <v>0.9723000000000001</v>
+      </c>
+      <c r="D104" s="5" t="n">
+        <v>0.9801</v>
+      </c>
+      <c r="E104" s="5" t="n">
+        <v>0.9798</v>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>0.9754</v>
+      </c>
+      <c r="G104" s="5" t="n">
+        <v>0.976</v>
+      </c>
+      <c r="H104" s="5" t="n">
+        <v>0.9759</v>
+      </c>
+      <c r="I104" s="5" t="n">
+        <v>0.9782999999999999</v>
+      </c>
+      <c r="J104" s="5" t="n">
+        <v>0.9782</v>
+      </c>
       <c r="K104" s="5" t="n">
-        <v>0.9864000000000001</v>
-      </c>
-      <c r="L104" s="5" t="n">
-        <v>0.9804</v>
-      </c>
+        <v>0.9809</v>
+      </c>
+      <c r="L104" s="5" t="inlineStr"/>
       <c r="M104" s="5" t="n">
-        <v>0.9873</v>
-      </c>
-      <c r="N104" s="5" t="n">
-        <v>0.9802</v>
-      </c>
+        <v>0.9815</v>
+      </c>
+      <c r="N104" s="5" t="inlineStr"/>
       <c r="O104" s="5" t="n">
         <v>0.9834000000000001</v>
       </c>
-      <c r="P104" s="5" t="n">
-        <v>0.9873</v>
-      </c>
+      <c r="P104" s="5" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>LOYYB1</t>
-        </is>
-      </c>
-      <c r="B105" s="5" t="n">
-        <v>0.9742</v>
-      </c>
-      <c r="C105" s="5" t="n">
-        <v>0.9723000000000001</v>
-      </c>
-      <c r="D105" s="5" t="n">
-        <v>0.9801</v>
-      </c>
-      <c r="E105" s="5" t="n">
-        <v>0.9798</v>
-      </c>
-      <c r="F105" s="5" t="n">
-        <v>0.9754</v>
-      </c>
-      <c r="G105" s="5" t="n">
-        <v>0.976</v>
-      </c>
-      <c r="H105" s="5" t="n">
-        <v>0.9759</v>
-      </c>
-      <c r="I105" s="5" t="n">
-        <v>0.9782999999999999</v>
-      </c>
-      <c r="J105" s="5" t="n">
-        <v>0.9782</v>
-      </c>
+          <t>HBESS1</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="inlineStr"/>
+      <c r="C105" s="5" t="inlineStr"/>
+      <c r="D105" s="5" t="inlineStr"/>
+      <c r="E105" s="5" t="inlineStr"/>
+      <c r="F105" s="5" t="inlineStr"/>
+      <c r="G105" s="5" t="inlineStr"/>
+      <c r="H105" s="5" t="inlineStr"/>
+      <c r="I105" s="5" t="inlineStr"/>
+      <c r="J105" s="5" t="inlineStr"/>
       <c r="K105" s="5" t="n">
-        <v>0.9809</v>
-      </c>
-      <c r="L105" s="5" t="inlineStr"/>
+        <v>0.9864000000000001</v>
+      </c>
+      <c r="L105" s="5" t="n">
+        <v>0.9804</v>
+      </c>
       <c r="M105" s="5" t="n">
-        <v>0.9815</v>
-      </c>
-      <c r="N105" s="5" t="inlineStr"/>
+        <v>0.9873</v>
+      </c>
+      <c r="N105" s="5" t="n">
+        <v>0.9802</v>
+      </c>
       <c r="O105" s="5" t="n">
         <v>0.9834000000000001</v>
       </c>
-      <c r="P105" s="5" t="inlineStr"/>
+      <c r="P105" s="5" t="n">
+        <v>0.9873</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
@@ -16697,7 +16703,7 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>MREHA2</t>
+          <t>MREHA1</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr"/>
@@ -16731,7 +16737,7 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>MREHA1</t>
+          <t>MREHA2</t>
         </is>
       </c>
       <c r="B119" s="5" t="inlineStr"/>
@@ -16795,87 +16801,87 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>PIBESS1</t>
-        </is>
-      </c>
-      <c r="B121" s="5" t="inlineStr"/>
-      <c r="C121" s="5" t="inlineStr"/>
-      <c r="D121" s="5" t="inlineStr"/>
-      <c r="E121" s="5" t="inlineStr"/>
-      <c r="F121" s="5" t="inlineStr"/>
-      <c r="G121" s="5" t="inlineStr"/>
-      <c r="H121" s="5" t="inlineStr"/>
-      <c r="I121" s="5" t="inlineStr"/>
-      <c r="J121" s="5" t="inlineStr"/>
+          <t>LONGFORD</t>
+        </is>
+      </c>
+      <c r="B121" s="5" t="n">
+        <v>0.9799</v>
+      </c>
+      <c r="C121" s="5" t="n">
+        <v>0.9759</v>
+      </c>
+      <c r="D121" s="5" t="n">
+        <v>0.9886</v>
+      </c>
+      <c r="E121" s="5" t="n">
+        <v>0.9879</v>
+      </c>
+      <c r="F121" s="5" t="n">
+        <v>0.9938</v>
+      </c>
+      <c r="G121" s="5" t="n">
+        <v>0.9955000000000001</v>
+      </c>
+      <c r="H121" s="5" t="n">
+        <v>0.9936</v>
+      </c>
+      <c r="I121" s="5" t="n">
+        <v>0.9977</v>
+      </c>
+      <c r="J121" s="5" t="n">
+        <v>0.9825</v>
+      </c>
       <c r="K121" s="5" t="n">
         <v>0.9848</v>
       </c>
-      <c r="L121" s="5" t="n">
-        <v>0.9848</v>
-      </c>
+      <c r="L121" s="5" t="inlineStr"/>
       <c r="M121" s="5" t="n">
         <v>0.9862</v>
       </c>
-      <c r="N121" s="5" t="n">
-        <v>0.9862</v>
-      </c>
+      <c r="N121" s="5" t="inlineStr"/>
       <c r="O121" s="5" t="n">
         <v>0.992</v>
       </c>
-      <c r="P121" s="5" t="n">
-        <v>0.992</v>
-      </c>
+      <c r="P121" s="5" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>GLENMAG1</t>
-        </is>
-      </c>
-      <c r="B122" s="5" t="n">
-        <v>0.9799</v>
-      </c>
-      <c r="C122" s="5" t="n">
-        <v>0.9759</v>
-      </c>
-      <c r="D122" s="5" t="n">
-        <v>0.9886</v>
-      </c>
-      <c r="E122" s="5" t="n">
-        <v>0.9879</v>
-      </c>
-      <c r="F122" s="5" t="n">
-        <v>0.9938</v>
-      </c>
-      <c r="G122" s="5" t="n">
-        <v>0.9955000000000001</v>
-      </c>
-      <c r="H122" s="5" t="n">
-        <v>0.9936</v>
-      </c>
-      <c r="I122" s="5" t="n">
-        <v>0.9977</v>
-      </c>
-      <c r="J122" s="5" t="n">
-        <v>0.9825</v>
-      </c>
+          <t>PIBESS1</t>
+        </is>
+      </c>
+      <c r="B122" s="5" t="inlineStr"/>
+      <c r="C122" s="5" t="inlineStr"/>
+      <c r="D122" s="5" t="inlineStr"/>
+      <c r="E122" s="5" t="inlineStr"/>
+      <c r="F122" s="5" t="inlineStr"/>
+      <c r="G122" s="5" t="inlineStr"/>
+      <c r="H122" s="5" t="inlineStr"/>
+      <c r="I122" s="5" t="inlineStr"/>
+      <c r="J122" s="5" t="inlineStr"/>
       <c r="K122" s="5" t="n">
         <v>0.9848</v>
       </c>
-      <c r="L122" s="5" t="inlineStr"/>
+      <c r="L122" s="5" t="n">
+        <v>0.9848</v>
+      </c>
       <c r="M122" s="5" t="n">
         <v>0.9862</v>
       </c>
-      <c r="N122" s="5" t="inlineStr"/>
+      <c r="N122" s="5" t="n">
+        <v>0.9862</v>
+      </c>
       <c r="O122" s="5" t="n">
         <v>0.992</v>
       </c>
-      <c r="P122" s="5" t="inlineStr"/>
+      <c r="P122" s="5" t="n">
+        <v>0.992</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>TOORAWF</t>
+          <t>WONWP</t>
         </is>
       </c>
       <c r="B123" s="5" t="n">
@@ -16921,7 +16927,7 @@
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>WONWP</t>
+          <t>GLENMAG1</t>
         </is>
       </c>
       <c r="B124" s="5" t="n">
@@ -16967,7 +16973,7 @@
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>TGNSS1</t>
+          <t>TOORAWF</t>
         </is>
       </c>
       <c r="B125" s="5" t="n">
@@ -17013,7 +17019,7 @@
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>LONGFORD</t>
+          <t>BALDHWF1</t>
         </is>
       </c>
       <c r="B126" s="5" t="n">
@@ -17059,7 +17065,7 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>BALDHWF1</t>
+          <t>TGNSS1</t>
         </is>
       </c>
       <c r="B127" s="5" t="n">
@@ -17185,7 +17191,7 @@
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>CODRNGTON</t>
+          <t>YAMBUKWF</t>
         </is>
       </c>
       <c r="B130" s="5" t="n">
@@ -17231,26 +17237,16 @@
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>YAMBUKWF</t>
-        </is>
-      </c>
-      <c r="B131" s="5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="C131" s="5" t="n">
-        <v>1.0339</v>
-      </c>
-      <c r="D131" s="5" t="n">
-        <v>1.0322</v>
-      </c>
-      <c r="E131" s="5" t="n">
-        <v>1.0149</v>
-      </c>
-      <c r="F131" s="5" t="n">
-        <v>1.0019</v>
-      </c>
+          <t>FSWF1</t>
+        </is>
+      </c>
+      <c r="B131" s="5" t="inlineStr"/>
+      <c r="C131" s="5" t="inlineStr"/>
+      <c r="D131" s="5" t="inlineStr"/>
+      <c r="E131" s="5" t="inlineStr"/>
+      <c r="F131" s="5" t="inlineStr"/>
       <c r="G131" s="5" t="n">
-        <v>1.0063</v>
+        <v>1.0079</v>
       </c>
       <c r="H131" s="5" t="n">
         <v>1.0035</v>
@@ -17277,12 +17273,18 @@
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>TIMWEST</t>
-        </is>
-      </c>
-      <c r="B132" s="5" t="inlineStr"/>
-      <c r="C132" s="5" t="inlineStr"/>
-      <c r="D132" s="5" t="inlineStr"/>
+          <t>OAKLAND1</t>
+        </is>
+      </c>
+      <c r="B132" s="5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="C132" s="5" t="n">
+        <v>1.0339</v>
+      </c>
+      <c r="D132" s="5" t="n">
+        <v>1.0322</v>
+      </c>
       <c r="E132" s="5" t="n">
         <v>1.0149</v>
       </c>
@@ -17317,7 +17319,7 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>OAKLAND1</t>
+          <t>CODRNGTON</t>
         </is>
       </c>
       <c r="B133" s="5" t="n">
@@ -17363,16 +17365,26 @@
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>FSWF1</t>
-        </is>
-      </c>
-      <c r="B134" s="5" t="inlineStr"/>
-      <c r="C134" s="5" t="inlineStr"/>
-      <c r="D134" s="5" t="inlineStr"/>
-      <c r="E134" s="5" t="inlineStr"/>
-      <c r="F134" s="5" t="inlineStr"/>
+          <t>MLWF1</t>
+        </is>
+      </c>
+      <c r="B134" s="5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="C134" s="5" t="n">
+        <v>1.0339</v>
+      </c>
+      <c r="D134" s="5" t="n">
+        <v>1.0322</v>
+      </c>
+      <c r="E134" s="5" t="n">
+        <v>1.0149</v>
+      </c>
+      <c r="F134" s="5" t="n">
+        <v>1.0019</v>
+      </c>
       <c r="G134" s="5" t="n">
-        <v>1.0079</v>
+        <v>1.0063</v>
       </c>
       <c r="H134" s="5" t="n">
         <v>1.0035</v>
@@ -17399,18 +17411,12 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>MLWF1</t>
-        </is>
-      </c>
-      <c r="B135" s="5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="C135" s="5" t="n">
-        <v>1.0339</v>
-      </c>
-      <c r="D135" s="5" t="n">
-        <v>1.0322</v>
-      </c>
+          <t>TIMWEST</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="inlineStr"/>
+      <c r="C135" s="5" t="inlineStr"/>
+      <c r="D135" s="5" t="inlineStr"/>
       <c r="E135" s="5" t="n">
         <v>1.0149</v>
       </c>
@@ -17751,7 +17757,7 @@
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>HASTING3</t>
+          <t>HASTING2</t>
         </is>
       </c>
       <c r="B143" s="5" t="inlineStr"/>
@@ -17781,7 +17787,7 @@
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>HASTING2</t>
+          <t>HASTING3</t>
         </is>
       </c>
       <c r="B144" s="5" t="inlineStr"/>
@@ -17849,17 +17855,17 @@
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>WOLLERT1</t>
+          <t>RUBICON</t>
         </is>
       </c>
       <c r="B146" s="5" t="n">
-        <v>0.9987</v>
+        <v>1</v>
       </c>
       <c r="C146" s="5" t="n">
-        <v>0.9985000000000001</v>
+        <v>1</v>
       </c>
       <c r="D146" s="5" t="n">
-        <v>0.998</v>
+        <v>1</v>
       </c>
       <c r="E146" s="5" t="n">
         <v>0.9979</v>
@@ -17895,17 +17901,17 @@
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>RUBICON</t>
+          <t>EILDON3</t>
         </is>
       </c>
       <c r="B147" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C147" s="5" t="n">
-        <v>1</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="D147" s="5" t="n">
-        <v>1</v>
+        <v>0.998</v>
       </c>
       <c r="E147" s="5" t="n">
         <v>0.9979</v>
@@ -17941,11 +17947,11 @@
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>EILDON3</t>
+          <t>WOLLERT1</t>
         </is>
       </c>
       <c r="B148" s="5" t="n">
-        <v>1</v>
+        <v>0.9987</v>
       </c>
       <c r="C148" s="5" t="n">
         <v>0.9985000000000001</v>
@@ -18067,7 +18073,7 @@
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>LNGS2</t>
+          <t>LNGS1</t>
         </is>
       </c>
       <c r="B151" s="5" t="n">
@@ -18113,7 +18119,7 @@
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>LNGS1</t>
+          <t>LNGS2</t>
         </is>
       </c>
       <c r="B152" s="5" t="n">
@@ -18343,14 +18349,20 @@
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>YAWWF1</t>
-        </is>
-      </c>
-      <c r="B157" s="5" t="inlineStr"/>
-      <c r="C157" s="5" t="inlineStr"/>
-      <c r="D157" s="5" t="inlineStr"/>
+          <t>CBWF1</t>
+        </is>
+      </c>
+      <c r="B157" s="5" t="n">
+        <v>1.0672</v>
+      </c>
+      <c r="C157" s="5" t="n">
+        <v>1.0664</v>
+      </c>
+      <c r="D157" s="5" t="n">
+        <v>1.0398</v>
+      </c>
       <c r="E157" s="5" t="n">
-        <v>1.0136</v>
+        <v>1.0139</v>
       </c>
       <c r="F157" s="5" t="n">
         <v>1.0012</v>
@@ -18383,20 +18395,14 @@
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>CBWF1</t>
-        </is>
-      </c>
-      <c r="B158" s="5" t="n">
-        <v>1.0672</v>
-      </c>
-      <c r="C158" s="5" t="n">
-        <v>1.0664</v>
-      </c>
-      <c r="D158" s="5" t="n">
-        <v>1.0398</v>
-      </c>
+          <t>YAWWF1</t>
+        </is>
+      </c>
+      <c r="B158" s="5" t="inlineStr"/>
+      <c r="C158" s="5" t="inlineStr"/>
+      <c r="D158" s="5" t="inlineStr"/>
       <c r="E158" s="5" t="n">
-        <v>1.0139</v>
+        <v>1.0136</v>
       </c>
       <c r="F158" s="5" t="n">
         <v>1.0012</v>
@@ -18429,7 +18435,7 @@
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
         <is>
-          <t>TATURA01</t>
+          <t>SHEP1</t>
         </is>
       </c>
       <c r="B159" s="5" t="n">
@@ -18475,7 +18481,7 @@
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>SHEP1</t>
+          <t>TATURA01</t>
         </is>
       </c>
       <c r="B160" s="5" t="n">
@@ -18613,11 +18619,11 @@
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>MORNL1</t>
+          <t>APS</t>
         </is>
       </c>
       <c r="B163" s="5" t="n">
-        <v>0.9799</v>
+        <v>0.9915</v>
       </c>
       <c r="C163" s="5" t="inlineStr"/>
       <c r="D163" s="5" t="inlineStr"/>
@@ -18637,11 +18643,11 @@
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>APS</t>
+          <t>MORNL1</t>
         </is>
       </c>
       <c r="B164" s="5" t="n">
-        <v>0.9915</v>
+        <v>0.9799</v>
       </c>
       <c r="C164" s="5" t="inlineStr"/>
       <c r="D164" s="5" t="inlineStr"/>
@@ -18685,7 +18691,7 @@
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>MOR3</t>
+          <t>MOR2</t>
         </is>
       </c>
       <c r="B166" s="5" t="n">
@@ -18709,7 +18715,7 @@
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
         <is>
-          <t>MOR2</t>
+          <t>MOR3</t>
         </is>
       </c>
       <c r="B167" s="5" t="n">
@@ -18785,7 +18791,7 @@
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>HWPS6</t>
+          <t>HWPNL1</t>
         </is>
       </c>
       <c r="B170" s="5" t="n">
@@ -18811,7 +18817,7 @@
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
         <is>
-          <t>HWPS5</t>
+          <t>HWPS1</t>
         </is>
       </c>
       <c r="B171" s="5" t="n">
@@ -18837,7 +18843,7 @@
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>HWPS4</t>
+          <t>HWPS2</t>
         </is>
       </c>
       <c r="B172" s="5" t="n">
@@ -18889,7 +18895,7 @@
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>HWPS2</t>
+          <t>HWPS4</t>
         </is>
       </c>
       <c r="B174" s="5" t="n">
@@ -18915,7 +18921,7 @@
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
         <is>
-          <t>HWPS1</t>
+          <t>HWPS5</t>
         </is>
       </c>
       <c r="B175" s="5" t="n">
@@ -18941,7 +18947,7 @@
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>HWPNL1</t>
+          <t>HWPS6</t>
         </is>
       </c>
       <c r="B176" s="5" t="n">
@@ -18967,17 +18973,17 @@
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
         <is>
-          <t>WYNDW</t>
+          <t>MORNW</t>
         </is>
       </c>
       <c r="B177" s="5" t="n">
-        <v>1.0032</v>
+        <v>0.9923999999999999</v>
       </c>
       <c r="C177" s="5" t="n">
-        <v>1.0068</v>
+        <v>0.9925</v>
       </c>
       <c r="D177" s="5" t="n">
-        <v>1.0084</v>
+        <v>0.9963</v>
       </c>
       <c r="E177" s="5" t="inlineStr"/>
       <c r="F177" s="5" t="inlineStr"/>
@@ -18995,17 +19001,17 @@
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>MORNW</t>
+          <t>WYNDW</t>
         </is>
       </c>
       <c r="B178" s="5" t="n">
-        <v>0.9923999999999999</v>
+        <v>1.0032</v>
       </c>
       <c r="C178" s="5" t="n">
-        <v>0.9925</v>
+        <v>1.0068</v>
       </c>
       <c r="D178" s="5" t="n">
-        <v>0.9963</v>
+        <v>1.0084</v>
       </c>
       <c r="E178" s="5" t="inlineStr"/>
       <c r="F178" s="5" t="inlineStr"/>
@@ -19099,35 +19105,35 @@
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t>BROADMDW</t>
+          <t>SVALE1</t>
         </is>
       </c>
       <c r="B181" s="5" t="n">
-        <v>1</v>
+        <v>0.997</v>
       </c>
       <c r="C181" s="5" t="n">
-        <v>1</v>
+        <v>0.9972</v>
       </c>
       <c r="D181" s="5" t="n">
-        <v>1</v>
+        <v>0.9989</v>
       </c>
       <c r="E181" s="5" t="n">
-        <v>1</v>
+        <v>0.9986</v>
       </c>
       <c r="F181" s="5" t="n">
-        <v>1</v>
+        <v>0.9987</v>
       </c>
       <c r="G181" s="5" t="n">
-        <v>1</v>
+        <v>0.9984</v>
       </c>
       <c r="H181" s="5" t="n">
-        <v>1</v>
+        <v>0.9957</v>
       </c>
       <c r="I181" s="5" t="n">
-        <v>1</v>
+        <v>0.9972</v>
       </c>
       <c r="J181" s="5" t="n">
-        <v>1</v>
+        <v>1.0001</v>
       </c>
       <c r="K181" s="5" t="inlineStr"/>
       <c r="L181" s="5" t="inlineStr"/>
@@ -19139,35 +19145,35 @@
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>SVALE1</t>
+          <t>BROADMDW</t>
         </is>
       </c>
       <c r="B182" s="5" t="n">
-        <v>0.997</v>
+        <v>1</v>
       </c>
       <c r="C182" s="5" t="n">
-        <v>0.9972</v>
+        <v>1</v>
       </c>
       <c r="D182" s="5" t="n">
-        <v>0.9989</v>
+        <v>1</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>0.9986</v>
+        <v>1</v>
       </c>
       <c r="F182" s="5" t="n">
-        <v>0.9987</v>
+        <v>1</v>
       </c>
       <c r="G182" s="5" t="n">
-        <v>0.9984</v>
+        <v>1</v>
       </c>
       <c r="H182" s="5" t="n">
-        <v>0.9957</v>
+        <v>1</v>
       </c>
       <c r="I182" s="5" t="n">
-        <v>0.9972</v>
+        <v>1</v>
       </c>
       <c r="J182" s="5" t="n">
-        <v>1.0001</v>
+        <v>1</v>
       </c>
       <c r="K182" s="5" t="inlineStr"/>
       <c r="L182" s="5" t="inlineStr"/>
@@ -19209,32 +19215,26 @@
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>GANNBG1</t>
+          <t>BULBESG1</t>
         </is>
       </c>
       <c r="B184" s="5" t="inlineStr"/>
       <c r="C184" s="5" t="inlineStr"/>
       <c r="D184" s="5" t="inlineStr"/>
-      <c r="E184" s="5" t="n">
-        <v>1.007</v>
-      </c>
-      <c r="F184" s="5" t="n">
-        <v>0.9643</v>
-      </c>
-      <c r="G184" s="5" t="n">
-        <v>0.9792999999999999</v>
-      </c>
+      <c r="E184" s="5" t="inlineStr"/>
+      <c r="F184" s="5" t="inlineStr"/>
+      <c r="G184" s="5" t="inlineStr"/>
       <c r="H184" s="5" t="n">
-        <v>0.9772999999999999</v>
+        <v>0.8949</v>
       </c>
       <c r="I184" s="5" t="n">
-        <v>1.0026</v>
+        <v>0.8839</v>
       </c>
       <c r="J184" s="5" t="n">
-        <v>1.029</v>
+        <v>0.8821</v>
       </c>
       <c r="K184" s="5" t="n">
-        <v>1.0155</v>
+        <v>0.8733</v>
       </c>
       <c r="L184" s="5" t="inlineStr"/>
       <c r="M184" s="5" t="inlineStr"/>
@@ -19245,7 +19245,7 @@
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
         <is>
-          <t>BULBESG1</t>
+          <t>HBESSG1</t>
         </is>
       </c>
       <c r="B185" s="5" t="inlineStr"/>
@@ -19254,17 +19254,15 @@
       <c r="E185" s="5" t="inlineStr"/>
       <c r="F185" s="5" t="inlineStr"/>
       <c r="G185" s="5" t="inlineStr"/>
-      <c r="H185" s="5" t="n">
-        <v>0.8949</v>
-      </c>
+      <c r="H185" s="5" t="inlineStr"/>
       <c r="I185" s="5" t="n">
-        <v>0.8839</v>
+        <v>0.9785</v>
       </c>
       <c r="J185" s="5" t="n">
-        <v>0.8821</v>
+        <v>0.9789</v>
       </c>
       <c r="K185" s="5" t="n">
-        <v>0.8733</v>
+        <v>0.9804</v>
       </c>
       <c r="L185" s="5" t="inlineStr"/>
       <c r="M185" s="5" t="inlineStr"/>
@@ -19275,7 +19273,7 @@
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t>HBESSG1</t>
+          <t>FNWF1</t>
         </is>
       </c>
       <c r="B186" s="5" t="inlineStr"/>
@@ -19283,16 +19281,20 @@
       <c r="D186" s="5" t="inlineStr"/>
       <c r="E186" s="5" t="inlineStr"/>
       <c r="F186" s="5" t="inlineStr"/>
-      <c r="G186" s="5" t="inlineStr"/>
-      <c r="H186" s="5" t="inlineStr"/>
+      <c r="G186" s="5" t="n">
+        <v>1.0079</v>
+      </c>
+      <c r="H186" s="5" t="n">
+        <v>1.0035</v>
+      </c>
       <c r="I186" s="5" t="n">
-        <v>0.9785</v>
+        <v>0.9972</v>
       </c>
       <c r="J186" s="5" t="n">
-        <v>0.9789</v>
+        <v>0.9933</v>
       </c>
       <c r="K186" s="5" t="n">
-        <v>0.9804</v>
+        <v>0.9993</v>
       </c>
       <c r="L186" s="5" t="inlineStr"/>
       <c r="M186" s="5" t="inlineStr"/>
@@ -19303,32 +19305,32 @@
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
         <is>
-          <t>BALBG1</t>
+          <t>GANNBG1</t>
         </is>
       </c>
       <c r="B187" s="5" t="inlineStr"/>
       <c r="C187" s="5" t="inlineStr"/>
       <c r="D187" s="5" t="inlineStr"/>
       <c r="E187" s="5" t="n">
-        <v>0.9948</v>
+        <v>1.007</v>
       </c>
       <c r="F187" s="5" t="n">
-        <v>0.9634</v>
+        <v>0.9643</v>
       </c>
       <c r="G187" s="5" t="n">
-        <v>0.9643</v>
+        <v>0.9792999999999999</v>
       </c>
       <c r="H187" s="5" t="n">
-        <v>0.9573</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="I187" s="5" t="n">
-        <v>0.9663</v>
+        <v>1.0026</v>
       </c>
       <c r="J187" s="5" t="n">
-        <v>0.9756</v>
+        <v>1.029</v>
       </c>
       <c r="K187" s="5" t="n">
-        <v>0.9713000000000001</v>
+        <v>1.0155</v>
       </c>
       <c r="L187" s="5" t="inlineStr"/>
       <c r="M187" s="5" t="inlineStr"/>
@@ -19367,28 +19369,32 @@
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
         <is>
-          <t>FNWF1</t>
+          <t>BALBG1</t>
         </is>
       </c>
       <c r="B189" s="5" t="inlineStr"/>
       <c r="C189" s="5" t="inlineStr"/>
       <c r="D189" s="5" t="inlineStr"/>
-      <c r="E189" s="5" t="inlineStr"/>
-      <c r="F189" s="5" t="inlineStr"/>
+      <c r="E189" s="5" t="n">
+        <v>0.9948</v>
+      </c>
+      <c r="F189" s="5" t="n">
+        <v>0.9634</v>
+      </c>
       <c r="G189" s="5" t="n">
-        <v>1.0079</v>
+        <v>0.9643</v>
       </c>
       <c r="H189" s="5" t="n">
-        <v>1.0035</v>
+        <v>0.9573</v>
       </c>
       <c r="I189" s="5" t="n">
-        <v>0.9972</v>
+        <v>0.9663</v>
       </c>
       <c r="J189" s="5" t="n">
-        <v>0.9933</v>
+        <v>0.9756</v>
       </c>
       <c r="K189" s="5" t="n">
-        <v>0.9993</v>
+        <v>0.9713000000000001</v>
       </c>
       <c r="L189" s="5" t="inlineStr"/>
       <c r="M189" s="5" t="inlineStr"/>
@@ -19399,7 +19405,7 @@
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
         <is>
-          <t>CHPSTWF1</t>
+          <t>BBASEHOS</t>
         </is>
       </c>
       <c r="B190" s="5" t="n">
@@ -19443,7 +19449,7 @@
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
         <is>
-          <t>BBASEHOS</t>
+          <t>CHPSTWF1</t>
         </is>
       </c>
       <c r="B191" s="5" t="n">
@@ -19908,12 +19914,12 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>WUNUSF1</t>
+          <t>GIRGSF</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Wunghnu Solar Farm</t>
+          <t>Girgarre Solar Farm</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -19937,12 +19943,12 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>NUMURSF1</t>
+          <t>WUNUSF1</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Numurkah Solar Farm</t>
+          <t>Wunghnu Solar Farm</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -19966,12 +19972,12 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>GIRGSF</t>
+          <t>NUMURSF1</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Girgarre Solar Farm</t>
+          <t>Numurkah Solar Farm</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -20227,7 +20233,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>WKIEWA1</t>
+          <t>WKIEWA2</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -20256,7 +20262,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>WKIEWA2</t>
+          <t>WKIEWA1</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -20285,17 +20291,17 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>YWNGAHYD</t>
+          <t>SHEP1</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Yarrawonga Hydro Power Station</t>
+          <t>Shepparton Wastewater Treatment Facility</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Hydro</t>
+          <t>Other Renewable</t>
         </is>
       </c>
       <c r="D22" s="5" t="n">
@@ -20358,12 +20364,12 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>YATSF1</t>
+          <t>KARSF1</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Yatpool Solar Farm</t>
+          <t>Karadoc Solar Farm</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -20387,12 +20393,12 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>KARSF1</t>
+          <t>YATSF1</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Karadoc Solar Farm</t>
+          <t>Yatpool Solar Farm</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -20445,12 +20451,12 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>BANN1</t>
+          <t>WEMENSF1</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Bannerton Solar Park</t>
+          <t>Wemen Solar Farm</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -20474,12 +20480,12 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>WEMENSF1</t>
+          <t>BANN1</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Wemen Solar Farm</t>
+          <t>Bannerton Solar Park</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -20590,17 +20596,17 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>BALDHWF1</t>
+          <t>LONGFORD</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Bald Hills Wind Farm</t>
+          <t>LONGFORD PLANT</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D35" s="5" t="n">
@@ -20619,17 +20625,17 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>WONWP</t>
+          <t>PIBESS1</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Wonthaggi Wind Farm</t>
+          <t>Phillip Island BESS</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D36" s="5" t="n">
@@ -20648,17 +20654,17 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>TGNSS1</t>
+          <t>WONWP</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Traralgon Network Support Station</t>
+          <t>Wonthaggi Wind Farm</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D37" s="5" t="n">
@@ -20677,17 +20683,17 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>LONGFORD</t>
+          <t>GLENMAG1</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>LONGFORD PLANT</t>
+          <t>Glenmaggie Hydro Power Station</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Hydro</t>
         </is>
       </c>
       <c r="D38" s="5" t="n">
@@ -20735,17 +20741,17 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>PIBESS1</t>
+          <t>BALDHWF1</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Phillip Island BESS</t>
+          <t>Bald Hills Wind Farm</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D40" s="5" t="n">
@@ -20764,17 +20770,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>GLENMAG1</t>
+          <t>TGNSS1</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Glenmaggie Hydro Power Station</t>
+          <t>Traralgon Network Support Station</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Hydro</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D41" s="5" t="n">
@@ -20822,7 +20828,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>JLB02</t>
+          <t>JLB01</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -20851,7 +20857,7 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>JLB01</t>
+          <t>JLB02</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
